--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>172</v>
       </c>
       <c r="T2" t="n">
-        <v>1743</v>
+        <v>1752</v>
       </c>
       <c r="U2" t="n">
-        <v>1591</v>
+        <v>1600</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>45280</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>44865</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41957-2025</t>
+          <t>A 40643-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2034,14 +2034,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45903</v>
+        <v>45558</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2090,146 +2090,146 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Bergsslok
+Getrams</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 41957-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45903</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Gröngöling
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 40643-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45558</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Bergsslok
-Getrams</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
         <v/>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
         <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46757-2023</t>
+          <t>A 15452-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45198</v>
+        <v>45020</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2486,8 +2486,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2496,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2511,7 +2516,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2523,50 +2528,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33751-2024</t>
+          <t>A 6893-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2576,14 +2581,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45520</v>
+        <v>46057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2595,25 +2600,20 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2628,59 +2628,55 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 6893-2026</t>
+          <t>A 39716-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2694,10 +2690,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46057</v>
+        <v>45166</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2710,22 +2706,22 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2737,7 +2733,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2750,42 +2746,46 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 39716-2023</t>
+          <t>A 33751-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2795,14 +2795,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45166</v>
+        <v>45520</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2814,8 +2814,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2827,10 +2832,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2848,53 +2853,53 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15452-2023</t>
+          <t>A 46757-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2908,10 +2913,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45020</v>
+        <v>45198</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2923,13 +2928,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2938,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2953,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2965,43 +2965,43 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
         <v/>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
         <v>44618</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44468</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44467</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>44619</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>44474</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45251</v>
+        <v>45089</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3563,8 +3563,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3607,7 +3612,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 49592-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3617,14 +3622,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45330</v>
+        <v>45211</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3680,7 +3685,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 49592-2023</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3690,14 +3695,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45211</v>
+        <v>45700</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3710,7 +3715,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3753,7 +3758,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 24105-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3767,10 +3772,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44904</v>
+        <v>45796</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3783,7 +3788,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3826,7 +3831,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 41702-2023</t>
+          <t>A 60934-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3840,10 +3845,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45176</v>
+        <v>45261</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3855,13 +3860,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3904,7 +3904,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 60949-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45575</v>
+        <v>45996</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>21.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3977,7 +3977,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 60969-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45160</v>
+        <v>45996</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>18.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4050,7 +4050,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45054</v>
+        <v>45540</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4123,7 +4123,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 24636-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45222</v>
+        <v>45084</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 3673-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44904</v>
+        <v>46043</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45061</v>
+        <v>44989</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4356,10 +4356,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44749</v>
+        <v>46048</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4415,7 +4415,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 28681-2025</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45819</v>
+        <v>45461</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4488,7 +4488,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 42572-2024</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4498,14 +4498,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45565</v>
+        <v>44571</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4561,7 +4561,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4575,10 +4575,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44894</v>
+        <v>44827</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4590,8 +4590,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4634,7 +4639,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 28681-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4648,10 +4653,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45930</v>
+        <v>45819</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4664,7 +4669,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.3</v>
+        <v>7.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4707,7 +4712,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4721,10 +4726,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45940</v>
+        <v>45930</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4737,7 +4742,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4780,7 +4785,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4794,10 +4799,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46086</v>
+        <v>45940</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4810,7 +4815,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4853,7 +4858,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4867,10 +4872,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46097</v>
+        <v>44642</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4882,8 +4887,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4926,7 +4936,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4940,10 +4950,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44989</v>
+        <v>44557</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4956,7 +4966,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4999,7 +5009,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5013,10 +5023,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45089</v>
+        <v>46086</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5028,13 +5038,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5077,7 +5082,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5091,10 +5096,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45089</v>
+        <v>45478</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5106,13 +5111,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5155,7 +5155,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5165,14 +5165,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44502</v>
+        <v>46097</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>14.7</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5228,7 +5228,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 41702-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5242,10 +5242,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45261</v>
+        <v>45176</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5257,8 +5257,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5301,7 +5306,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5315,10 +5320,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45061</v>
+        <v>44803</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5331,7 +5336,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.3</v>
+        <v>6.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5374,7 +5379,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 60969-2025</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5384,14 +5389,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45996</v>
+        <v>44678</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5404,7 +5409,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5447,7 +5452,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60949-2025</t>
+          <t>A 42572-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5461,10 +5466,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45996</v>
+        <v>45565</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5477,7 +5482,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>21.9</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5520,7 +5525,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5534,10 +5539,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45187</v>
+        <v>45575</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5550,7 +5555,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5593,7 +5598,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5603,14 +5608,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44546</v>
+        <v>45257</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5622,8 +5627,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5666,7 +5676,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3673-2026</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5676,14 +5686,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46043</v>
+        <v>45363</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5696,7 +5706,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5739,7 +5749,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5749,14 +5759,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46048</v>
+        <v>44776</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5768,8 +5778,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5812,7 +5827,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5826,10 +5841,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44557</v>
+        <v>45035</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5842,7 +5857,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5885,7 +5900,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5895,14 +5910,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45035</v>
+        <v>45330</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5915,7 +5930,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5958,7 +5973,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5972,10 +5987,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44606</v>
+        <v>45061</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5988,7 +6003,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6031,7 +6046,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 22913-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6045,10 +6060,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45191</v>
+        <v>46159</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6062,11 +6077,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6109,7 +6124,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6119,14 +6134,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45363</v>
+        <v>44904</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6139,7 +6154,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6182,7 +6197,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6192,14 +6207,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44678</v>
+        <v>44749</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6212,7 +6227,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6255,7 +6270,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6269,10 +6284,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45478</v>
+        <v>45110</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6285,7 +6300,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6328,7 +6343,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6338,14 +6353,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44571</v>
+        <v>45713</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6357,8 +6372,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6401,7 +6421,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 22913-2026</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6415,10 +6435,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46159</v>
+        <v>45110</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6430,13 +6450,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6479,7 +6494,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24636-2023</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6489,14 +6504,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45084</v>
+        <v>44502</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6509,7 +6524,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>14.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6552,7 +6567,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6562,14 +6577,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45653</v>
+        <v>45191</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6581,8 +6596,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6625,7 +6645,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6639,10 +6659,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45110</v>
+        <v>46275</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6655,7 +6675,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6698,7 +6718,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6708,14 +6728,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44776</v>
+        <v>46275</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6727,13 +6747,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6776,7 +6791,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6790,10 +6805,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45110</v>
+        <v>45261</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6806,7 +6821,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6849,7 +6864,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6863,10 +6878,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45257</v>
+        <v>45054</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6878,13 +6893,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6927,7 +6937,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2496-2024</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6941,10 +6951,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45313</v>
+        <v>45160</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6956,13 +6966,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>3.3</v>
+        <v>18.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7005,7 +7010,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 2496-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7019,10 +7024,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45533</v>
+        <v>45313</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7034,8 +7039,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7078,7 +7088,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7092,10 +7102,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44803</v>
+        <v>44904</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7108,7 +7118,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7151,7 +7161,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7161,14 +7171,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44803</v>
+        <v>44546</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7181,7 +7191,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7224,7 +7234,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7234,14 +7244,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45700</v>
+        <v>45061</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7254,7 +7264,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7297,7 +7307,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7311,10 +7321,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44992</v>
+        <v>45251</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7327,7 +7337,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7370,7 +7380,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 60922-2023</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7384,10 +7394,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45261</v>
+        <v>45187</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7400,7 +7410,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>7.6</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7443,7 +7453,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7457,10 +7467,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44642</v>
+        <v>44894</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7472,13 +7482,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7521,7 +7526,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7535,10 +7540,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44827</v>
+        <v>44803</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7550,13 +7555,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 60922-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45540</v>
+        <v>45261</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7672,7 +7672,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7682,14 +7682,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45162</v>
+        <v>45653</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7745,7 +7745,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7755,14 +7755,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44776</v>
+        <v>45162</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7774,13 +7774,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7823,7 +7818,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7837,10 +7832,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45644</v>
+        <v>44606</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7853,7 +7848,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7896,7 +7891,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7910,10 +7905,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45713</v>
+        <v>44992</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7925,13 +7920,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>9.699999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7974,7 +7964,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7988,10 +7978,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45461</v>
+        <v>45089</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8003,8 +7993,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8047,7 +8042,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8061,10 +8056,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46275</v>
+        <v>45644</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8077,7 +8072,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.6</v>
+        <v>0.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8120,7 +8115,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8134,10 +8129,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46275</v>
+        <v>45222</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8150,7 +8145,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8193,7 +8188,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8203,14 +8198,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45567</v>
+        <v>44776</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8222,8 +8217,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8266,7 +8266,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45461</v>
+        <v>45533</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>12.5</v>
+        <v>0.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8356,7 +8356,7 @@
         <v>45684</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21513-2025</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8426,10 +8426,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45782</v>
+        <v>45567</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8485,7 +8485,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48375-2024</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8499,10 +8499,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45590</v>
+        <v>45461</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8514,13 +8514,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>4.8</v>
+        <v>12.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8563,7 +8558,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 22402-2025</t>
+          <t>A 21513-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8577,10 +8572,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45786</v>
+        <v>45782</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8593,7 +8588,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8636,7 +8631,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 35961-2024</t>
+          <t>A 19031-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8646,14 +8641,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45533</v>
+        <v>45427</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8666,7 +8661,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8709,7 +8704,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 19031-2024</t>
+          <t>A 35961-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8719,14 +8714,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45427</v>
+        <v>45533</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8739,7 +8734,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8782,7 +8777,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 24105-2025</t>
+          <t>A 22402-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8796,10 +8791,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45796</v>
+        <v>45786</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8812,7 +8807,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8855,7 +8850,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 60934-2023</t>
+          <t>A 48375-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8869,10 +8864,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45261</v>
+        <v>45590</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8884,8 +8879,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         <v>72</v>
       </c>
       <c r="K2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L2" t="n">
         <v>61</v>
@@ -649,13 +649,13 @@
         <v>39</v>
       </c>
       <c r="S2" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T2" t="n">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="U2" t="n">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -777,6 +777,7 @@
 Gulpudrad spiklav
 Hasselticka
 Kornig nållav
+Kransrams
 Liten baronmossa
 Lundbräsma
 Läderskål
@@ -886,7 +887,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1017,7 +1018,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1137,7 +1138,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1256,7 +1257,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1374,7 +1375,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1490,7 +1491,7 @@
         <v>45280</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1608,7 +1609,7 @@
         <v>44865</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1716,7 +1717,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1828,7 +1829,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1935,7 +1936,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2024,7 +2025,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 40643-2024</t>
+          <t>A 64345-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2038,10 +2039,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45558</v>
+        <v>45280</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2054,16 +2055,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -2078,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2087,377 +2088,377 @@
         <v>2</v>
       </c>
       <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 64345-2023 artfynd.xlsx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 64345-2023 karta.png", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 64345-2023 georefererad karta.tif", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 64345-2023 FSC-klagomål.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 64345-2023 FSC-klagomål mail.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 64345-2023 tillsynsbegäran.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 64345-2023 tillsynsbegäran mail.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 64345-2023 prioriterade fågelarter.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 41957-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45903</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J14" t="n">
         <v>2</v>
       </c>
-      <c r="U13" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Gröngöling
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 40643-2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45558</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Bergsslok
 Getrams</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 41957-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 22874-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
-        <v>45903</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="D16" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="T16" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Gröngöling
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 22874-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46156</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Kandelabersvamp
 Blåsippa</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 22874-2026 artfynd.xlsx", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 22874-2026 karta.png", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 22874-2026 georefererad karta.tif", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 22874-2026 FSC-klagomål.docx", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 22874-2026 FSC-klagomål mail.docx", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 22874-2026 tillsynsbegäran.docx", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 22874-2026 tillsynsbegäran mail.docx", "A 22874-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 64345-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45280</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 64345-2023 artfynd.xlsx", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 64345-2023 karta.png", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 64345-2023 georefererad karta.tif", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 64345-2023 FSC-klagomål.docx", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 64345-2023 FSC-klagomål mail.docx", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 64345-2023 tillsynsbegäran.docx", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 64345-2023 tillsynsbegäran mail.docx", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 64345-2023 prioriterade fågelarter.docx", "A 64345-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 15452-2023</t>
+          <t>A 46757-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2471,10 +2472,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45020</v>
+        <v>45198</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2486,13 +2487,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2501,7 +2497,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2516,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2528,43 +2524,43 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
         <v/>
       </c>
     </row>
@@ -2588,7 +2584,7 @@
         <v>46057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2676,7 +2672,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 39716-2023</t>
+          <t>A 33751-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2686,14 +2682,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45166</v>
+        <v>45520</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2705,8 +2701,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2718,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2739,53 +2740,53 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33751-2024</t>
+          <t>A 39716-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2795,14 +2796,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45520</v>
+        <v>45166</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2814,13 +2815,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2832,10 +2828,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2853,53 +2849,53 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 46757-2023</t>
+          <t>A 15452-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2913,10 +2909,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45198</v>
+        <v>45020</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2928,8 +2924,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2938,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2953,7 +2954,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2965,43 +2966,43 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
         <v/>
       </c>
     </row>
@@ -3025,7 +3026,7 @@
         <v>44618</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3098,7 +3099,7 @@
         <v>44468</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3176,7 +3177,7 @@
         <v>44467</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3249,7 +3250,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3327,7 +3328,7 @@
         <v>44619</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3400,7 +3401,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3461,7 +3462,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 55112-2021</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3471,14 +3472,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44474</v>
+        <v>44776</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,8 +3491,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3534,7 +3540,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3548,10 +3554,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45089</v>
+        <v>45251</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3563,13 +3569,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3629,7 +3630,7 @@
         <v>45211</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3685,7 +3686,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3699,10 +3700,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45700</v>
+        <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3715,7 +3716,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3758,7 +3759,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 24105-2025</t>
+          <t>A 55112-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3772,10 +3773,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45796</v>
+        <v>44474</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3788,7 +3789,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3831,7 +3832,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60934-2023</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3845,10 +3846,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45261</v>
+        <v>45257</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3860,8 +3861,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3904,7 +3910,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60949-2025</t>
+          <t>A 2496-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3918,10 +3924,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45996</v>
+        <v>45313</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3933,8 +3939,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>21.9</v>
+        <v>3.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3977,7 +3988,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60969-2025</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3991,10 +4002,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45996</v>
+        <v>45533</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4007,7 +4018,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>8.800000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4050,7 +4061,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4064,10 +4075,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45540</v>
+        <v>44803</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4080,7 +4091,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>6.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4123,7 +4134,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24636-2023</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4137,10 +4148,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45084</v>
+        <v>44803</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4153,7 +4164,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4196,7 +4207,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3673-2026</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4210,10 +4221,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46043</v>
+        <v>44904</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4226,7 +4237,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4269,7 +4280,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4283,10 +4294,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44989</v>
+        <v>46086</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4299,7 +4310,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4342,7 +4353,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 41702-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4356,10 +4367,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46048</v>
+        <v>45176</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4371,8 +4382,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4415,7 +4431,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4429,10 +4445,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45461</v>
+        <v>46097</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4445,7 +4461,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4488,7 +4504,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4502,10 +4518,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44571</v>
+        <v>45700</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4518,7 +4534,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4561,7 +4577,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4575,10 +4591,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44827</v>
+        <v>45160</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4590,13 +4606,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>18.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4639,7 +4650,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28681-2025</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4653,10 +4664,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45819</v>
+        <v>45575</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4669,7 +4680,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4712,7 +4723,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4726,10 +4737,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45930</v>
+        <v>45054</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4742,7 +4753,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4785,7 +4796,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4799,10 +4810,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45940</v>
+        <v>45222</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4815,7 +4826,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4858,7 +4869,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4872,10 +4883,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44642</v>
+        <v>44904</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4887,13 +4898,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4936,7 +4942,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4950,10 +4956,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44557</v>
+        <v>45930</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4966,7 +4972,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5009,7 +5015,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5023,10 +5029,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46086</v>
+        <v>45061</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5039,7 +5045,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5082,7 +5088,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5096,10 +5102,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45478</v>
+        <v>44749</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5112,7 +5118,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5155,7 +5161,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5169,10 +5175,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46097</v>
+        <v>45940</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5185,7 +5191,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5228,7 +5234,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 41702-2023</t>
+          <t>A 42572-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5242,10 +5248,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45176</v>
+        <v>45565</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5257,13 +5263,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5306,7 +5307,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5320,10 +5321,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44803</v>
+        <v>44894</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5336,7 +5337,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6.1</v>
+        <v>5.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5379,7 +5380,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5389,14 +5390,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44678</v>
+        <v>44992</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5409,7 +5410,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5452,7 +5453,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 42572-2024</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5462,14 +5463,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45565</v>
+        <v>45363</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5482,7 +5483,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5525,7 +5526,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 60922-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5539,10 +5540,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45575</v>
+        <v>45261</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5555,7 +5556,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>7.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5598,7 +5599,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5612,10 +5613,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45257</v>
+        <v>44989</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5625,11 +5626,6 @@
       <c r="G57" t="inlineStr">
         <is>
           <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -5676,7 +5672,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5686,14 +5682,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45363</v>
+        <v>45089</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5705,8 +5701,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5749,7 +5750,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5759,14 +5760,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44776</v>
+        <v>45089</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5780,11 +5781,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5827,7 +5828,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5837,14 +5838,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45035</v>
+        <v>44502</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5857,7 +5858,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>14.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5900,7 +5901,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 60969-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5910,14 +5911,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45330</v>
+        <v>45996</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5930,7 +5931,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5973,7 +5974,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 60949-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5987,10 +5988,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45061</v>
+        <v>45996</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6003,7 +6004,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.3</v>
+        <v>21.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6063,7 +6064,7 @@
         <v>46159</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6124,7 +6125,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6138,10 +6139,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44904</v>
+        <v>45261</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6154,7 +6155,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6197,7 +6198,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6211,10 +6212,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44749</v>
+        <v>45110</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6227,7 +6228,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6270,7 +6271,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 3673-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6284,10 +6285,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45110</v>
+        <v>46043</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6300,7 +6301,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6343,7 +6344,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6357,10 +6358,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45713</v>
+        <v>46048</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6372,13 +6373,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>9.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6421,7 +6417,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6435,10 +6431,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45110</v>
+        <v>44642</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6450,8 +6446,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6494,7 +6495,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6504,14 +6505,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44502</v>
+        <v>45110</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6524,7 +6525,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>14.7</v>
+        <v>3.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6567,7 +6568,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6581,10 +6582,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45191</v>
+        <v>45061</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6596,13 +6597,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6645,7 +6641,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6659,10 +6655,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46275</v>
+        <v>45187</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6675,7 +6671,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6718,7 +6714,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6728,14 +6724,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46275</v>
+        <v>44546</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6748,7 +6744,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6791,7 +6787,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6805,10 +6801,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45261</v>
+        <v>44557</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6821,7 +6817,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6864,7 +6860,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6878,10 +6874,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45054</v>
+        <v>44827</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6893,8 +6889,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6937,7 +6938,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6951,10 +6952,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45160</v>
+        <v>45035</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6967,7 +6968,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>18.1</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7010,7 +7011,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 2496-2024</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7024,10 +7025,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45313</v>
+        <v>44606</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7039,13 +7040,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7088,7 +7084,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7102,10 +7098,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44904</v>
+        <v>45191</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7117,8 +7113,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7161,7 +7162,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7171,14 +7172,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44546</v>
+        <v>45540</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7191,7 +7192,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7234,7 +7235,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7244,14 +7245,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45061</v>
+        <v>44678</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7264,7 +7265,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7307,7 +7308,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7321,10 +7322,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45251</v>
+        <v>45162</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7337,7 +7338,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7380,7 +7381,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7394,10 +7395,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45187</v>
+        <v>45478</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7410,7 +7411,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7453,7 +7454,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7463,14 +7464,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44894</v>
+        <v>44776</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7482,8 +7483,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7526,7 +7532,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7536,14 +7542,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44803</v>
+        <v>44571</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7556,7 +7562,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7599,7 +7605,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 60922-2023</t>
+          <t>A 24636-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7613,10 +7619,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45261</v>
+        <v>45084</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7629,7 +7635,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>7.6</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7689,7 +7695,7 @@
         <v>45653</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7745,7 +7751,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7759,10 +7765,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45162</v>
+        <v>45644</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7775,7 +7781,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7818,7 +7824,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7832,10 +7838,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44606</v>
+        <v>45713</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7847,8 +7853,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7891,7 +7902,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7905,10 +7916,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44992</v>
+        <v>45461</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7921,7 +7932,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7964,7 +7975,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7978,10 +7989,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45089</v>
+        <v>46275</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7993,13 +8004,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8042,7 +8048,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8056,10 +8062,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45644</v>
+        <v>46275</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8072,7 +8078,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8115,7 +8121,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8129,10 +8135,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45222</v>
+        <v>45567</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8145,7 +8151,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8188,7 +8194,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8198,14 +8204,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44776</v>
+        <v>45461</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8217,13 +8223,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>2.5</v>
+        <v>12.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8266,7 +8267,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 3890-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8280,10 +8281,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45533</v>
+        <v>45684</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8296,7 +8297,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8339,7 +8340,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 3890-2025</t>
+          <t>A 21513-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8353,10 +8354,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45684</v>
+        <v>45782</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8369,7 +8370,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8412,7 +8413,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 48375-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8426,10 +8427,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45567</v>
+        <v>45590</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8441,8 +8442,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8485,7 +8491,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 22402-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8499,10 +8505,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45461</v>
+        <v>45786</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8515,7 +8521,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>12.5</v>
+        <v>4.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8558,7 +8564,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 21513-2025</t>
+          <t>A 35961-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8572,10 +8578,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45782</v>
+        <v>45533</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8588,7 +8594,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8648,7 +8654,7 @@
         <v>45427</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8704,7 +8710,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 35961-2024</t>
+          <t>A 24105-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8718,10 +8724,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45533</v>
+        <v>45796</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8734,7 +8740,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8777,7 +8783,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 22402-2025</t>
+          <t>A 60934-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8791,10 +8797,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45786</v>
+        <v>45261</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8807,7 +8813,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8850,7 +8856,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 48375-2024</t>
+          <t>A 28681-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8864,10 +8870,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45590</v>
+        <v>45819</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8879,13 +8885,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1474,80 +1474,195 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
+          <t>A 51189-2022</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44865</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>48</v>
+      </c>
+      <c r="U8" t="n">
+        <v>48</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin
+Gulsparv
+Järnsparv
+Vedskivlav
+Större vattensalamander
+Åkergroda
+Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 51189-2022 artfynd.xlsx", "A 51189-2022")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 51189-2022 karta.png", "A 51189-2022")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 51189-2022 georefererad karta.tif", "A 51189-2022")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 51189-2022 FSC-klagomål.docx", "A 51189-2022")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 51189-2022 FSC-klagomål mail.docx", "A 51189-2022")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 51189-2022 tillsynsbegäran.docx", "A 51189-2022")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 51189-2022 tillsynsbegäran mail.docx", "A 51189-2022")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 51189-2022 prioriterade fågelarter.docx", "A 51189-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>A 64357-2023</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D9" s="1" t="n">
         <v>45280</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="E9" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I9" t="n">
         <v>6.7</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>5</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S9" t="n">
         <v>5</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>7</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>7</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Gulsparv
@@ -1556,144 +1671,36 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 64357-2023 artfynd.xlsx", "A 64357-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 64357-2023 karta.png", "A 64357-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 64357-2023 georefererad karta.tif", "A 64357-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 64357-2023 FSC-klagomål.docx", "A 64357-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 64357-2023 FSC-klagomål mail.docx", "A 64357-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 64357-2023 tillsynsbegäran.docx", "A 64357-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 64357-2023 tillsynsbegäran mail.docx", "A 64357-2023")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 64357-2023 prioriterade fågelarter.docx", "A 64357-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 51189-2022</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>44865</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>41</v>
-      </c>
-      <c r="U9" t="n">
-        <v>41</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Vedskivlav
-Större vattensalamander
-Åkergroda
-Mindre vattensalamander</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 51189-2022 artfynd.xlsx", "A 51189-2022")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 51189-2022 karta.png", "A 51189-2022")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 51189-2022 georefererad karta.tif", "A 51189-2022")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 51189-2022 FSC-klagomål.docx", "A 51189-2022")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 51189-2022 FSC-klagomål mail.docx", "A 51189-2022")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 51189-2022 tillsynsbegäran.docx", "A 51189-2022")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 51189-2022 tillsynsbegäran mail.docx", "A 51189-2022")</f>
         <v/>
       </c>
     </row>
@@ -1717,7 +1724,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1829,7 +1836,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1936,7 +1943,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2025,7 +2032,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 64345-2023</t>
+          <t>A 40643-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2039,10 +2046,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45280</v>
+        <v>45558</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2055,16 +2062,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -2079,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2088,377 +2095,377 @@
         <v>2</v>
       </c>
       <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Bergsslok
+Getrams</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 41957-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45903</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Gröngöling
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 22874-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 22874-2026 artfynd.xlsx", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 22874-2026 karta.png", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 22874-2026 georefererad karta.tif", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 22874-2026 FSC-klagomål.docx", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 22874-2026 FSC-klagomål mail.docx", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 22874-2026 tillsynsbegäran.docx", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 22874-2026 tillsynsbegäran mail.docx", "A 22874-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 64345-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45280</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
         <v>3</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U16" t="n">
         <v>3</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 64345-2023 artfynd.xlsx", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 64345-2023 karta.png", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 64345-2023 georefererad karta.tif", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 64345-2023 FSC-klagomål.docx", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 64345-2023 FSC-klagomål mail.docx", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 64345-2023 tillsynsbegäran.docx", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 64345-2023 tillsynsbegäran mail.docx", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 64345-2023 prioriterade fågelarter.docx", "A 64345-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 41957-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45903</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Gröngöling
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 40643-2024</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45558</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Bergsslok
-Getrams</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 22874-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46156</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Kandelabersvamp
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 22874-2026 artfynd.xlsx", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 22874-2026 karta.png", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 22874-2026 georefererad karta.tif", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 22874-2026 FSC-klagomål.docx", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 22874-2026 FSC-klagomål mail.docx", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 22874-2026 tillsynsbegäran.docx", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 22874-2026 tillsynsbegäran mail.docx", "A 22874-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46757-2023</t>
+          <t>A 6893-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2468,14 +2475,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45198</v>
+        <v>46057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2488,10 +2495,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2528,46 +2535,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 6893-2026</t>
+          <t>A 39716-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2581,10 +2584,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46057</v>
+        <v>45166</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2597,22 +2600,22 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2624,7 +2627,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2637,35 +2640,39 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
         <v/>
       </c>
     </row>
@@ -2689,7 +2696,7 @@
         <v>45520</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2786,7 +2793,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 39716-2023</t>
+          <t>A 46757-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2796,14 +2803,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45166</v>
+        <v>45198</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2816,7 +2823,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2825,13 +2832,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2843,7 +2850,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2856,39 +2863,39 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
         <v/>
       </c>
     </row>
@@ -2912,7 +2919,7 @@
         <v>45020</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3026,7 +3033,7 @@
         <v>44618</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3099,7 +3106,7 @@
         <v>44468</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3177,7 +3184,7 @@
         <v>44467</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3250,7 +3257,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3328,7 +3335,7 @@
         <v>44619</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3401,7 +3408,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3462,7 +3469,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 55112-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3472,14 +3479,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44776</v>
+        <v>44474</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3491,13 +3498,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3540,7 +3542,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 49592-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3554,10 +3556,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45251</v>
+        <v>45211</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3570,7 +3572,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3613,7 +3615,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 49592-2023</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3623,14 +3625,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45211</v>
+        <v>45700</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3643,7 +3645,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3686,7 +3688,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3696,14 +3698,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45330</v>
+        <v>45089</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3715,8 +3717,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3759,7 +3766,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55112-2021</t>
+          <t>A 24636-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3773,10 +3780,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44474</v>
+        <v>45084</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3789,7 +3796,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3832,7 +3839,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3846,10 +3853,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45257</v>
+        <v>45540</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3861,13 +3868,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3910,7 +3912,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2496-2024</t>
+          <t>A 60934-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3924,10 +3926,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45313</v>
+        <v>45261</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3939,13 +3941,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3988,7 +3985,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4002,10 +3999,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45533</v>
+        <v>44989</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4018,7 +4015,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4061,7 +4058,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4075,10 +4072,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44803</v>
+        <v>45461</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4091,7 +4088,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4134,7 +4131,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4144,14 +4141,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44803</v>
+        <v>44571</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4164,7 +4161,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4207,7 +4204,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4221,10 +4218,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44904</v>
+        <v>44827</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4234,6 +4231,11 @@
       <c r="G38" t="inlineStr">
         <is>
           <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -4280,7 +4282,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4294,10 +4296,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46086</v>
+        <v>44642</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4309,8 +4311,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4353,7 +4360,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 41702-2023</t>
+          <t>A 28681-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4367,10 +4374,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45176</v>
+        <v>45819</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4382,13 +4389,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.8</v>
+        <v>7.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4431,7 +4433,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4445,10 +4447,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46097</v>
+        <v>45930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4461,7 +4463,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4504,7 +4506,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4514,14 +4516,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45700</v>
+        <v>44557</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4577,7 +4579,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 3673-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4591,10 +4593,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45160</v>
+        <v>46043</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4607,7 +4609,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>18.1</v>
+        <v>3.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4650,7 +4652,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4664,10 +4666,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45575</v>
+        <v>45940</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4723,7 +4725,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4737,10 +4739,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45054</v>
+        <v>46048</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4753,7 +4755,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4796,7 +4798,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4810,10 +4812,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45222</v>
+        <v>45478</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4826,7 +4828,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4869,7 +4871,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 41702-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4883,10 +4885,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44904</v>
+        <v>45176</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4898,8 +4900,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4942,7 +4949,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4956,10 +4963,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45930</v>
+        <v>44803</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4972,7 +4979,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5015,7 +5022,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5025,14 +5032,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45061</v>
+        <v>44678</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5045,7 +5052,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5088,7 +5095,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 42572-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5102,10 +5109,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44749</v>
+        <v>45565</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5118,7 +5125,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5161,7 +5168,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5175,10 +5182,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45940</v>
+        <v>45575</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5234,7 +5241,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 42572-2024</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5248,10 +5255,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45565</v>
+        <v>45257</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5263,8 +5270,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5307,7 +5319,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5321,10 +5333,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44894</v>
+        <v>46086</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5337,7 +5349,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5380,7 +5392,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 60949-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5394,10 +5406,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44992</v>
+        <v>45996</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5410,7 +5422,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>21.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5453,7 +5465,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 60969-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5463,14 +5475,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45363</v>
+        <v>45996</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5483,7 +5495,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5526,7 +5538,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 60922-2023</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5540,10 +5552,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45261</v>
+        <v>46097</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5556,7 +5568,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.6</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5599,7 +5611,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5609,14 +5621,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44989</v>
+        <v>44776</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5628,8 +5640,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5672,7 +5689,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5686,10 +5703,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45089</v>
+        <v>45035</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5701,13 +5718,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5750,7 +5762,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5760,14 +5772,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45089</v>
+        <v>45330</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5779,13 +5791,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5828,7 +5835,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5838,14 +5845,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44502</v>
+        <v>45061</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5858,7 +5865,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>14.7</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5901,7 +5908,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 60969-2025</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5915,10 +5922,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45996</v>
+        <v>44904</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5931,7 +5938,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>8.800000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5974,7 +5981,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 60949-2025</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5988,10 +5995,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45996</v>
+        <v>44749</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6004,7 +6011,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>21.9</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6047,7 +6054,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 22913-2026</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6061,10 +6068,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46159</v>
+        <v>45713</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6078,11 +6085,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6125,7 +6132,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6135,14 +6142,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45261</v>
+        <v>44502</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6155,7 +6162,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>14.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6198,7 +6205,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6212,10 +6219,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45110</v>
+        <v>45191</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6227,8 +6234,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6271,7 +6283,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 3673-2026</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6285,10 +6297,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46043</v>
+        <v>45261</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6301,7 +6313,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6344,7 +6356,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6354,14 +6366,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46048</v>
+        <v>45363</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6417,7 +6429,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6431,10 +6443,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44642</v>
+        <v>45054</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6446,13 +6458,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6495,7 +6502,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 22913-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6509,10 +6516,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45110</v>
+        <v>46159</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6524,8 +6531,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6568,7 +6580,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6582,10 +6594,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45061</v>
+        <v>45160</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6598,7 +6610,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.3</v>
+        <v>18.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6641,7 +6653,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 2496-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6655,10 +6667,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45187</v>
+        <v>45313</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6670,8 +6682,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6714,7 +6731,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6724,14 +6741,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44546</v>
+        <v>44904</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6744,7 +6761,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6787,7 +6804,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6797,14 +6814,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44557</v>
+        <v>44546</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6817,7 +6834,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6860,7 +6877,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6874,10 +6891,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44827</v>
+        <v>45110</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6889,13 +6906,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6938,7 +6950,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6952,10 +6964,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45035</v>
+        <v>45110</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6968,7 +6980,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7011,7 +7023,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7025,10 +7037,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44606</v>
+        <v>45061</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7041,7 +7053,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7084,7 +7096,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7098,10 +7110,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45191</v>
+        <v>45251</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7113,13 +7125,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7162,7 +7169,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7176,10 +7183,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45540</v>
+        <v>45187</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7192,7 +7199,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7235,7 +7242,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7245,14 +7252,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44678</v>
+        <v>44894</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7265,7 +7272,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7308,7 +7315,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7322,10 +7329,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45162</v>
+        <v>44803</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7338,7 +7345,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7381,7 +7388,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 60922-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7395,10 +7402,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45478</v>
+        <v>45261</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7411,7 +7418,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7454,7 +7461,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7464,14 +7471,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44776</v>
+        <v>45653</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7483,13 +7490,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7532,7 +7534,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7542,14 +7544,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44571</v>
+        <v>45162</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7562,7 +7564,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7605,7 +7607,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 24636-2023</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7619,10 +7621,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45084</v>
+        <v>44606</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7635,7 +7637,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7678,7 +7680,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7688,14 +7690,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45653</v>
+        <v>44992</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7708,7 +7710,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7751,7 +7753,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7765,10 +7767,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45644</v>
+        <v>45089</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7780,8 +7782,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7824,7 +7831,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7838,10 +7845,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45713</v>
+        <v>45644</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7853,13 +7860,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>9.699999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7902,7 +7904,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7916,10 +7918,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45461</v>
+        <v>46275</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7932,7 +7934,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7992,7 +7994,7 @@
         <v>46275</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8048,7 +8050,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8062,10 +8064,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46275</v>
+        <v>45222</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8078,7 +8080,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8121,7 +8123,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8131,14 +8133,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45567</v>
+        <v>44776</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8150,8 +8152,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8194,7 +8201,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8208,10 +8215,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45461</v>
+        <v>45533</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8224,7 +8231,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>12.5</v>
+        <v>0.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8284,7 +8291,7 @@
         <v>45684</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8340,7 +8347,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 21513-2025</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8354,10 +8361,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45782</v>
+        <v>45567</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8370,7 +8377,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8413,7 +8420,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 48375-2024</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8427,10 +8434,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45590</v>
+        <v>45461</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8442,13 +8449,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>4.8</v>
+        <v>12.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8491,7 +8493,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 22402-2025</t>
+          <t>A 21513-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8505,10 +8507,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45786</v>
+        <v>45782</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8521,7 +8523,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8564,7 +8566,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 35961-2024</t>
+          <t>A 19031-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8574,14 +8576,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45533</v>
+        <v>45427</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8594,7 +8596,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8637,7 +8639,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 19031-2024</t>
+          <t>A 35961-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8647,14 +8649,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45427</v>
+        <v>45533</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8667,7 +8669,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8710,7 +8712,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 24105-2025</t>
+          <t>A 22402-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8724,10 +8726,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45796</v>
+        <v>45786</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8740,7 +8742,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8783,7 +8785,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 60934-2023</t>
+          <t>A 48375-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8797,10 +8799,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45261</v>
+        <v>45590</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8812,8 +8814,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8856,7 +8863,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 28681-2025</t>
+          <t>A 24105-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8870,10 +8877,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45819</v>
+        <v>45796</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8886,7 +8893,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45558</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>45903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6893-2026</t>
+          <t>A 46757-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2475,14 +2475,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46057</v>
+        <v>45198</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2535,42 +2535,46 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 39716-2023</t>
+          <t>A 33751-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2580,14 +2584,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45166</v>
+        <v>45520</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2599,8 +2603,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2612,10 +2621,10 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2633,53 +2642,53 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33751-2024</t>
+          <t>A 39716-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2689,14 +2698,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45520</v>
+        <v>45166</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2708,13 +2717,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2726,10 +2730,10 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2747,53 +2751,53 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 46757-2023</t>
+          <t>A 6893-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2803,14 +2807,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45198</v>
+        <v>46057</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2823,10 +2827,10 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2863,39 +2867,35 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
         <v>45020</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>44618</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>44468</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>44467</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>44619</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>44474</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 49592-2023</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45211</v>
+        <v>45251</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 49592-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3625,14 +3625,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45700</v>
+        <v>45211</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3688,7 +3688,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3698,14 +3698,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45089</v>
+        <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3717,13 +3717,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3766,7 +3761,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 24636-2023</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3780,10 +3775,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45084</v>
+        <v>44904</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3796,7 +3791,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3839,7 +3834,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 41702-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3853,10 +3848,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45540</v>
+        <v>45176</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3868,8 +3863,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3912,7 +3912,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60934-2023</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45261</v>
+        <v>45575</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3985,7 +3985,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3999,10 +3999,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44989</v>
+        <v>45054</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4058,7 +4058,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45461</v>
+        <v>45160</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.5</v>
+        <v>18.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44571</v>
+        <v>45222</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44827</v>
+        <v>44904</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4233,13 +4233,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4282,7 +4277,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4296,10 +4291,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44642</v>
+        <v>45061</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4311,13 +4306,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4360,7 +4350,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28681-2025</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4374,10 +4364,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45819</v>
+        <v>44749</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4390,7 +4380,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>7.5</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4433,7 +4423,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4447,10 +4437,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45930</v>
+        <v>46086</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4463,7 +4453,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4506,7 +4496,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4520,10 +4510,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44557</v>
+        <v>46097</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4536,7 +4526,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4579,7 +4569,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3673-2026</t>
+          <t>A 28681-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4593,10 +4583,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46043</v>
+        <v>45819</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4609,7 +4599,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.8</v>
+        <v>7.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4652,7 +4642,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 42572-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4666,10 +4656,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45940</v>
+        <v>45565</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4682,7 +4672,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4725,7 +4715,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4739,10 +4729,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46048</v>
+        <v>44894</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4755,7 +4745,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4798,7 +4788,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4812,10 +4802,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45478</v>
+        <v>44989</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4828,7 +4818,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4871,7 +4861,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 41702-2023</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4885,10 +4875,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45176</v>
+        <v>45089</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4902,11 +4892,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4949,7 +4939,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4963,10 +4953,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44803</v>
+        <v>45089</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4978,8 +4968,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>6.1</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5022,7 +5017,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5036,10 +5031,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44678</v>
+        <v>44502</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5052,7 +5047,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.6</v>
+        <v>14.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5095,7 +5090,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 42572-2024</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5109,10 +5104,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45565</v>
+        <v>45261</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5125,7 +5120,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5168,7 +5163,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5182,10 +5177,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45575</v>
+        <v>45930</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5198,7 +5193,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5241,7 +5236,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5251,14 +5246,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45257</v>
+        <v>45363</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5270,13 +5265,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5319,7 +5309,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5333,10 +5323,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46086</v>
+        <v>45061</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5349,7 +5339,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5392,7 +5382,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 60949-2025</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5406,10 +5396,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45996</v>
+        <v>45187</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5422,7 +5412,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>21.9</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5465,7 +5455,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60969-2025</t>
+          <t>A 22913-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5479,10 +5469,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45996</v>
+        <v>46159</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5494,8 +5484,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>8.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5538,7 +5533,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5548,14 +5543,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46097</v>
+        <v>44546</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5568,7 +5563,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5611,7 +5606,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5621,14 +5616,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44776</v>
+        <v>45940</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5640,13 +5635,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5689,7 +5679,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5703,10 +5693,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45035</v>
+        <v>44557</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5719,7 +5709,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5762,7 +5752,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5772,14 +5762,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45330</v>
+        <v>45035</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5792,7 +5782,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5835,7 +5825,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5849,10 +5839,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45061</v>
+        <v>45110</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5865,7 +5855,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5908,7 +5898,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5922,10 +5912,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44904</v>
+        <v>44606</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5938,7 +5928,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5981,7 +5971,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5995,10 +5985,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44749</v>
+        <v>45191</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6010,8 +6000,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6054,7 +6049,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6068,10 +6063,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45713</v>
+        <v>45110</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6083,13 +6078,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>9.699999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6132,7 +6122,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6146,10 +6136,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44502</v>
+        <v>44678</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6162,7 +6152,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>14.7</v>
+        <v>3.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6205,7 +6195,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6219,10 +6209,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45191</v>
+        <v>45478</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6234,13 +6224,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6283,7 +6268,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6293,14 +6278,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45261</v>
+        <v>44571</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6313,7 +6298,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6356,7 +6341,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 24636-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6366,14 +6351,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45363</v>
+        <v>45084</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6386,7 +6371,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6429,7 +6414,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6439,14 +6424,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45054</v>
+        <v>45653</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6459,7 +6444,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6502,7 +6487,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 22913-2026</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6512,14 +6497,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46159</v>
+        <v>44776</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6533,7 +6518,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -6580,7 +6565,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6594,10 +6579,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45160</v>
+        <v>45257</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6609,8 +6594,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>18.1</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6670,7 +6660,7 @@
         <v>45313</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6731,7 +6721,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6745,10 +6735,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44904</v>
+        <v>45533</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6761,7 +6751,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6804,7 +6794,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6814,14 +6804,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44546</v>
+        <v>44803</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6834,7 +6824,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>6.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6877,7 +6867,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6891,10 +6881,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45110</v>
+        <v>44803</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6907,7 +6897,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6950,7 +6940,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6960,14 +6950,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45110</v>
+        <v>45700</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6980,7 +6970,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7023,7 +7013,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 60969-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7037,10 +7027,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45061</v>
+        <v>45996</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7053,7 +7043,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7096,7 +7086,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 60949-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7110,10 +7100,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45251</v>
+        <v>45996</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7126,7 +7116,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>21.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7169,7 +7159,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7183,10 +7173,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45187</v>
+        <v>46275</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7199,7 +7189,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7242,7 +7232,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7256,10 +7246,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44894</v>
+        <v>46275</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7272,7 +7262,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7315,7 +7305,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7329,10 +7319,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44803</v>
+        <v>44992</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7345,7 +7335,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7405,7 +7395,7 @@
         <v>45261</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7461,7 +7451,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7471,14 +7461,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45653</v>
+        <v>44642</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7490,8 +7480,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7534,7 +7529,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 3673-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7548,10 +7543,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45162</v>
+        <v>46043</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7564,7 +7559,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7607,7 +7602,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7621,10 +7616,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44606</v>
+        <v>46048</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7637,7 +7632,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7680,7 +7675,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7694,10 +7689,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44992</v>
+        <v>44827</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7709,8 +7704,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7753,7 +7753,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7767,10 +7767,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45089</v>
+        <v>45540</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7782,13 +7782,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7831,7 +7826,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7845,10 +7840,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45644</v>
+        <v>45162</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7861,7 +7856,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7904,7 +7899,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7914,14 +7909,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46275</v>
+        <v>44776</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7933,8 +7928,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7977,7 +7977,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7991,10 +7991,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46275</v>
+        <v>45644</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.6</v>
+        <v>0.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8050,7 +8050,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8064,10 +8064,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45222</v>
+        <v>45713</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8079,8 +8079,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>3.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8123,7 +8128,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8133,14 +8138,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44776</v>
+        <v>45461</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8152,13 +8157,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8201,7 +8201,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8215,10 +8215,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45533</v>
+        <v>45567</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8274,7 +8274,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 3890-2025</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8288,10 +8288,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45684</v>
+        <v>45461</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.9</v>
+        <v>12.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8347,7 +8347,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 3890-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8361,10 +8361,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45567</v>
+        <v>45684</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8420,7 +8420,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 21513-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8434,10 +8434,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45461</v>
+        <v>45782</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>12.5</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8493,7 +8493,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 21513-2025</t>
+          <t>A 48375-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8507,10 +8507,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45782</v>
+        <v>45590</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8522,8 +8522,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8566,7 +8571,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 19031-2024</t>
+          <t>A 22402-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8576,14 +8581,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45427</v>
+        <v>45786</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8596,7 +8601,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8656,7 +8661,7 @@
         <v>45533</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8712,7 +8717,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 22402-2025</t>
+          <t>A 19031-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8722,14 +8727,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45786</v>
+        <v>45427</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8742,7 +8747,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8785,7 +8790,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 48375-2024</t>
+          <t>A 24105-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8799,10 +8804,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45590</v>
+        <v>45796</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8814,13 +8819,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8863,7 +8863,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 24105-2025</t>
+          <t>A 60934-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8877,10 +8877,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45796</v>
+        <v>45261</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE101"/>
+  <dimension ref="A1:AE102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         <v>72</v>
       </c>
       <c r="K2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L2" t="n">
         <v>61</v>
@@ -649,13 +649,13 @@
         <v>39</v>
       </c>
       <c r="S2" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="T2" t="n">
-        <v>1754</v>
+        <v>1791</v>
       </c>
       <c r="U2" t="n">
-        <v>1602</v>
+        <v>1639</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -769,6 +769,7 @@
 Dvärgtufs
 Fällmossa
 Granbarkgnagare
+Grov baronmossa
 Grovticka
 Grå skärelav
 Grön sköldmossa
@@ -887,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1018,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1138,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1257,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1375,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1491,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1606,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1724,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1836,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1943,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2049,7 +2050,7 @@
         <v>45558</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2155,7 +2156,7 @@
         <v>45903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2261,7 +2262,7 @@
         <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2372,7 +2373,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2465,7 +2466,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46757-2023</t>
+          <t>A 6893-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2475,14 +2476,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45198</v>
+        <v>46057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2495,10 +2496,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2535,46 +2536,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33751-2024</t>
+          <t>A 39716-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2584,14 +2581,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45520</v>
+        <v>45166</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2603,13 +2600,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2621,10 +2613,10 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2642,53 +2634,53 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 39716-2023</t>
+          <t>A 33751-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2698,14 +2690,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45166</v>
+        <v>45520</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2717,8 +2709,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2730,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2751,53 +2748,53 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 6893-2026</t>
+          <t>A 46757-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2807,14 +2804,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46057</v>
+        <v>45198</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2827,10 +2824,10 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2867,35 +2864,39 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
         <v/>
       </c>
     </row>
@@ -2919,7 +2920,7 @@
         <v>45020</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3033,7 +3034,7 @@
         <v>44618</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3106,7 +3107,7 @@
         <v>44468</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3184,7 +3185,7 @@
         <v>44467</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3257,7 +3258,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3335,7 +3336,7 @@
         <v>44619</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3408,7 +3409,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3486,7 +3487,7 @@
         <v>44474</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3543,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3556,10 +3557,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45251</v>
+        <v>45089</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3571,8 +3572,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3632,7 +3638,7 @@
         <v>45211</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3688,7 +3694,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3702,10 +3708,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45330</v>
+        <v>45700</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3718,7 +3724,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3761,7 +3767,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3775,10 +3781,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44904</v>
+        <v>45540</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3791,7 +3797,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3834,7 +3840,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 41702-2023</t>
+          <t>A 24636-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3848,10 +3854,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45176</v>
+        <v>45084</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3863,13 +3869,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3912,7 +3913,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3926,10 +3927,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45575</v>
+        <v>45461</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3942,7 +3943,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3985,7 +3986,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3999,10 +4000,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45054</v>
+        <v>44989</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4015,7 +4016,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4058,7 +4059,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4072,10 +4073,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45160</v>
+        <v>44827</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4087,8 +4088,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>18.1</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4131,7 +4137,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4141,14 +4147,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45222</v>
+        <v>44571</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4161,7 +4167,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4204,7 +4210,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4218,10 +4224,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44904</v>
+        <v>44642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4233,8 +4239,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4277,7 +4288,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4291,10 +4302,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45061</v>
+        <v>44557</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4307,7 +4318,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4350,7 +4361,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4364,10 +4375,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44749</v>
+        <v>45478</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4380,7 +4391,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4423,7 +4434,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 41702-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4437,10 +4448,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46086</v>
+        <v>45176</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4452,8 +4463,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4496,7 +4512,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4510,10 +4526,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46097</v>
+        <v>44803</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4526,7 +4542,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4569,7 +4585,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28681-2025</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4579,14 +4595,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45819</v>
+        <v>44678</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4599,7 +4615,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4659,7 +4675,7 @@
         <v>45565</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4715,7 +4731,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4729,10 +4745,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44894</v>
+        <v>45575</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4745,7 +4761,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4788,7 +4804,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4802,10 +4818,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44989</v>
+        <v>45257</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4815,6 +4831,11 @@
       <c r="G46" t="inlineStr">
         <is>
           <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -4861,7 +4882,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4871,14 +4892,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45089</v>
+        <v>44776</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4892,11 +4913,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4939,7 +4960,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4953,10 +4974,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45089</v>
+        <v>45035</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4968,13 +4989,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5017,7 +5033,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5027,14 +5043,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44502</v>
+        <v>45930</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5047,7 +5063,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>14.7</v>
+        <v>3.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5090,7 +5106,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5100,14 +5116,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45261</v>
+        <v>45363</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5120,7 +5136,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5163,7 +5179,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5173,14 +5189,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45930</v>
+        <v>45330</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5193,7 +5209,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5236,7 +5252,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5246,14 +5262,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45363</v>
+        <v>45061</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5266,7 +5282,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5309,7 +5325,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5323,10 +5339,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45061</v>
+        <v>45940</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5339,7 +5355,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5382,7 +5398,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5396,10 +5412,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45187</v>
+        <v>44904</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5412,7 +5428,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5455,7 +5471,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 22913-2026</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5469,10 +5485,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46159</v>
+        <v>44749</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5484,13 +5500,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5533,7 +5544,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5543,14 +5554,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44546</v>
+        <v>45713</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5562,8 +5573,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5606,7 +5622,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5616,14 +5632,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45940</v>
+        <v>44502</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5636,7 +5652,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>14.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5679,7 +5695,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5693,10 +5709,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44557</v>
+        <v>45191</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5708,8 +5724,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5752,7 +5773,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 22913-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5766,10 +5787,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45035</v>
+        <v>46159</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5781,8 +5802,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5825,7 +5851,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5839,10 +5865,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45110</v>
+        <v>45261</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5855,7 +5881,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5898,7 +5924,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 60949-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5912,10 +5938,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44606</v>
+        <v>45996</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5928,7 +5954,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>21.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5971,7 +5997,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 60969-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5985,10 +6011,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45191</v>
+        <v>45996</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6000,13 +6026,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6049,7 +6070,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6063,10 +6084,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45110</v>
+        <v>45054</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6079,7 +6100,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6122,7 +6143,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6132,14 +6153,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44678</v>
+        <v>45160</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6152,7 +6173,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.6</v>
+        <v>18.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6195,7 +6216,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 2496-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6209,10 +6230,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45478</v>
+        <v>45313</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6224,8 +6245,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6268,7 +6294,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6278,14 +6304,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44571</v>
+        <v>44904</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6298,7 +6324,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6341,7 +6367,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 24636-2023</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6351,14 +6377,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45084</v>
+        <v>44546</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6371,7 +6397,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6414,7 +6440,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6424,14 +6450,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45653</v>
+        <v>45110</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6444,7 +6470,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6487,7 +6513,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 3673-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6497,14 +6523,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44776</v>
+        <v>46043</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6516,13 +6542,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6565,7 +6586,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6579,10 +6600,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45257</v>
+        <v>46048</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6594,13 +6615,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6643,7 +6659,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 2496-2024</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6657,10 +6673,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45313</v>
+        <v>45110</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6672,13 +6688,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6721,7 +6732,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6735,10 +6746,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45533</v>
+        <v>45061</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6751,7 +6762,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6794,7 +6805,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6808,10 +6819,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44803</v>
+        <v>46086</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6824,7 +6835,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6867,7 +6878,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6881,10 +6892,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44803</v>
+        <v>46097</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6897,7 +6908,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6940,7 +6951,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6950,14 +6961,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45700</v>
+        <v>45251</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6970,7 +6981,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7013,7 +7024,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60969-2025</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7027,10 +7038,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45996</v>
+        <v>45187</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7043,7 +7054,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>8.800000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7086,7 +7097,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 60949-2025</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7100,10 +7111,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45996</v>
+        <v>44894</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7116,7 +7127,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>21.9</v>
+        <v>5.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7159,7 +7170,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7173,10 +7184,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46275</v>
+        <v>44803</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7189,7 +7200,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7232,7 +7243,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 60922-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7246,10 +7257,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46275</v>
+        <v>45261</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7262,7 +7273,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>7.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7305,7 +7316,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7315,14 +7326,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44992</v>
+        <v>45653</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7335,7 +7346,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7378,7 +7389,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 60922-2023</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7392,10 +7403,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45261</v>
+        <v>45162</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7408,7 +7419,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7451,7 +7462,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7465,10 +7476,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44642</v>
+        <v>44606</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7480,13 +7491,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7529,7 +7535,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 3673-2026</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7543,10 +7549,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46043</v>
+        <v>44992</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7559,7 +7565,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7602,7 +7608,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7616,10 +7622,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46048</v>
+        <v>45089</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7631,8 +7637,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7675,7 +7686,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7689,10 +7700,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44827</v>
+        <v>45644</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7704,13 +7715,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7753,7 +7759,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7767,10 +7773,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45540</v>
+        <v>45222</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7783,7 +7789,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7826,7 +7832,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7836,14 +7842,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45162</v>
+        <v>44776</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7855,8 +7861,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7899,7 +7910,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7909,14 +7920,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44776</v>
+        <v>45533</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7928,13 +7939,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7977,7 +7983,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 3890-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7991,10 +7997,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45644</v>
+        <v>45684</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8007,7 +8013,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.2</v>
+        <v>2.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8050,7 +8056,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8064,10 +8070,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45713</v>
+        <v>45567</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8079,13 +8085,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>9.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8128,7 +8129,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8145,7 +8146,7 @@
         <v>45461</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8158,7 +8159,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.5</v>
+        <v>12.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8201,7 +8202,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 21513-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8215,10 +8216,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45567</v>
+        <v>45782</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8231,7 +8232,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8274,7 +8275,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8288,10 +8289,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45461</v>
+        <v>46275</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8304,7 +8305,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>12.5</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8347,7 +8348,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 3890-2025</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8361,10 +8362,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45684</v>
+        <v>46275</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8377,7 +8378,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8420,7 +8421,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21513-2025</t>
+          <t>A 19031-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8430,14 +8431,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45782</v>
+        <v>45427</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8450,7 +8451,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8493,7 +8494,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48375-2024</t>
+          <t>A 35961-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8507,10 +8508,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45590</v>
+        <v>45533</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8522,13 +8523,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8588,7 +8584,7 @@
         <v>45786</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8644,7 +8640,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 35961-2024</t>
+          <t>A 48375-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8658,10 +8654,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45533</v>
+        <v>45590</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8673,8 +8669,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8717,7 +8718,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 19031-2024</t>
+          <t>A 24105-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8727,14 +8728,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45427</v>
+        <v>45796</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8747,7 +8748,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8790,7 +8791,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 24105-2025</t>
+          <t>A 38695-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8804,10 +8805,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45796</v>
+        <v>46283</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8820,7 +8821,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8860,7 +8861,7 @@
       </c>
       <c r="V100" s="2" t="inlineStr"/>
     </row>
-    <row r="101">
+    <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
           <t>A 60934-2023</t>
@@ -8880,7 +8881,7 @@
         <v>45261</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8932,6 +8933,79 @@
         <v>0</v>
       </c>
       <c r="V101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>A 28681-2025</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D102" s="1" t="n">
+        <v>45819</v>
+      </c>
+      <c r="E102" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>45558</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>45903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>46057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45166</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45520</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>45198</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45020</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44618</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>44468</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>44467</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>44619</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44474</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>45089</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45211</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>45700</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>45540</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>45084</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>45461</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>44989</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>44827</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>44571</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>44557</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>45478</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>45176</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44803</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>44678</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>45565</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>45575</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45257</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>44776</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>45035</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>45930</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>45363</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>45330</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>45061</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45940</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>44904</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>44749</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>45713</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>44502</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45191</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>46159</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>45261</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>45996</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>45996</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>45054</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>45160</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>45313</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>44904</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>44546</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>45110</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>46043</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>46048</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>45110</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>45061</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>46086</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>46097</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>45251</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>45187</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>44894</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>44803</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45261</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>45653</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>45162</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>44606</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>44992</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>45089</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>45644</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>45222</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>44776</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>45533</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>45684</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>45567</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>45461</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>45782</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>46275</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         <v>46275</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>45427</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>45533</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>45786</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>45590</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>45796</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>46283</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45261</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>45819</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE102"/>
+  <dimension ref="A1:AE101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>45558</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>45903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>46057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45166</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45520</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>45198</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45020</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44618</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>44468</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>44467</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>44619</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44474</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 49592-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45089</v>
+        <v>45211</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3572,13 +3572,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3621,7 +3616,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 49592-2023</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3631,14 +3626,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45211</v>
+        <v>45700</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3651,7 +3646,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3694,7 +3689,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3704,14 +3699,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45700</v>
+        <v>45540</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3724,7 +3719,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3767,7 +3762,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3781,10 +3776,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45540</v>
+        <v>45089</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3796,8 +3791,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3857,7 +3857,7 @@
         <v>45084</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>45461</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>44989</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>44827</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>44571</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>44557</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>45478</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>45176</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44803</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>44678</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>45565</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45575</v>
+        <v>45930</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4804,7 +4804,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4818,10 +4818,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45257</v>
+        <v>45575</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4831,11 +4831,6 @@
       <c r="G46" t="inlineStr">
         <is>
           <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -4882,7 +4877,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4892,14 +4887,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44776</v>
+        <v>45257</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4913,11 +4908,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4960,7 +4955,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4970,14 +4965,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45035</v>
+        <v>45363</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5033,7 +5028,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5047,10 +5042,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45930</v>
+        <v>45940</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5063,7 +5058,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5106,7 +5101,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 22913-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5116,14 +5111,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45363</v>
+        <v>46159</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5135,8 +5130,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5179,7 +5179,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5189,14 +5189,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45330</v>
+        <v>44776</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5208,8 +5208,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5252,7 +5257,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5266,10 +5271,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45061</v>
+        <v>45035</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5282,7 +5287,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5325,7 +5330,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5335,14 +5340,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45940</v>
+        <v>45330</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5398,7 +5403,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5412,10 +5417,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44904</v>
+        <v>45061</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5428,7 +5433,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5471,7 +5476,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5485,10 +5490,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44749</v>
+        <v>44904</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5501,7 +5506,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5544,7 +5549,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5558,10 +5563,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45713</v>
+        <v>44749</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5573,13 +5578,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>9.699999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5622,7 +5622,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5632,14 +5632,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44502</v>
+        <v>45713</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5651,8 +5651,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>14.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5695,7 +5700,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5705,14 +5710,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45191</v>
+        <v>44502</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5724,13 +5729,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>2.7</v>
+        <v>14.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5773,7 +5773,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 22913-2026</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46159</v>
+        <v>45110</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5802,13 +5802,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5851,7 +5846,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5865,10 +5860,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45261</v>
+        <v>45191</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5880,8 +5875,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5941,7 +5941,7 @@
         <v>45996</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 60969-2025</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45996</v>
+        <v>45110</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>8.800000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6070,7 +6070,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 3673-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45054</v>
+        <v>46043</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45160</v>
+        <v>46048</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>18.1</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 2496-2024</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45313</v>
+        <v>45261</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6245,13 +6245,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6294,7 +6289,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6308,10 +6303,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44904</v>
+        <v>45054</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6324,7 +6319,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6367,7 +6362,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6377,14 +6372,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44546</v>
+        <v>46086</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6397,7 +6392,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6440,7 +6435,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6454,10 +6449,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45110</v>
+        <v>45160</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6470,7 +6465,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.5</v>
+        <v>18.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6513,7 +6508,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3673-2026</t>
+          <t>A 2496-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6527,10 +6522,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46043</v>
+        <v>45313</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6542,8 +6537,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6586,7 +6586,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46048</v>
+        <v>46097</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6659,7 +6659,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6673,10 +6673,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45110</v>
+        <v>44904</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6732,7 +6732,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6742,14 +6742,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45061</v>
+        <v>44546</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6805,7 +6805,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46086</v>
+        <v>45061</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6878,7 +6878,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46097</v>
+        <v>45251</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45251</v>
+        <v>45187</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7038,10 +7038,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45187</v>
+        <v>44894</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7111,10 +7111,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44894</v>
+        <v>44803</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7170,7 +7170,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44803</v>
+        <v>46275</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7243,7 +7243,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 60922-2023</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45261</v>
+        <v>46275</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>7.6</v>
+        <v>3.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7316,7 +7316,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 60922-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7326,14 +7326,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45653</v>
+        <v>45261</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>7.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7389,7 +7389,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7399,14 +7399,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45162</v>
+        <v>45653</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7462,7 +7462,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7476,10 +7476,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44606</v>
+        <v>45162</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7535,7 +7535,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7549,10 +7549,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44992</v>
+        <v>44606</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7608,7 +7608,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7622,10 +7622,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45089</v>
+        <v>44992</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7635,11 +7635,6 @@
       <c r="G84" t="inlineStr">
         <is>
           <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -7686,7 +7681,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7700,10 +7695,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45644</v>
+        <v>45089</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7715,8 +7710,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7759,7 +7759,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 38695-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45222</v>
+        <v>46283</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7832,7 +7832,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7842,14 +7842,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44776</v>
+        <v>45644</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7861,13 +7861,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7910,7 +7905,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7924,10 +7919,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45533</v>
+        <v>45222</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7940,7 +7935,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7983,7 +7978,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 3890-2025</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7993,14 +7988,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45684</v>
+        <v>44776</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8012,8 +8007,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8056,7 +8056,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8070,10 +8070,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45567</v>
+        <v>45533</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8129,7 +8129,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 3890-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8143,10 +8143,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45461</v>
+        <v>45684</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>12.5</v>
+        <v>2.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8202,7 +8202,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 21513-2025</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8216,10 +8216,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45782</v>
+        <v>45567</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8275,7 +8275,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8289,10 +8289,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46275</v>
+        <v>45461</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8348,7 +8348,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 21513-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8362,10 +8362,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46275</v>
+        <v>45782</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8438,7 +8438,7 @@
         <v>45427</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>45533</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>45786</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>45590</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>45796</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 38695-2026</t>
+          <t>A 60934-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46283</v>
+        <v>45261</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8861,10 +8861,10 @@
       </c>
       <c r="V100" s="2" t="inlineStr"/>
     </row>
-    <row r="101" ht="15" customHeight="1">
+    <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 60934-2023</t>
+          <t>A 28681-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8878,10 +8878,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45261</v>
+        <v>45819</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>7.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8933,79 +8933,6 @@
         <v>0</v>
       </c>
       <c r="V101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>A 28681-2025</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="n">
-        <v>45819</v>
-      </c>
-      <c r="E102" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I102" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" t="n">
-        <v>0</v>
-      </c>
-      <c r="T102" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" t="n">
-        <v>0</v>
-      </c>
-      <c r="V102" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 40643-2024</t>
+          <t>A 41957-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2043,14 +2043,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45558</v>
+        <v>45903</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2099,153 +2099,153 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Gröngöling
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 40643-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45558</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Bergsslok
 Getrams</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 41957-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45903</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Gröngöling
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 22874-2026</t>
+          <t>A 64345-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2255,14 +2255,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46156</v>
+        <v>45280</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2274,16 +2274,11 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>9.199999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2313,160 +2308,165 @@
         <v>2</v>
       </c>
       <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 64345-2023 artfynd.xlsx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 64345-2023 karta.png", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 64345-2023 georefererad karta.tif", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 64345-2023 FSC-klagomål.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 64345-2023 FSC-klagomål mail.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 64345-2023 tillsynsbegäran.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 64345-2023 tillsynsbegäran mail.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 64345-2023 prioriterade fågelarter.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 22874-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Kandelabersvamp
 Blåsippa</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 22874-2026 artfynd.xlsx", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 22874-2026 karta.png", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 22874-2026 georefererad karta.tif", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 22874-2026 FSC-klagomål.docx", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 22874-2026 FSC-klagomål mail.docx", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 22874-2026 tillsynsbegäran.docx", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 22874-2026 tillsynsbegäran mail.docx", "A 22874-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 64345-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45280</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 64345-2023 artfynd.xlsx", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 64345-2023 karta.png", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 64345-2023 georefererad karta.tif", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 64345-2023 FSC-klagomål.docx", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 64345-2023 FSC-klagomål mail.docx", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 64345-2023 tillsynsbegäran.docx", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 64345-2023 tillsynsbegäran mail.docx", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 64345-2023 prioriterade fågelarter.docx", "A 64345-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6893-2026</t>
+          <t>A 46757-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2476,14 +2476,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46057</v>
+        <v>45198</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2536,42 +2536,46 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 39716-2023</t>
+          <t>A 15452-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2581,14 +2585,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45166</v>
+        <v>45020</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2600,8 +2604,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2616,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2625,10 +2634,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2637,43 +2646,43 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
         <v/>
       </c>
     </row>
@@ -2697,7 +2706,7 @@
         <v>45520</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2794,7 +2803,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 46757-2023</t>
+          <t>A 39716-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2804,14 +2813,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45198</v>
+        <v>45166</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2824,7 +2833,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2833,13 +2842,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2851,7 +2860,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2864,46 +2873,46 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15452-2023</t>
+          <t>A 6893-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2913,14 +2922,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45020</v>
+        <v>46057</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2932,23 +2941,18 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
@@ -2962,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2974,43 +2978,39 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
         <v>44618</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>44468</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>44467</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>44619</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 55112-2021</t>
+          <t>A 48375-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44474</v>
+        <v>45590</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3499,8 +3499,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3543,7 +3548,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 49592-2023</t>
+          <t>A 22402-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3557,10 +3562,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45211</v>
+        <v>45786</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3573,7 +3578,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3616,7 +3621,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 35961-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3626,14 +3631,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45700</v>
+        <v>45533</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3646,7 +3651,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3689,7 +3694,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 55112-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3703,10 +3708,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45540</v>
+        <v>44474</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3719,7 +3724,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3762,7 +3767,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3776,10 +3781,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45089</v>
+        <v>44989</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3791,13 +3796,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3840,7 +3840,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 24636-2023</t>
+          <t>A 19031-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3850,14 +3850,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45084</v>
+        <v>45427</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3927,10 +3927,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45461</v>
+        <v>45089</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3942,8 +3942,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3986,7 +3991,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4000,10 +4005,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44989</v>
+        <v>45089</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4015,8 +4020,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4059,7 +4069,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4069,14 +4079,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44827</v>
+        <v>44502</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4088,13 +4098,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>14.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4137,7 +4142,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4147,14 +4152,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44571</v>
+        <v>45251</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4167,7 +4172,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4210,7 +4215,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 49592-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4224,10 +4229,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44642</v>
+        <v>45211</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4239,13 +4244,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4288,7 +4288,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4298,14 +4298,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44557</v>
+        <v>45330</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4361,7 +4361,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 24105-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4375,10 +4375,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45478</v>
+        <v>45796</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 41702-2023</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4448,10 +4448,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45176</v>
+        <v>45261</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4463,13 +4463,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4512,7 +4507,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4526,10 +4521,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44803</v>
+        <v>45061</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4542,7 +4537,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.1</v>
+        <v>0.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4585,7 +4580,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4595,14 +4590,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44678</v>
+        <v>45187</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4615,7 +4610,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4658,7 +4653,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 42572-2024</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4672,10 +4667,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45565</v>
+        <v>44904</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4688,7 +4683,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4731,7 +4726,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4741,14 +4736,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45930</v>
+        <v>44546</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4761,7 +4756,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4804,7 +4799,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 60934-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4818,10 +4813,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45575</v>
+        <v>45261</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4834,7 +4829,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4877,7 +4872,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 41702-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4891,10 +4886,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45257</v>
+        <v>45176</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4908,11 +4903,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4955,7 +4950,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4965,14 +4960,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45363</v>
+        <v>44557</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4985,7 +4980,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5028,7 +5023,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5042,10 +5037,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45940</v>
+        <v>45035</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5058,7 +5053,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5101,7 +5096,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 22913-2026</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5115,10 +5110,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46159</v>
+        <v>44606</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5130,13 +5125,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5179,7 +5169,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5189,14 +5179,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44776</v>
+        <v>45191</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5210,11 +5200,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5257,7 +5247,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5271,10 +5261,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45035</v>
+        <v>45160</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5287,7 +5277,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>18.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5330,7 +5320,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5340,14 +5330,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45330</v>
+        <v>45575</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5403,7 +5393,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5417,10 +5407,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45061</v>
+        <v>45054</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5433,7 +5423,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5476,7 +5466,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5490,10 +5480,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44904</v>
+        <v>45930</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5506,7 +5496,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5549,7 +5539,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5563,10 +5553,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44749</v>
+        <v>45222</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5579,7 +5569,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5622,7 +5612,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5636,10 +5626,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45713</v>
+        <v>45940</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5651,13 +5641,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>9.699999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5700,7 +5685,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5714,10 +5699,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44502</v>
+        <v>44678</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5730,7 +5715,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>14.7</v>
+        <v>3.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5773,7 +5758,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5787,10 +5772,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45110</v>
+        <v>44904</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5803,7 +5788,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5846,7 +5831,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5860,10 +5845,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45191</v>
+        <v>45478</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5875,13 +5860,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5924,7 +5904,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 60949-2025</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5938,10 +5918,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45996</v>
+        <v>45061</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5954,7 +5934,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>21.9</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5997,7 +5977,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6011,10 +5991,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45110</v>
+        <v>44749</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6027,7 +6007,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6070,7 +6050,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 3673-2026</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6080,14 +6060,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46043</v>
+        <v>44571</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6100,7 +6080,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6143,7 +6123,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 24636-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6157,10 +6137,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46048</v>
+        <v>45084</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6173,7 +6153,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6216,7 +6196,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 42572-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6230,10 +6210,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45261</v>
+        <v>45565</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6246,7 +6226,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6289,7 +6269,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6299,14 +6279,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45054</v>
+        <v>45653</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6319,7 +6299,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6362,7 +6342,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6376,10 +6356,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46086</v>
+        <v>44894</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6392,7 +6372,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6435,7 +6415,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6445,14 +6425,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45160</v>
+        <v>44776</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6464,8 +6444,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>18.1</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6508,7 +6493,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 2496-2024</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6522,10 +6507,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45313</v>
+        <v>45257</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6539,11 +6524,11 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6586,7 +6571,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 2496-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6600,10 +6585,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46097</v>
+        <v>45313</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6615,8 +6600,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6659,7 +6649,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6673,10 +6663,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44904</v>
+        <v>45533</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6689,7 +6679,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6732,7 +6722,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6742,14 +6732,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44546</v>
+        <v>44803</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6762,7 +6752,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>6.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6805,7 +6795,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 3673-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6819,10 +6809,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45061</v>
+        <v>46043</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6835,7 +6825,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6878,7 +6868,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6892,10 +6882,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45251</v>
+        <v>44803</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6908,7 +6898,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6951,7 +6941,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6965,10 +6955,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45187</v>
+        <v>46048</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6981,7 +6971,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7024,7 +7014,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 60949-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7038,10 +7028,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44894</v>
+        <v>45996</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7054,7 +7044,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5.2</v>
+        <v>21.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7097,7 +7087,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7107,14 +7097,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44803</v>
+        <v>45700</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7127,7 +7117,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7170,7 +7160,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 38695-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7184,10 +7174,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7200,7 +7190,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7243,7 +7233,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7257,10 +7247,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46275</v>
+        <v>46086</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7273,7 +7263,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7316,7 +7306,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 60922-2023</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7330,10 +7320,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45261</v>
+        <v>44992</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7346,7 +7336,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7389,7 +7379,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7399,14 +7389,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45653</v>
+        <v>46097</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7419,7 +7409,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7462,7 +7452,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 60922-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7476,10 +7466,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45162</v>
+        <v>45261</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7492,7 +7482,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7535,7 +7525,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 28681-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7549,10 +7539,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44606</v>
+        <v>45819</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7565,7 +7555,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7608,7 +7598,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7622,10 +7612,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44992</v>
+        <v>44642</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7637,8 +7627,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7681,7 +7676,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7695,10 +7690,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45089</v>
+        <v>44827</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7712,11 +7707,11 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7759,7 +7754,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 38695-2026</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7773,10 +7768,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46283</v>
+        <v>45540</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7789,7 +7784,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7832,7 +7827,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7846,10 +7841,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45644</v>
+        <v>45162</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7862,7 +7857,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7905,7 +7900,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7915,14 +7910,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45222</v>
+        <v>44776</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7934,8 +7929,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7978,7 +7978,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7988,14 +7988,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44776</v>
+        <v>45644</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8007,13 +8007,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8056,7 +8051,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8070,10 +8065,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45533</v>
+        <v>45713</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8085,8 +8080,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>0.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8129,7 +8129,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 3890-2025</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8143,10 +8143,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45684</v>
+        <v>45461</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8202,7 +8202,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8212,14 +8212,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45567</v>
+        <v>45363</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8275,7 +8275,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8289,10 +8289,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45461</v>
+        <v>45567</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8348,7 +8348,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 21513-2025</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8362,10 +8362,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45782</v>
+        <v>45461</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.2</v>
+        <v>12.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8421,7 +8421,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 19031-2024</t>
+          <t>A 3890-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8431,14 +8431,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45427</v>
+        <v>45684</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8494,7 +8494,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 35961-2024</t>
+          <t>A 21513-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8508,10 +8508,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45533</v>
+        <v>45782</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8567,7 +8567,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 22402-2025</t>
+          <t>A 22913-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8581,10 +8581,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45786</v>
+        <v>46159</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8596,8 +8596,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8640,7 +8645,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 48375-2024</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8654,10 +8659,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45590</v>
+        <v>45110</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8669,13 +8674,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 24105-2025</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45796</v>
+        <v>45110</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 60934-2023</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45261</v>
+        <v>46275</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8864,7 +8864,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 28681-2025</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8878,10 +8878,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45819</v>
+        <v>46275</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41957-2025</t>
+          <t>A 40643-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2043,14 +2043,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45903</v>
+        <v>45558</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2099,153 +2099,153 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Bergsslok
+Getrams</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 41957-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45903</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Gröngöling
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 40643-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45558</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Bergsslok
-Getrams</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 64345-2023</t>
+          <t>A 22874-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2255,14 +2255,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45280</v>
+        <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2274,11 +2274,16 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2308,165 +2313,160 @@
         <v>2</v>
       </c>
       <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 22874-2026 artfynd.xlsx", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 22874-2026 karta.png", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 22874-2026 georefererad karta.tif", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 22874-2026 FSC-klagomål.docx", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 22874-2026 FSC-klagomål mail.docx", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 22874-2026 tillsynsbegäran.docx", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 22874-2026 tillsynsbegäran mail.docx", "A 22874-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 64345-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45280</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
         <v>3</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>3</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 64345-2023 artfynd.xlsx", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 64345-2023 karta.png", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 64345-2023 georefererad karta.tif", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 64345-2023 FSC-klagomål.docx", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 64345-2023 FSC-klagomål mail.docx", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 64345-2023 tillsynsbegäran.docx", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 64345-2023 tillsynsbegäran mail.docx", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 64345-2023 prioriterade fågelarter.docx", "A 64345-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 22874-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46156</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Kandelabersvamp
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 22874-2026 artfynd.xlsx", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 22874-2026 karta.png", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 22874-2026 georefererad karta.tif", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 22874-2026 FSC-klagomål.docx", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 22874-2026 FSC-klagomål mail.docx", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 22874-2026 tillsynsbegäran.docx", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 22874-2026 tillsynsbegäran mail.docx", "A 22874-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46757-2023</t>
+          <t>A 6893-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2476,14 +2476,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45198</v>
+        <v>46057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2536,46 +2536,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 15452-2023</t>
+          <t>A 39716-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2585,14 +2581,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45020</v>
+        <v>45166</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,13 +2600,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2625,7 +2616,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2634,10 +2625,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2646,43 +2637,43 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
         <v/>
       </c>
     </row>
@@ -2706,7 +2697,7 @@
         <v>45520</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2803,7 +2794,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 39716-2023</t>
+          <t>A 46757-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2813,14 +2804,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45166</v>
+        <v>45198</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2833,7 +2824,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2842,13 +2833,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2860,7 +2851,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2873,46 +2864,46 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 6893-2026</t>
+          <t>A 15452-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2922,14 +2913,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46057</v>
+        <v>45020</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2941,17 +2932,22 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2966,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2978,39 +2974,43 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
         <v/>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
         <v>44618</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>44468</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>44467</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>44619</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 48375-2024</t>
+          <t>A 55112-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45590</v>
+        <v>44474</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3499,13 +3499,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3548,7 +3543,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 22402-2025</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3562,10 +3557,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45786</v>
+        <v>45089</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3577,8 +3572,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3621,7 +3621,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35961-2024</t>
+          <t>A 49592-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45533</v>
+        <v>45211</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55112-2021</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3704,14 +3704,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44474</v>
+        <v>45700</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3767,7 +3767,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44989</v>
+        <v>45540</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3840,7 +3840,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19031-2024</t>
+          <t>A 24636-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3850,14 +3850,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45427</v>
+        <v>45084</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3927,10 +3927,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45089</v>
+        <v>45461</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3942,13 +3942,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3991,7 +3986,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4005,10 +4000,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45089</v>
+        <v>44989</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4020,13 +4015,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4069,7 +4059,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4079,14 +4069,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44502</v>
+        <v>44827</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4098,8 +4088,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>14.7</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4142,7 +4137,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4152,14 +4147,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45251</v>
+        <v>44571</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4172,7 +4167,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4215,7 +4210,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 49592-2023</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4229,10 +4224,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45211</v>
+        <v>44642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4244,8 +4239,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4288,7 +4288,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4298,14 +4298,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45330</v>
+        <v>44557</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4361,7 +4361,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 24105-2025</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4375,10 +4375,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45796</v>
+        <v>45478</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 41702-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4448,10 +4448,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45261</v>
+        <v>45176</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4463,8 +4463,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4507,7 +4512,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4521,10 +4526,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45061</v>
+        <v>44803</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4537,7 +4542,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.3</v>
+        <v>6.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4580,7 +4585,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4590,14 +4595,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45187</v>
+        <v>44678</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4610,7 +4615,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4653,7 +4658,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 42572-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4667,10 +4672,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44904</v>
+        <v>45565</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4683,7 +4688,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4726,7 +4731,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4736,14 +4741,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44546</v>
+        <v>45575</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4756,7 +4761,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4799,7 +4804,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 60934-2023</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4813,10 +4818,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45261</v>
+        <v>45257</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4828,8 +4833,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4872,7 +4882,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 41702-2023</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4886,10 +4896,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45176</v>
+        <v>45930</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4901,13 +4911,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4950,7 +4955,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4964,10 +4969,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44557</v>
+        <v>45940</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4980,7 +4985,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5023,7 +5028,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5033,14 +5038,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45035</v>
+        <v>44776</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5052,8 +5057,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5096,7 +5106,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5110,10 +5120,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44606</v>
+        <v>45035</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5126,7 +5136,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5169,7 +5179,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5179,14 +5189,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45191</v>
+        <v>45330</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5198,13 +5208,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5247,7 +5252,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5261,10 +5266,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45160</v>
+        <v>45061</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5277,7 +5282,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>18.1</v>
+        <v>0.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5320,7 +5325,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5334,10 +5339,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45575</v>
+        <v>44904</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5393,7 +5398,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5407,10 +5412,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45054</v>
+        <v>44749</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5423,7 +5428,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5466,7 +5471,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5480,10 +5485,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45930</v>
+        <v>45713</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5495,8 +5500,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>3.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5539,7 +5549,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5549,14 +5559,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45222</v>
+        <v>44502</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5569,7 +5579,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.8</v>
+        <v>14.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5612,7 +5622,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5622,14 +5632,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45940</v>
+        <v>45363</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5642,7 +5652,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5685,7 +5695,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5695,14 +5705,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44678</v>
+        <v>45191</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5714,8 +5724,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5758,7 +5773,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 22913-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5772,10 +5787,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44904</v>
+        <v>46159</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5787,8 +5802,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5831,7 +5851,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 60949-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5845,10 +5865,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45478</v>
+        <v>45996</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5861,7 +5881,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>21.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5904,7 +5924,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5918,10 +5938,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45061</v>
+        <v>45261</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5934,7 +5954,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5977,7 +5997,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 3673-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5991,10 +6011,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44749</v>
+        <v>46043</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6007,7 +6027,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6050,7 +6070,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6060,14 +6080,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44571</v>
+        <v>46048</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6080,7 +6100,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6123,7 +6143,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 24636-2023</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6137,10 +6157,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45084</v>
+        <v>45054</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6153,7 +6173,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6196,7 +6216,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 42572-2024</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6210,10 +6230,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45565</v>
+        <v>45160</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6226,7 +6246,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.3</v>
+        <v>18.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6269,7 +6289,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 2496-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6279,14 +6299,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45653</v>
+        <v>45313</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6298,8 +6318,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6342,7 +6367,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6356,10 +6381,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44894</v>
+        <v>44904</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6372,7 +6397,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6415,7 +6440,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6425,14 +6450,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44776</v>
+        <v>45110</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6444,13 +6469,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6493,7 +6513,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6507,10 +6527,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45257</v>
+        <v>46086</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6522,13 +6542,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6571,7 +6586,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 2496-2024</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6581,14 +6596,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45313</v>
+        <v>44546</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6600,13 +6615,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6649,7 +6659,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6663,10 +6673,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45533</v>
+        <v>46097</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6679,7 +6689,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6722,7 +6732,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6736,10 +6746,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44803</v>
+        <v>45110</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6752,7 +6762,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.1</v>
+        <v>3.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6795,7 +6805,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 3673-2026</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6809,10 +6819,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46043</v>
+        <v>45061</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6825,7 +6835,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6868,7 +6878,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6882,10 +6892,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44803</v>
+        <v>45251</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6898,7 +6908,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6941,7 +6951,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6955,10 +6965,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46048</v>
+        <v>45187</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6971,7 +6981,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7014,7 +7024,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60949-2025</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7028,10 +7038,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45996</v>
+        <v>44894</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7044,7 +7054,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>21.9</v>
+        <v>5.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7087,7 +7097,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7097,14 +7107,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45700</v>
+        <v>44803</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7117,7 +7127,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7160,7 +7170,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 38695-2026</t>
+          <t>A 60922-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7174,10 +7184,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46283</v>
+        <v>45261</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7190,7 +7200,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.3</v>
+        <v>7.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7233,7 +7243,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7243,14 +7253,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46086</v>
+        <v>45653</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7263,7 +7273,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7306,7 +7316,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7320,10 +7330,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44992</v>
+        <v>45162</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7379,7 +7389,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7393,10 +7403,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46097</v>
+        <v>44606</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7409,7 +7419,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7452,7 +7462,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 60922-2023</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7466,10 +7476,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45261</v>
+        <v>44992</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7482,7 +7492,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7525,7 +7535,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 28681-2025</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7539,10 +7549,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45819</v>
+        <v>45089</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7554,8 +7564,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>7.5</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7598,7 +7613,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7612,10 +7627,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44642</v>
+        <v>45644</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7627,13 +7642,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7676,7 +7686,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7690,10 +7700,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44827</v>
+        <v>46275</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7705,13 +7715,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7754,7 +7759,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7768,10 +7773,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45540</v>
+        <v>46275</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7784,7 +7789,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7827,7 +7832,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7841,10 +7846,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45162</v>
+        <v>45222</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7857,7 +7862,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7917,7 +7922,7 @@
         <v>44776</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7978,7 +7983,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7992,10 +7997,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45644</v>
+        <v>45533</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8008,7 +8013,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8051,7 +8056,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 38695-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8065,10 +8070,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45713</v>
+        <v>46283</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8080,13 +8085,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>9.699999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8129,7 +8129,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 3890-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8143,10 +8143,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45461</v>
+        <v>45684</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8202,7 +8202,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8212,14 +8212,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45363</v>
+        <v>45567</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8275,7 +8275,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8289,10 +8289,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45567</v>
+        <v>45461</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8348,7 +8348,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 21513-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8362,10 +8362,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45461</v>
+        <v>45782</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>12.5</v>
+        <v>2.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8421,7 +8421,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 3890-2025</t>
+          <t>A 19031-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8431,14 +8431,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45684</v>
+        <v>45427</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8494,7 +8494,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 21513-2025</t>
+          <t>A 35961-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8508,10 +8508,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45782</v>
+        <v>45533</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8567,7 +8567,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 22913-2026</t>
+          <t>A 22402-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8581,10 +8581,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46159</v>
+        <v>45786</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8596,13 +8596,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8645,7 +8640,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 48375-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8659,10 +8654,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45110</v>
+        <v>45590</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8674,8 +8669,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 24105-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45110</v>
+        <v>45796</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 60934-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46275</v>
+        <v>45261</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8864,7 +8864,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 28681-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8878,10 +8878,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46275</v>
+        <v>45819</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 40643-2024</t>
+          <t>A 41957-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2043,14 +2043,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45558</v>
+        <v>45903</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2099,146 +2099,146 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Gröngöling
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 40643-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45558</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Bergsslok
 Getrams</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 41957-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45903</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Gröngöling
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
         <v/>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
         <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6893-2026</t>
+          <t>A 15452-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2476,14 +2476,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46057</v>
+        <v>45020</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2495,17 +2495,22 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2520,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2532,46 +2537,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 39716-2023</t>
+          <t>A 6893-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2585,10 +2594,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45166</v>
+        <v>46057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2601,22 +2610,22 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2628,7 +2637,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2641,46 +2650,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33751-2024</t>
+          <t>A 46757-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2694,10 +2699,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45520</v>
+        <v>45198</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2709,13 +2714,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2724,10 +2724,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2742,59 +2742,59 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 46757-2023</t>
+          <t>A 33751-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45198</v>
+        <v>45520</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2823,8 +2823,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2833,10 +2838,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2851,59 +2856,59 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15452-2023</t>
+          <t>A 39716-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2913,14 +2918,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45020</v>
+        <v>45166</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2932,13 +2937,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2953,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2962,10 +2962,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2974,43 +2974,43 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
         <v/>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
         <v>44618</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>44468</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>44467</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>44619</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44474</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45089</v>
+        <v>45251</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3572,13 +3572,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3638,7 +3633,7 @@
         <v>45211</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3694,7 +3689,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3708,10 +3703,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45700</v>
+        <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3724,7 +3719,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3767,7 +3762,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 24105-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3781,10 +3776,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45540</v>
+        <v>45796</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3797,7 +3792,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3840,7 +3835,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 24636-2023</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3854,10 +3849,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45084</v>
+        <v>44904</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3870,7 +3865,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3913,7 +3908,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 60949-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3927,10 +3922,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45461</v>
+        <v>45996</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3943,7 +3938,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.5</v>
+        <v>21.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3986,7 +3981,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 41702-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4000,10 +3995,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44989</v>
+        <v>45176</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4015,8 +4010,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4059,7 +4059,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 3673-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44827</v>
+        <v>46043</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4088,13 +4088,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4137,7 +4132,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 60934-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4147,14 +4142,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44571</v>
+        <v>45261</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4167,7 +4162,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4210,7 +4205,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4224,10 +4219,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44642</v>
+        <v>46048</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4239,13 +4234,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4288,7 +4278,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4302,10 +4292,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44557</v>
+        <v>45160</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4318,7 +4308,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>18.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4361,7 +4351,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4375,10 +4365,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45478</v>
+        <v>45575</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4391,7 +4381,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4434,7 +4424,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 41702-2023</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4448,10 +4438,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45176</v>
+        <v>45054</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4463,13 +4453,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4512,7 +4497,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4526,10 +4511,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44803</v>
+        <v>45222</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4542,7 +4527,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.1</v>
+        <v>3.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4585,7 +4570,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4595,14 +4580,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44678</v>
+        <v>44904</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4615,7 +4600,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4658,7 +4643,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 42572-2024</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4672,10 +4657,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45565</v>
+        <v>45930</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4688,7 +4673,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4731,7 +4716,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4745,10 +4730,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45575</v>
+        <v>45061</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4761,7 +4746,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4804,7 +4789,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4818,10 +4803,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45257</v>
+        <v>44749</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4833,13 +4818,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4882,7 +4862,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4896,10 +4876,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45930</v>
+        <v>46086</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4912,7 +4892,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4972,7 +4952,7 @@
         <v>45940</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5028,7 +5008,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5038,14 +5018,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44776</v>
+        <v>46097</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5057,13 +5037,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5106,7 +5081,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 42572-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5120,10 +5095,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45035</v>
+        <v>45565</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5136,7 +5111,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5179,7 +5154,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5189,14 +5164,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45330</v>
+        <v>44894</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5209,7 +5184,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5252,7 +5227,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5266,10 +5241,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45061</v>
+        <v>44989</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5282,7 +5257,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5325,7 +5300,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5339,10 +5314,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44904</v>
+        <v>45089</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5354,8 +5329,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5398,7 +5378,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5412,10 +5392,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44749</v>
+        <v>45089</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5427,8 +5407,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5471,7 +5456,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5481,14 +5466,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45713</v>
+        <v>44502</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5500,13 +5485,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>9.699999999999999</v>
+        <v>14.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5549,7 +5529,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5563,10 +5543,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44502</v>
+        <v>45363</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5579,7 +5559,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>14.7</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5622,7 +5602,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5632,14 +5612,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45363</v>
+        <v>45261</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5652,7 +5632,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5695,7 +5675,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5709,10 +5689,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45191</v>
+        <v>45061</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5724,13 +5704,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5790,7 +5765,7 @@
         <v>46159</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5851,7 +5826,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 60949-2025</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5865,10 +5840,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45996</v>
+        <v>45187</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5881,7 +5856,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>21.9</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5924,7 +5899,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5934,14 +5909,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45261</v>
+        <v>44546</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5954,7 +5929,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5997,7 +5972,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3673-2026</t>
+          <t>A 28681-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6011,10 +5986,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46043</v>
+        <v>45819</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6027,7 +6002,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.8</v>
+        <v>7.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6070,7 +6045,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6084,10 +6059,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46048</v>
+        <v>45110</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6100,7 +6075,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6143,7 +6118,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6157,10 +6132,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45054</v>
+        <v>44557</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6173,7 +6148,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6216,7 +6191,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6230,10 +6205,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45160</v>
+        <v>45110</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6246,7 +6221,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>18.1</v>
+        <v>3.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6289,7 +6264,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 2496-2024</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6303,10 +6278,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45313</v>
+        <v>45035</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6318,13 +6293,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6367,7 +6337,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6381,10 +6351,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44904</v>
+        <v>44606</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6397,7 +6367,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6440,7 +6410,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6454,10 +6424,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45110</v>
+        <v>45191</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6469,8 +6439,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6513,7 +6488,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6523,14 +6498,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46086</v>
+        <v>44678</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6543,7 +6518,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6586,7 +6561,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6596,14 +6571,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44546</v>
+        <v>45478</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6616,7 +6591,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6659,7 +6634,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6669,14 +6644,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46097</v>
+        <v>44571</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6689,7 +6664,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6732,7 +6707,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 24636-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6746,10 +6721,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45110</v>
+        <v>45084</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6762,7 +6737,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6805,7 +6780,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6815,14 +6790,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45061</v>
+        <v>45653</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6878,7 +6853,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6888,14 +6863,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45251</v>
+        <v>44776</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6907,8 +6882,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6951,7 +6931,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6965,10 +6945,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45187</v>
+        <v>45257</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6980,8 +6960,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7024,7 +7009,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 2496-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7038,10 +7023,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44894</v>
+        <v>45313</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7053,8 +7038,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7097,7 +7087,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7111,10 +7101,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44803</v>
+        <v>45533</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7127,7 +7117,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7170,7 +7160,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60922-2023</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7184,10 +7174,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45261</v>
+        <v>44803</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7200,7 +7190,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7243,7 +7233,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7253,14 +7243,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45653</v>
+        <v>44803</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7273,7 +7263,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7316,7 +7306,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7330,10 +7320,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45162</v>
+        <v>46275</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7346,7 +7336,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7389,7 +7379,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7403,10 +7393,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44606</v>
+        <v>46275</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7419,7 +7409,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7462,7 +7452,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7472,14 +7462,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44992</v>
+        <v>45700</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7492,7 +7482,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7535,7 +7525,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 38695-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7549,10 +7539,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45089</v>
+        <v>46283</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7564,13 +7554,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7613,7 +7598,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7627,10 +7612,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45644</v>
+        <v>44992</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7643,7 +7628,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7686,7 +7671,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 60922-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7700,10 +7685,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46275</v>
+        <v>45261</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7716,7 +7701,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>7.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7759,7 +7744,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7773,10 +7758,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46275</v>
+        <v>44642</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7788,8 +7773,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7832,7 +7822,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7846,10 +7836,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45222</v>
+        <v>44827</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7861,8 +7851,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7905,7 +7900,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7915,14 +7910,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44776</v>
+        <v>45540</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7934,13 +7929,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7983,7 +7973,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7997,10 +7987,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45533</v>
+        <v>45162</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8013,7 +8003,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8056,7 +8046,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 38695-2026</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8066,14 +8056,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46283</v>
+        <v>44776</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8085,8 +8075,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8129,7 +8124,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 3890-2025</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8143,10 +8138,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45684</v>
+        <v>45644</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8159,7 +8154,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8202,7 +8197,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8216,10 +8211,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45567</v>
+        <v>45713</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8231,8 +8226,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8275,7 +8275,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8292,7 +8292,7 @@
         <v>45461</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>12.5</v>
+        <v>3.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8348,7 +8348,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 21513-2025</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8362,10 +8362,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45782</v>
+        <v>45567</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8421,7 +8421,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 19031-2024</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8431,14 +8431,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45427</v>
+        <v>45461</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.7</v>
+        <v>12.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8494,7 +8494,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 35961-2024</t>
+          <t>A 3890-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8508,10 +8508,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45533</v>
+        <v>45684</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8567,7 +8567,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 22402-2025</t>
+          <t>A 21513-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8581,10 +8581,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45786</v>
+        <v>45782</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8657,7 +8657,7 @@
         <v>45590</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 24105-2025</t>
+          <t>A 22402-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45796</v>
+        <v>45786</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 60934-2023</t>
+          <t>A 35961-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45261</v>
+        <v>45533</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8864,7 +8864,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 28681-2025</t>
+          <t>A 19031-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8874,14 +8874,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45819</v>
+        <v>45427</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>7.5</v>
+        <v>2.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>45903</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>45558</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45020</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>46057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>45198</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>45520</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>45166</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44618</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>44468</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>44467</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>44619</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44474</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>45251</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45211</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45796</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44904</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45996</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>45176</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>46043</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>45261</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>46048</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>45160</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>45575</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>45054</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>45222</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>44904</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>45930</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>45061</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>44749</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>46086</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>45940</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>46097</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45565</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44894</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>44989</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>45089</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>45089</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>44502</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>45363</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>45261</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>45061</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>46159</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>45187</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>44546</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>45819</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>45110</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>44557</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45110</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>45035</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44606</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>45191</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>44678</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>45478</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>44571</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>45084</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>45653</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>44776</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>45257</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>45313</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>45533</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44803</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44803</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>46275</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>46275</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>45700</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>46283</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>44992</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>45261</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>44642</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>44827</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>45540</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>45162</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>44776</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>45644</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>45713</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>45461</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         <v>45567</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>45461</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>45684</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>45782</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>45590</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>45786</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>45533</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45427</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>45903</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>45558</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45020</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>46057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>45198</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>45520</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>45166</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44618</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>44468</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>44467</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>44619</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44474</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>45251</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45211</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>45330</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45796</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44904</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45996</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>45176</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>46043</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>45261</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>46048</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>45160</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>45575</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>45054</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>45222</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>44904</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>45930</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>45061</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>44749</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>46086</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>45940</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>46097</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45565</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44894</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>44989</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>45089</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>45089</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>44502</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>45363</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>45261</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>45061</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>46159</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>45187</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>44546</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>45819</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>45110</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>44557</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45110</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>45035</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44606</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>45191</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>44678</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>45478</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>44571</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>45084</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>45653</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>44776</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>45257</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>45313</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>45533</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44803</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44803</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>46275</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>46275</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>45700</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>46283</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>44992</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>45261</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>44642</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>44827</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>45540</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>45162</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>44776</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>45644</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>45713</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>45461</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         <v>45567</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>45461</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>45684</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>45782</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>45590</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>45786</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>45533</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45427</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE101"/>
+  <dimension ref="A1:AE100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41957-2025</t>
+          <t>A 40643-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2043,14 +2043,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45903</v>
+        <v>45558</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2099,146 +2099,146 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Bergsslok
+Getrams</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 41957-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45903</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Gröngöling
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 40643-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45558</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Bergsslok
-Getrams</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
         <v/>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
         <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45020</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>46057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 46757-2023</t>
+          <t>A 39716-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2695,14 +2695,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45198</v>
+        <v>45166</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2724,13 +2724,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2742,7 +2742,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2755,39 +2755,39 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
         <v/>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         <v>45520</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 39716-2023</t>
+          <t>A 46757-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2918,14 +2918,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45166</v>
+        <v>45198</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2947,13 +2947,13 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,7 +2965,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2978,39 +2978,39 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
         <v/>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
         <v>44618</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>44468</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 53090-2021</t>
+          <t>A 31697-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3178,14 +3178,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44467</v>
+        <v>44776</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3197,8 +3197,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3241,7 +3246,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31697-2022</t>
+          <t>A 9767-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3251,14 +3256,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44776</v>
+        <v>44619</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3270,13 +3275,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 9767-2022</t>
+          <t>A 65340-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3329,14 +3329,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44619</v>
+        <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3348,8 +3348,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3392,7 +3397,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 65340-2021</t>
+          <t>A 55112-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3402,14 +3407,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44515</v>
+        <v>44474</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3421,13 +3426,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3470,7 +3470,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 55112-2021</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44474</v>
+        <v>45089</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3497,6 +3497,11 @@
       <c r="G28" t="inlineStr">
         <is>
           <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -3543,7 +3548,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 49592-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3557,10 +3562,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45251</v>
+        <v>45211</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3573,7 +3578,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3616,7 +3621,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 49592-2023</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3626,14 +3631,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45211</v>
+        <v>45700</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3646,7 +3651,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3689,7 +3694,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 22402-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3699,14 +3704,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45330</v>
+        <v>45786</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3719,7 +3724,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3762,7 +3767,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 24105-2025</t>
+          <t>A 48375-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3776,10 +3781,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45796</v>
+        <v>45590</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3791,8 +3796,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3835,7 +3845,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 24105-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3849,10 +3859,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44904</v>
+        <v>45796</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3865,7 +3875,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3925,7 +3935,7 @@
         <v>45996</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3981,7 +3991,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 41702-2023</t>
+          <t>A 60934-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3995,10 +4005,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45176</v>
+        <v>45261</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4010,13 +4020,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4059,7 +4064,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3673-2026</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4073,10 +4078,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46043</v>
+        <v>45540</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4089,7 +4094,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4132,7 +4137,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60934-2023</t>
+          <t>A 24636-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4146,10 +4151,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45261</v>
+        <v>45084</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4162,7 +4167,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4205,7 +4210,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4219,10 +4224,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46048</v>
+        <v>44989</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4235,7 +4240,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4278,7 +4283,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4292,10 +4297,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45160</v>
+        <v>45461</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4308,7 +4313,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>18.1</v>
+        <v>3.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4351,7 +4356,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4365,10 +4370,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45575</v>
+        <v>45930</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4381,7 +4386,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4424,7 +4429,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4434,14 +4439,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45054</v>
+        <v>44571</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4454,7 +4459,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4497,7 +4502,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4511,10 +4516,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45222</v>
+        <v>44827</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4526,8 +4531,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4570,7 +4580,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4584,10 +4594,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44904</v>
+        <v>45940</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4643,7 +4653,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 28681-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4657,10 +4667,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45930</v>
+        <v>45819</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4673,7 +4683,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.3</v>
+        <v>7.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4716,7 +4726,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4730,10 +4740,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45061</v>
+        <v>44642</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4745,8 +4755,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4789,7 +4804,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4803,10 +4818,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44749</v>
+        <v>44557</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4819,7 +4834,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4862,7 +4877,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 3673-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4876,10 +4891,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46086</v>
+        <v>46043</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4892,7 +4907,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4935,7 +4950,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4949,10 +4964,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45940</v>
+        <v>45478</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4965,7 +4980,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5008,7 +5023,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5022,10 +5037,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46097</v>
+        <v>46048</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5038,7 +5053,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5081,7 +5096,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 42572-2024</t>
+          <t>A 41702-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5095,10 +5110,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45565</v>
+        <v>45176</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5110,8 +5125,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5154,7 +5174,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5168,10 +5188,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44894</v>
+        <v>44803</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5184,7 +5204,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5227,7 +5247,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5237,14 +5257,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44989</v>
+        <v>44678</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5257,7 +5277,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5300,7 +5320,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 42572-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5314,10 +5334,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45089</v>
+        <v>45565</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5329,13 +5349,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5378,7 +5393,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5392,10 +5407,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45089</v>
+        <v>45575</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5407,13 +5422,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5456,7 +5466,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5466,14 +5476,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44502</v>
+        <v>45257</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5485,8 +5495,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>14.7</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5529,7 +5544,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5539,14 +5554,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45363</v>
+        <v>46086</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5559,7 +5574,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5602,7 +5617,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5616,10 +5631,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45261</v>
+        <v>46097</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5632,7 +5647,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5675,7 +5690,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5685,14 +5700,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45061</v>
+        <v>44776</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5704,8 +5719,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5748,7 +5768,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 22913-2026</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5762,10 +5782,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46159</v>
+        <v>45035</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5777,13 +5797,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5826,7 +5841,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5836,14 +5851,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45187</v>
+        <v>45330</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5856,7 +5871,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5899,7 +5914,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5909,14 +5924,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44546</v>
+        <v>45061</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5929,7 +5944,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5972,7 +5987,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28681-2025</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5986,10 +6001,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45819</v>
+        <v>44904</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6002,7 +6017,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6045,7 +6060,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6059,10 +6074,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45110</v>
+        <v>44749</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6075,7 +6090,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6118,7 +6133,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6132,10 +6147,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44557</v>
+        <v>45713</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6147,8 +6162,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6191,7 +6211,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6201,14 +6221,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45110</v>
+        <v>44502</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6221,7 +6241,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.1</v>
+        <v>14.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6264,7 +6284,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6278,10 +6298,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45035</v>
+        <v>45191</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6293,8 +6313,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6337,7 +6362,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6351,10 +6376,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44606</v>
+        <v>45261</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6367,7 +6392,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6410,7 +6435,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6420,14 +6445,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45191</v>
+        <v>45363</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6439,13 +6464,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6488,7 +6508,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6498,14 +6518,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44678</v>
+        <v>45054</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6518,7 +6538,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6561,7 +6581,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 22913-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6575,10 +6595,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45478</v>
+        <v>46159</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6590,8 +6610,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6634,7 +6659,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6644,14 +6669,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44571</v>
+        <v>45160</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6664,7 +6689,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>18.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6707,7 +6732,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 24636-2023</t>
+          <t>A 2496-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6721,10 +6746,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45084</v>
+        <v>45313</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6736,8 +6761,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6780,7 +6810,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6790,14 +6820,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45653</v>
+        <v>44904</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6810,7 +6840,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6853,7 +6883,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6863,14 +6893,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44776</v>
+        <v>44546</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6882,13 +6912,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6931,7 +6956,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6945,10 +6970,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45257</v>
+        <v>45110</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6960,13 +6985,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7009,7 +7029,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 2496-2024</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7023,10 +7043,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45313</v>
+        <v>45110</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7038,13 +7058,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7087,7 +7102,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7101,10 +7116,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45533</v>
+        <v>45061</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7117,7 +7132,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7160,7 +7175,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7174,10 +7189,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44803</v>
+        <v>45251</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7190,7 +7205,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7233,7 +7248,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7247,10 +7262,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44803</v>
+        <v>45187</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7263,7 +7278,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7306,7 +7321,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7320,10 +7335,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46275</v>
+        <v>44894</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7336,7 +7351,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7379,7 +7394,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7393,10 +7408,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46275</v>
+        <v>44803</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7409,7 +7424,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7452,7 +7467,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 60922-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7462,14 +7477,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45700</v>
+        <v>45261</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7482,7 +7497,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7525,7 +7540,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 38695-2026</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7535,14 +7550,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46283</v>
+        <v>45653</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7555,7 +7570,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7598,7 +7613,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7612,10 +7627,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44992</v>
+        <v>45162</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7671,7 +7686,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 60922-2023</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7685,10 +7700,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45261</v>
+        <v>44606</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7701,7 +7716,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>7.6</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7744,7 +7759,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7758,10 +7773,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44642</v>
+        <v>44992</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7773,13 +7788,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7822,7 +7832,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7836,10 +7846,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44827</v>
+        <v>45089</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7853,11 +7863,11 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7900,7 +7910,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7914,10 +7924,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45540</v>
+        <v>45644</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7930,7 +7940,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7973,7 +7983,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7987,10 +7997,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45162</v>
+        <v>46275</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8003,7 +8013,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8046,7 +8056,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8056,14 +8066,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44776</v>
+        <v>46275</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8075,13 +8085,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8124,7 +8129,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8138,10 +8143,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45644</v>
+        <v>45222</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8154,7 +8159,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8197,7 +8202,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8207,14 +8212,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45713</v>
+        <v>44776</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8228,11 +8233,11 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>9.699999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8275,7 +8280,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8289,10 +8294,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45461</v>
+        <v>45533</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8305,7 +8310,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8348,7 +8353,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 3890-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8362,10 +8367,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45567</v>
+        <v>45684</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8378,7 +8383,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8421,7 +8426,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8435,10 +8440,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45461</v>
+        <v>45567</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8451,7 +8456,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8494,7 +8499,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 3890-2025</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8508,10 +8513,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45684</v>
+        <v>45461</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8524,7 +8529,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.9</v>
+        <v>12.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8584,7 +8589,7 @@
         <v>45782</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8640,7 +8645,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 48375-2024</t>
+          <t>A 38695-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8654,10 +8659,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45590</v>
+        <v>46283</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8669,13 +8674,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 22402-2025</t>
+          <t>A 19031-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8728,14 +8728,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45786</v>
+        <v>45427</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8788,7 +8788,7 @@
       </c>
       <c r="V99" s="2" t="inlineStr"/>
     </row>
-    <row r="100" ht="15" customHeight="1">
+    <row r="100">
       <c r="A100" t="inlineStr">
         <is>
           <t>A 35961-2024</t>
@@ -8808,7 +8808,7 @@
         <v>45533</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8860,79 +8860,6 @@
         <v>0</v>
       </c>
       <c r="V100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>A 19031-2024</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="n">
-        <v>45427</v>
-      </c>
-      <c r="E101" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I101" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J101" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" t="n">
-        <v>0</v>
-      </c>
-      <c r="T101" t="n">
-        <v>0</v>
-      </c>
-      <c r="U101" t="n">
-        <v>0</v>
-      </c>
-      <c r="V101" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE100"/>
+  <dimension ref="A1:AE99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 40643-2024</t>
+          <t>A 41957-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2043,14 +2043,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45558</v>
+        <v>45903</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2099,146 +2099,146 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Gröngöling
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 40643-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45558</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Bergsslok
 Getrams</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 41957-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45903</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Gröngöling
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
         <v/>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
         <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45020</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>46057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 39716-2023</t>
+          <t>A 46757-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2695,14 +2695,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45166</v>
+        <v>45198</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2724,13 +2724,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2742,7 +2742,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2755,39 +2755,39 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
         <v/>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         <v>45520</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 46757-2023</t>
+          <t>A 39716-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2918,14 +2918,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45198</v>
+        <v>45166</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2947,13 +2947,13 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,7 +2965,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2978,39 +2978,39 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
         <v/>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
         <v>44618</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 53462-2021</t>
+          <t>A 31697-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3100,14 +3100,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44468</v>
+        <v>44776</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3121,11 +3121,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3168,7 +3168,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31697-2022</t>
+          <t>A 9767-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3178,14 +3178,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44776</v>
+        <v>44619</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3197,13 +3197,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3246,7 +3241,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9767-2022</t>
+          <t>A 65340-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3256,14 +3251,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44619</v>
+        <v>44515</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3275,8 +3270,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 65340-2021</t>
+          <t>A 55112-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3329,14 +3329,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44515</v>
+        <v>44474</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3348,13 +3348,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3397,7 +3392,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 55112-2021</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3411,10 +3406,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44474</v>
+        <v>45251</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3427,7 +3422,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3470,7 +3465,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 49592-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3484,10 +3479,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45089</v>
+        <v>45211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3499,13 +3494,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3548,7 +3538,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 49592-2023</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3558,14 +3548,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45211</v>
+        <v>45330</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3621,7 +3611,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 60949-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3631,14 +3621,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45700</v>
+        <v>45996</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3651,7 +3641,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>21.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3694,7 +3684,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22402-2025</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3708,10 +3698,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45786</v>
+        <v>44904</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3724,7 +3714,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3767,7 +3757,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 48375-2024</t>
+          <t>A 24105-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3781,10 +3771,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45590</v>
+        <v>45796</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3796,13 +3786,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3845,7 +3830,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 24105-2025</t>
+          <t>A 41702-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3859,10 +3844,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45796</v>
+        <v>45176</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3874,8 +3859,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3918,7 +3908,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60949-2025</t>
+          <t>A 60934-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3932,10 +3922,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45996</v>
+        <v>45261</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3948,7 +3938,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>21.9</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3991,7 +3981,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60934-2023</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4005,10 +3995,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45261</v>
+        <v>45160</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4021,7 +4011,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>18.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4064,7 +4054,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4078,10 +4068,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45540</v>
+        <v>45575</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4094,7 +4084,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4137,7 +4127,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24636-2023</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4151,10 +4141,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45084</v>
+        <v>45054</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4167,7 +4157,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4210,7 +4200,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4224,10 +4214,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44989</v>
+        <v>45222</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4240,7 +4230,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4283,7 +4273,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4297,10 +4287,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45461</v>
+        <v>44904</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4313,7 +4303,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4373,7 +4363,7 @@
         <v>45930</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4429,7 +4419,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 3673-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4439,14 +4429,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44571</v>
+        <v>46043</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4459,7 +4449,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4502,7 +4492,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4516,10 +4506,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44827</v>
+        <v>45061</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4531,13 +4521,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4580,7 +4565,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4594,10 +4579,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45940</v>
+        <v>44749</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4610,7 +4595,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4653,7 +4638,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28681-2025</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4667,10 +4652,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45819</v>
+        <v>46048</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4683,7 +4668,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>7.5</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4726,7 +4711,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 28681-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4740,10 +4725,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44642</v>
+        <v>45819</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4755,13 +4740,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>7.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4804,7 +4784,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4818,10 +4798,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44557</v>
+        <v>45940</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4834,7 +4814,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4877,7 +4857,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 3673-2026</t>
+          <t>A 42572-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4891,10 +4871,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46043</v>
+        <v>45565</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4907,7 +4887,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4950,7 +4930,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4964,10 +4944,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45478</v>
+        <v>44894</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4980,7 +4960,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5023,7 +5003,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5037,10 +5017,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46048</v>
+        <v>44989</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5053,7 +5033,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5096,7 +5076,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 41702-2023</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5110,10 +5090,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45176</v>
+        <v>45089</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5127,11 +5107,11 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5174,7 +5154,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5188,10 +5168,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44803</v>
+        <v>45089</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5203,8 +5183,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>6.1</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5247,7 +5232,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5261,10 +5246,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44678</v>
+        <v>44502</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5277,7 +5262,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.6</v>
+        <v>14.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5320,7 +5305,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 42572-2024</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5334,10 +5319,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45565</v>
+        <v>46086</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5350,7 +5335,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5393,7 +5378,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5407,10 +5392,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45575</v>
+        <v>46097</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5423,7 +5408,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5466,7 +5451,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5480,10 +5465,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45257</v>
+        <v>45261</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5495,13 +5480,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5544,7 +5524,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5558,10 +5538,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46086</v>
+        <v>45061</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5574,7 +5554,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5617,7 +5597,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5631,10 +5611,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46097</v>
+        <v>45187</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5647,7 +5627,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5690,7 +5670,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5700,14 +5680,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44776</v>
+        <v>44546</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5719,13 +5699,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5768,7 +5743,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5782,10 +5757,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45035</v>
+        <v>44557</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5798,7 +5773,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5841,7 +5816,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5851,14 +5826,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45330</v>
+        <v>45035</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5871,7 +5846,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5914,7 +5889,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5928,10 +5903,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45061</v>
+        <v>44606</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5944,7 +5919,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5987,7 +5962,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6001,10 +5976,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44904</v>
+        <v>45191</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6016,8 +5991,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6060,7 +6040,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6070,14 +6050,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44749</v>
+        <v>45363</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6090,7 +6070,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6133,7 +6113,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6143,14 +6123,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45713</v>
+        <v>44678</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6162,13 +6142,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>9.699999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6211,7 +6186,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6221,14 +6196,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44502</v>
+        <v>45478</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6241,7 +6216,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>14.7</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6284,7 +6259,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6294,14 +6269,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45191</v>
+        <v>44571</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6313,13 +6288,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6362,7 +6332,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 22913-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6376,10 +6346,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45261</v>
+        <v>46159</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6391,8 +6361,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6435,7 +6410,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 24636-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6445,14 +6420,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45363</v>
+        <v>45084</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6465,7 +6440,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6508,7 +6483,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6518,14 +6493,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45054</v>
+        <v>45653</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6538,7 +6513,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6581,7 +6556,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 22913-2026</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6591,14 +6566,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46159</v>
+        <v>44776</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6612,7 +6587,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -6659,7 +6634,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6673,10 +6648,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45160</v>
+        <v>45110</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6689,7 +6664,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>18.1</v>
+        <v>2.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6732,7 +6707,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 2496-2024</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6746,10 +6721,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45313</v>
+        <v>45110</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6761,13 +6736,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6810,7 +6780,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6824,10 +6794,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44904</v>
+        <v>45257</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6839,8 +6809,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6883,7 +6858,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 2496-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6893,14 +6868,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44546</v>
+        <v>45313</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6912,8 +6887,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6956,7 +6936,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6970,10 +6950,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45110</v>
+        <v>45533</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6986,7 +6966,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7029,7 +7009,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7043,10 +7023,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45110</v>
+        <v>44803</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7059,7 +7039,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.1</v>
+        <v>6.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7102,7 +7082,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7116,10 +7096,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45061</v>
+        <v>44803</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7132,7 +7112,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7175,7 +7155,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7185,14 +7165,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45251</v>
+        <v>45700</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7205,7 +7185,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7248,7 +7228,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7262,10 +7242,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45187</v>
+        <v>44992</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7278,7 +7258,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7321,7 +7301,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 60922-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7335,10 +7315,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44894</v>
+        <v>45261</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7351,7 +7331,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7394,7 +7374,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7408,10 +7388,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44803</v>
+        <v>44642</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7423,8 +7403,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7467,7 +7452,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 60922-2023</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7481,10 +7466,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45261</v>
+        <v>44827</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7496,8 +7481,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>7.6</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7540,7 +7530,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7550,14 +7540,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45653</v>
+        <v>45540</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7570,7 +7560,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7630,7 +7620,7 @@
         <v>45162</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7686,7 +7676,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7700,10 +7690,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44606</v>
+        <v>46275</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7716,7 +7706,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7759,7 +7749,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7769,14 +7759,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44992</v>
+        <v>44776</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7788,8 +7778,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7832,7 +7827,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7846,10 +7841,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45089</v>
+        <v>46275</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7861,13 +7856,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7927,7 +7917,7 @@
         <v>45644</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7983,7 +7973,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 38695-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7997,10 +7987,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8013,7 +8003,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8056,7 +8046,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8070,10 +8060,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46275</v>
+        <v>45713</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8085,8 +8075,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>3.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8129,7 +8124,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8143,10 +8138,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45222</v>
+        <v>45461</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8159,7 +8154,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8202,7 +8197,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8212,14 +8207,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44776</v>
+        <v>45567</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8231,13 +8226,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8280,7 +8270,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8294,10 +8284,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45533</v>
+        <v>45461</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8310,7 +8300,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.4</v>
+        <v>12.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8370,7 +8360,7 @@
         <v>45684</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8426,7 +8416,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 21513-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8440,10 +8430,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45567</v>
+        <v>45782</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8456,7 +8446,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8499,7 +8489,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 48375-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8513,10 +8503,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45461</v>
+        <v>45590</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8528,8 +8518,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>12.5</v>
+        <v>4.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8572,7 +8567,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 21513-2025</t>
+          <t>A 22402-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8586,10 +8581,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45782</v>
+        <v>45786</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8602,7 +8597,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8645,7 +8640,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 38695-2026</t>
+          <t>A 35961-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8659,10 +8654,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46283</v>
+        <v>45533</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8675,7 +8670,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8715,7 +8710,7 @@
       </c>
       <c r="V98" s="2" t="inlineStr"/>
     </row>
-    <row r="99" ht="15" customHeight="1">
+    <row r="99">
       <c r="A99" t="inlineStr">
         <is>
           <t>A 19031-2024</t>
@@ -8735,7 +8730,7 @@
         <v>45427</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8787,79 +8782,6 @@
         <v>0</v>
       </c>
       <c r="V99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>A 35961-2024</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="n">
-        <v>45533</v>
-      </c>
-      <c r="E100" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I100" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J100" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" t="n">
-        <v>0</v>
-      </c>
-      <c r="S100" t="n">
-        <v>0</v>
-      </c>
-      <c r="T100" t="n">
-        <v>0</v>
-      </c>
-      <c r="U100" t="n">
-        <v>0</v>
-      </c>
-      <c r="V100" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41957-2025</t>
+          <t>A 40643-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2043,14 +2043,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45903</v>
+        <v>45558</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2099,374 +2099,374 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Bergsslok
+Getrams</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 64345-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45280</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 64345-2023 artfynd.xlsx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 64345-2023 karta.png", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 64345-2023 georefererad karta.tif", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 64345-2023 FSC-klagomål.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 64345-2023 FSC-klagomål mail.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 64345-2023 tillsynsbegäran.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 64345-2023 tillsynsbegäran mail.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 64345-2023 prioriterade fågelarter.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 41957-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45903</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Gröngöling
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 40643-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45558</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 22874-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T16" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>2</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Bergsslok
-Getrams</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 22874-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46156</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Kandelabersvamp
 Blåsippa</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 22874-2026 artfynd.xlsx", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 22874-2026 karta.png", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 22874-2026 georefererad karta.tif", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 22874-2026 FSC-klagomål.docx", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 22874-2026 FSC-klagomål mail.docx", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 22874-2026 tillsynsbegäran.docx", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 22874-2026 tillsynsbegäran mail.docx", "A 22874-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 64345-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45280</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 64345-2023 artfynd.xlsx", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 64345-2023 karta.png", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 64345-2023 georefererad karta.tif", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 64345-2023 FSC-klagomål.docx", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 64345-2023 FSC-klagomål mail.docx", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 64345-2023 tillsynsbegäran.docx", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 64345-2023 tillsynsbegäran mail.docx", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 64345-2023 prioriterade fågelarter.docx", "A 64345-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 15452-2023</t>
+          <t>A 39716-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2476,14 +2476,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45020</v>
+        <v>45166</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2495,13 +2495,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2516,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2525,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2537,50 +2532,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 6893-2026</t>
+          <t>A 33751-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2590,14 +2585,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46057</v>
+        <v>45520</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2609,20 +2604,25 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2637,48 +2637,52 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
         <v/>
       </c>
     </row>
@@ -2702,7 +2706,7 @@
         <v>45198</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2794,7 +2798,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33751-2024</t>
+          <t>A 15452-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2808,10 +2812,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45520</v>
+        <v>45020</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2829,7 +2833,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2841,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2853,62 +2857,62 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 39716-2023</t>
+          <t>A 6893-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2922,10 +2926,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45166</v>
+        <v>46057</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2938,22 +2942,22 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2978,39 +2982,35 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
         <v>44618</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31697-2022</t>
+          <t>A 9767-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3100,14 +3100,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44776</v>
+        <v>44619</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3119,13 +3119,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3168,7 +3163,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9767-2022</t>
+          <t>A 31697-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3178,14 +3173,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44619</v>
+        <v>44776</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3197,8 +3192,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3258,7 +3258,7 @@
         <v>44515</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 55112-2021</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44474</v>
+        <v>45089</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3346,6 +3346,11 @@
       <c r="G26" t="inlineStr">
         <is>
           <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -3392,7 +3397,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 55112-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3406,10 +3411,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45251</v>
+        <v>44474</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3422,7 +3427,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3465,7 +3470,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 49592-2023</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3479,10 +3484,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45211</v>
+        <v>45261</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3495,7 +3500,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3538,7 +3543,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3548,14 +3553,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45330</v>
+        <v>44557</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3568,7 +3573,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3611,7 +3616,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60949-2025</t>
+          <t>A 49592-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3625,10 +3630,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45996</v>
+        <v>45211</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3641,7 +3646,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>21.9</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3684,7 +3689,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 60922-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3698,10 +3703,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44904</v>
+        <v>45261</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3714,7 +3719,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>7.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3757,7 +3762,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 24105-2025</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3767,14 +3772,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45796</v>
+        <v>45653</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3787,7 +3792,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3830,7 +3835,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 41702-2023</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3844,10 +3849,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45176</v>
+        <v>45478</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3859,13 +3864,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3908,7 +3908,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60934-2023</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45261</v>
+        <v>45162</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3981,7 +3981,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45160</v>
+        <v>44606</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>18.1</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45575</v>
+        <v>45054</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45054</v>
+        <v>44992</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4200,7 +4200,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45222</v>
+        <v>45089</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4229,8 +4229,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4273,7 +4278,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4287,10 +4292,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44904</v>
+        <v>45644</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4303,7 +4308,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4346,7 +4351,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4356,14 +4361,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45930</v>
+        <v>45700</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4376,7 +4381,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4419,7 +4424,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 3673-2026</t>
+          <t>A 41702-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4433,10 +4438,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46043</v>
+        <v>45176</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4448,8 +4453,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4492,7 +4502,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4506,10 +4516,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45061</v>
+        <v>45160</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4522,7 +4532,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>18.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4565,7 +4575,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 2496-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4579,10 +4589,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44749</v>
+        <v>45313</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4594,8 +4604,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4638,7 +4653,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4652,10 +4667,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46048</v>
+        <v>44904</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4668,7 +4683,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4711,7 +4726,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 28681-2025</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4725,10 +4740,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45819</v>
+        <v>44803</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4741,7 +4756,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4784,7 +4799,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4794,14 +4809,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45940</v>
+        <v>44546</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4814,7 +4829,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4857,7 +4872,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 42572-2024</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4867,14 +4882,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45565</v>
+        <v>44678</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4887,7 +4902,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4930,7 +4945,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4944,10 +4959,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44894</v>
+        <v>45222</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4960,7 +4975,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5003,7 +5018,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 42572-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5017,10 +5032,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44989</v>
+        <v>45565</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5033,7 +5048,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5076,7 +5091,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5086,14 +5101,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45089</v>
+        <v>44776</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5107,11 +5122,11 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5154,7 +5169,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5168,10 +5183,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45089</v>
+        <v>45533</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5183,13 +5198,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5232,7 +5242,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5242,14 +5252,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44502</v>
+        <v>45575</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5262,7 +5272,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>14.7</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5305,7 +5315,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5319,10 +5329,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46086</v>
+        <v>45257</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5334,8 +5344,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5378,7 +5393,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 3890-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5392,10 +5407,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46097</v>
+        <v>45684</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5408,7 +5423,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5451,7 +5466,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5465,10 +5480,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45261</v>
+        <v>45567</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5481,7 +5496,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5524,7 +5539,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5538,10 +5553,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45061</v>
+        <v>45461</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5554,7 +5569,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.3</v>
+        <v>12.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5597,7 +5612,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 21513-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5611,10 +5626,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45187</v>
+        <v>45782</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5627,7 +5642,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5670,7 +5685,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5680,14 +5695,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44546</v>
+        <v>45061</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5700,7 +5715,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5743,7 +5758,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 19031-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5753,14 +5768,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44557</v>
+        <v>45427</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5773,7 +5788,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5816,7 +5831,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 35961-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5830,10 +5845,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45035</v>
+        <v>45533</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5846,7 +5861,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5889,7 +5904,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 22402-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5903,10 +5918,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44606</v>
+        <v>45786</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5919,7 +5934,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5962,7 +5977,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 48375-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5976,10 +5991,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45191</v>
+        <v>45590</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5997,7 +6012,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6040,7 +6055,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6050,14 +6065,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45363</v>
+        <v>44776</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6069,8 +6084,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6113,7 +6133,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6123,14 +6143,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44678</v>
+        <v>45035</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6143,7 +6163,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6186,7 +6206,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 24105-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6200,10 +6220,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45478</v>
+        <v>45796</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6216,7 +6236,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6259,7 +6279,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6269,14 +6289,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44571</v>
+        <v>45540</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6289,7 +6309,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6332,7 +6352,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 22913-2026</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6342,14 +6362,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46159</v>
+        <v>45330</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6361,13 +6381,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6410,7 +6425,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 24636-2023</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6424,10 +6439,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45084</v>
+        <v>45061</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6440,7 +6455,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6483,7 +6498,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 60934-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6493,14 +6508,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45653</v>
+        <v>45261</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6513,7 +6528,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6556,7 +6571,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 24636-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6566,14 +6581,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44776</v>
+        <v>45084</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6585,13 +6600,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6634,7 +6644,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6648,10 +6658,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45110</v>
+        <v>44904</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6664,7 +6674,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6707,7 +6717,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6721,10 +6731,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45110</v>
+        <v>44749</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6737,7 +6747,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6780,7 +6790,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6794,10 +6804,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45257</v>
+        <v>45713</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6811,11 +6821,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6858,7 +6868,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 2496-2024</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6868,14 +6878,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45313</v>
+        <v>44502</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6887,13 +6897,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>3.3</v>
+        <v>14.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6936,7 +6941,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6950,10 +6955,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45533</v>
+        <v>45251</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6966,7 +6971,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7009,7 +7014,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7023,10 +7028,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44803</v>
+        <v>44989</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7039,7 +7044,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.1</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7082,7 +7087,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7096,10 +7101,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44803</v>
+        <v>45461</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7112,7 +7117,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7155,7 +7160,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7165,14 +7170,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45700</v>
+        <v>45191</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7184,8 +7189,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7228,7 +7238,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7238,14 +7248,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44992</v>
+        <v>44571</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7258,7 +7268,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7301,7 +7311,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 60922-2023</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7315,10 +7325,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45261</v>
+        <v>44827</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7330,8 +7340,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>7.6</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7374,7 +7389,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7388,10 +7403,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44642</v>
+        <v>45187</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7403,13 +7418,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7452,7 +7462,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7466,10 +7476,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44827</v>
+        <v>44894</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7481,13 +7491,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7530,7 +7535,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7544,10 +7549,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45540</v>
+        <v>44803</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7560,7 +7565,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7603,7 +7608,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 28681-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7617,10 +7622,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45162</v>
+        <v>45819</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7633,7 +7638,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>7.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7676,7 +7681,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7690,10 +7695,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46275</v>
+        <v>44642</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7705,8 +7710,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7749,7 +7759,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7759,14 +7769,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44776</v>
+        <v>45940</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7778,13 +7788,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7827,7 +7832,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7841,10 +7846,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46275</v>
+        <v>45930</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7857,7 +7862,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7900,7 +7905,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 60949-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7914,10 +7919,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45644</v>
+        <v>45996</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7930,7 +7935,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.2</v>
+        <v>21.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7973,7 +7978,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 38695-2026</t>
+          <t>A 3673-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7987,10 +7992,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46283</v>
+        <v>46043</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8003,7 +8008,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8046,7 +8051,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8060,10 +8065,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45713</v>
+        <v>46048</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8075,13 +8080,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>9.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8124,7 +8124,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8138,10 +8138,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45461</v>
+        <v>46086</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8197,7 +8197,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8211,10 +8211,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45567</v>
+        <v>46097</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8270,7 +8270,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8280,14 +8280,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45461</v>
+        <v>45363</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>12.5</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 3890-2025</t>
+          <t>A 22913-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45684</v>
+        <v>46159</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8372,8 +8372,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8416,7 +8421,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21513-2025</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8430,10 +8435,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45782</v>
+        <v>45110</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8446,7 +8451,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8489,7 +8494,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48375-2024</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8503,10 +8508,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45590</v>
+        <v>45110</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8518,13 +8523,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8567,7 +8567,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 22402-2025</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8581,10 +8581,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45786</v>
+        <v>46275</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8640,7 +8640,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 35961-2024</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8654,10 +8654,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45533</v>
+        <v>46275</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8713,7 +8713,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 19031-2024</t>
+          <t>A 38695-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8723,14 +8723,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45427</v>
+        <v>46283</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 40643-2024</t>
+          <t>A 41957-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2043,14 +2043,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45558</v>
+        <v>45903</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2099,374 +2099,374 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Gröngöling
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 40643-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45558</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Bergsslok
 Getrams</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 22874-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 22874-2026 artfynd.xlsx", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 22874-2026 karta.png", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 22874-2026 georefererad karta.tif", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 22874-2026 FSC-klagomål.docx", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 22874-2026 FSC-klagomål mail.docx", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 22874-2026 tillsynsbegäran.docx", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 22874-2026 tillsynsbegäran mail.docx", "A 22874-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 64345-2023</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D16" s="1" t="n">
         <v>45280</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>2.7</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T16" t="n">
         <v>3</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U16" t="n">
         <v>3</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 64345-2023 artfynd.xlsx", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 64345-2023 karta.png", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 64345-2023 georefererad karta.tif", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 64345-2023 FSC-klagomål.docx", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 64345-2023 FSC-klagomål mail.docx", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 64345-2023 tillsynsbegäran.docx", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 64345-2023 tillsynsbegäran mail.docx", "A 64345-2023")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 64345-2023 prioriterade fågelarter.docx", "A 64345-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 41957-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45903</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Gröngöling
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 22874-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46156</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Kandelabersvamp
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 22874-2026 artfynd.xlsx", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 22874-2026 karta.png", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 22874-2026 georefererad karta.tif", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 22874-2026 FSC-klagomål.docx", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 22874-2026 FSC-klagomål mail.docx", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 22874-2026 tillsynsbegäran.docx", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 22874-2026 tillsynsbegäran mail.docx", "A 22874-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 39716-2023</t>
+          <t>A 15452-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2476,14 +2476,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45166</v>
+        <v>45020</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2495,8 +2495,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2511,7 +2516,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2520,10 +2525,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2532,50 +2537,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33751-2024</t>
+          <t>A 6893-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2585,14 +2590,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45520</v>
+        <v>46057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,25 +2609,20 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2637,52 +2637,48 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
     </row>
@@ -2706,7 +2702,7 @@
         <v>45198</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2798,7 +2794,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15452-2023</t>
+          <t>A 33751-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2812,10 +2808,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45020</v>
+        <v>45520</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2833,7 +2829,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2845,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2857,62 +2853,62 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 6893-2026</t>
+          <t>A 39716-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2926,10 +2922,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46057</v>
+        <v>45166</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2942,22 +2938,22 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2969,7 +2965,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2982,35 +2978,39 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
         <v/>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
         <v>44618</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 9767-2022</t>
+          <t>A 31697-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3100,14 +3100,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44619</v>
+        <v>44776</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3119,8 +3119,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3163,7 +3168,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31697-2022</t>
+          <t>A 9767-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3173,14 +3178,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44776</v>
+        <v>44619</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3192,13 +3197,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3258,7 +3258,7 @@
         <v>44515</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 55112-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45089</v>
+        <v>44474</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3346,11 +3346,6 @@
       <c r="G26" t="inlineStr">
         <is>
           <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -3397,7 +3392,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 55112-2021</t>
+          <t>A 49592-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3411,10 +3406,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44474</v>
+        <v>45211</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3427,7 +3422,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3470,7 +3465,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3484,10 +3479,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45261</v>
+        <v>45251</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3500,7 +3495,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3543,7 +3538,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3553,14 +3548,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44557</v>
+        <v>45330</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3573,7 +3568,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3616,7 +3611,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 49592-2023</t>
+          <t>A 60949-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3630,10 +3625,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45211</v>
+        <v>45996</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3646,7 +3641,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>21.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3689,7 +3684,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60922-2023</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3703,10 +3698,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45261</v>
+        <v>44904</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3719,7 +3714,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7.6</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3762,7 +3757,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 24105-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3772,14 +3767,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45653</v>
+        <v>45796</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3792,7 +3787,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3835,7 +3830,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 3673-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3849,10 +3844,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45478</v>
+        <v>46043</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3865,7 +3860,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3908,7 +3903,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3922,10 +3917,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45162</v>
+        <v>46048</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3938,7 +3933,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3981,7 +3976,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 41702-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3995,10 +3990,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44606</v>
+        <v>45176</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4010,8 +4005,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 60934-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45054</v>
+        <v>45261</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44992</v>
+        <v>45160</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>18.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4200,7 +4200,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45089</v>
+        <v>45575</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4229,13 +4229,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4278,7 +4273,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4292,10 +4287,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45644</v>
+        <v>45054</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4308,7 +4303,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4351,7 +4346,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4361,14 +4356,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45700</v>
+        <v>45930</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4381,7 +4376,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4424,7 +4419,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 41702-2023</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4438,10 +4433,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45176</v>
+        <v>45222</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4453,13 +4448,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4502,7 +4492,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4516,10 +4506,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45160</v>
+        <v>44904</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4532,7 +4522,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>18.1</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4575,7 +4565,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2496-2024</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4589,10 +4579,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45313</v>
+        <v>45940</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4604,13 +4594,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4653,7 +4638,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4667,10 +4652,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44904</v>
+        <v>46086</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4683,7 +4668,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4726,7 +4711,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4740,10 +4725,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44803</v>
+        <v>45061</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4756,7 +4741,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.1</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4799,7 +4784,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4809,14 +4794,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44546</v>
+        <v>44749</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4829,7 +4814,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4872,7 +4857,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4882,14 +4867,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44678</v>
+        <v>46097</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4902,7 +4887,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4945,7 +4930,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 42572-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4959,10 +4944,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45222</v>
+        <v>45565</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4975,7 +4960,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5018,7 +5003,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 42572-2024</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5032,10 +5017,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45565</v>
+        <v>44894</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5048,7 +5033,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>5.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5091,7 +5076,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5101,14 +5086,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44776</v>
+        <v>44989</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5120,13 +5105,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5169,7 +5149,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5183,10 +5163,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45533</v>
+        <v>45089</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5198,8 +5178,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5242,7 +5227,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5256,10 +5241,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45575</v>
+        <v>45089</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5271,8 +5256,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5315,7 +5305,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5325,14 +5315,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45257</v>
+        <v>44502</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5344,13 +5334,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>14.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5393,7 +5378,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3890-2025</t>
+          <t>A 28681-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5407,10 +5392,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45684</v>
+        <v>45819</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5423,7 +5408,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.9</v>
+        <v>7.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5466,7 +5451,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5476,14 +5461,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45567</v>
+        <v>45363</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5496,7 +5481,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5539,7 +5524,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5553,10 +5538,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45461</v>
+        <v>45261</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5569,7 +5554,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>12.5</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5612,7 +5597,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 21513-2025</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5626,10 +5611,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45782</v>
+        <v>45061</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5642,7 +5627,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5685,7 +5670,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5699,10 +5684,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45061</v>
+        <v>45187</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5715,7 +5700,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5758,7 +5743,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 19031-2024</t>
+          <t>A 22913-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5768,14 +5753,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45427</v>
+        <v>46159</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5787,8 +5772,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5831,7 +5821,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35961-2024</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5841,14 +5831,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45533</v>
+        <v>44546</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5861,7 +5851,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5904,7 +5894,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22402-2025</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5918,10 +5908,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45786</v>
+        <v>44557</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5934,7 +5924,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5977,7 +5967,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48375-2024</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5991,10 +5981,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45590</v>
+        <v>45035</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6006,13 +5996,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6055,7 +6040,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6065,14 +6050,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44776</v>
+        <v>45110</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6084,13 +6069,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6133,7 +6113,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6147,10 +6127,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45035</v>
+        <v>44606</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6163,7 +6143,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6206,7 +6186,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 24105-2025</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6220,10 +6200,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45796</v>
+        <v>45191</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6235,8 +6215,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6279,7 +6264,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6293,10 +6278,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45540</v>
+        <v>45110</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6309,7 +6294,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6352,7 +6337,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6366,10 +6351,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45330</v>
+        <v>44678</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6382,7 +6367,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6425,7 +6410,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6439,10 +6424,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45061</v>
+        <v>45478</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6455,7 +6440,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6498,7 +6483,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 60934-2023</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6508,14 +6493,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45261</v>
+        <v>44571</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6528,7 +6513,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6588,7 +6573,7 @@
         <v>45084</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6644,7 +6629,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6654,14 +6639,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44904</v>
+        <v>45653</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6674,7 +6659,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6717,7 +6702,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6727,14 +6712,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44749</v>
+        <v>44776</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6746,8 +6731,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6790,7 +6780,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6804,10 +6794,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45713</v>
+        <v>45257</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6821,11 +6811,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>9.699999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6868,7 +6858,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 2496-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6878,14 +6868,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44502</v>
+        <v>45313</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6897,8 +6887,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>14.7</v>
+        <v>3.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6941,7 +6936,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6955,10 +6950,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45251</v>
+        <v>45533</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6971,7 +6966,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7014,7 +7009,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7028,10 +7023,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44989</v>
+        <v>44803</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7044,7 +7039,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7087,7 +7082,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7101,10 +7096,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45461</v>
+        <v>44803</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7117,7 +7112,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7160,7 +7155,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7170,14 +7165,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45191</v>
+        <v>45700</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7189,13 +7184,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7238,7 +7228,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7248,14 +7238,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44571</v>
+        <v>46275</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7268,7 +7258,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7311,7 +7301,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7325,10 +7315,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44827</v>
+        <v>46275</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7340,13 +7330,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7389,7 +7374,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7403,10 +7388,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45187</v>
+        <v>44992</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7419,7 +7404,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7462,7 +7447,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 60922-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7476,10 +7461,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44894</v>
+        <v>45261</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7492,7 +7477,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7535,7 +7520,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 38695-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7549,10 +7534,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44803</v>
+        <v>46283</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7565,7 +7550,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7608,7 +7593,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 28681-2025</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7622,10 +7607,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45819</v>
+        <v>44642</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7637,8 +7622,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>7.5</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7681,7 +7671,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7695,10 +7685,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44642</v>
+        <v>44827</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7712,11 +7702,11 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7759,7 +7749,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7773,10 +7763,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45940</v>
+        <v>45540</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7789,7 +7779,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7832,7 +7822,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7846,10 +7836,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45930</v>
+        <v>45162</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7862,7 +7852,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7905,7 +7895,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60949-2025</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7915,14 +7905,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45996</v>
+        <v>44776</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7934,8 +7924,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>21.9</v>
+        <v>2.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7978,7 +7973,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 3673-2026</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7992,10 +7987,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46043</v>
+        <v>45644</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8008,7 +8003,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8051,7 +8046,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8065,10 +8060,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46048</v>
+        <v>45713</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8080,8 +8075,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8124,7 +8124,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8138,10 +8138,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46086</v>
+        <v>45461</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8197,7 +8197,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8211,10 +8211,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46097</v>
+        <v>45567</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8270,7 +8270,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8280,14 +8280,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45363</v>
+        <v>45461</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.3</v>
+        <v>12.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 22913-2026</t>
+          <t>A 3890-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46159</v>
+        <v>45684</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8372,13 +8372,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8421,7 +8416,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 21513-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8435,10 +8430,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45110</v>
+        <v>45782</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8451,7 +8446,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8494,7 +8489,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 48375-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8508,10 +8503,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45110</v>
+        <v>45590</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8523,8 +8518,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8567,7 +8567,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 22402-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8581,10 +8581,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46275</v>
+        <v>45786</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8640,7 +8640,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 35961-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8654,10 +8654,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46275</v>
+        <v>45533</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8713,7 +8713,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 38695-2026</t>
+          <t>A 19031-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8723,14 +8723,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46283</v>
+        <v>45427</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41957-2025</t>
+          <t>A 40643-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2043,14 +2043,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45903</v>
+        <v>45558</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2099,146 +2099,146 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Bergsslok
+Getrams</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 41957-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45903</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Gröngöling
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 40643-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45558</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Bergsslok
-Getrams</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
         <v/>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
         <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45020</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>46057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 46757-2023</t>
+          <t>A 39716-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2695,14 +2695,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45198</v>
+        <v>45166</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2724,13 +2724,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2742,7 +2742,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2755,39 +2755,39 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
         <v/>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         <v>45520</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 39716-2023</t>
+          <t>A 46757-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2918,14 +2918,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45166</v>
+        <v>45198</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2947,13 +2947,13 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,7 +2965,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2978,39 +2978,39 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
         <v/>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
         <v>44618</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>44776</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>44619</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>44515</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>44474</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45211</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45251</v>
+        <v>45089</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3494,8 +3494,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3538,7 +3543,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3552,10 +3557,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45330</v>
+        <v>45700</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3568,7 +3573,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3611,7 +3616,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60949-2025</t>
+          <t>A 22402-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3625,10 +3630,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45996</v>
+        <v>45786</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3641,7 +3646,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>21.9</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3684,7 +3689,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 48375-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3698,10 +3703,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44904</v>
+        <v>45590</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3713,8 +3718,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3757,7 +3767,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 24105-2025</t>
+          <t>A 60949-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3771,10 +3781,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45796</v>
+        <v>45996</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3787,7 +3797,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>21.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3830,7 +3840,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3673-2026</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3844,10 +3854,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46043</v>
+        <v>45540</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3860,7 +3870,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3903,7 +3913,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 24636-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3917,10 +3927,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46048</v>
+        <v>45084</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3933,7 +3943,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3976,7 +3986,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 41702-2023</t>
+          <t>A 3673-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3990,10 +4000,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45176</v>
+        <v>46043</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4005,13 +4015,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4054,7 +4059,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60934-2023</t>
+          <t>A 24105-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4068,10 +4073,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45261</v>
+        <v>45796</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4084,7 +4089,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4127,7 +4132,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 60934-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4141,10 +4146,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45160</v>
+        <v>45261</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4157,7 +4162,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>18.1</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4200,7 +4205,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4214,10 +4219,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45575</v>
+        <v>44989</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4273,7 +4278,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4287,10 +4292,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45054</v>
+        <v>46048</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4303,7 +4308,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4346,7 +4351,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4360,10 +4365,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45930</v>
+        <v>45461</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4376,7 +4381,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4419,7 +4424,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4429,14 +4434,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45222</v>
+        <v>44571</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4449,7 +4454,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4492,7 +4497,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4506,10 +4511,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44904</v>
+        <v>44827</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4521,8 +4526,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4565,7 +4575,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4579,10 +4589,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45940</v>
+        <v>45930</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4595,7 +4605,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4638,7 +4648,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4652,10 +4662,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46086</v>
+        <v>45940</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4668,7 +4678,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4711,7 +4721,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4725,10 +4735,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45061</v>
+        <v>44642</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4740,8 +4750,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4784,7 +4799,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4798,10 +4813,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44749</v>
+        <v>44557</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4814,7 +4829,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4857,7 +4872,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4871,10 +4886,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46097</v>
+        <v>46086</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4887,7 +4902,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4930,7 +4945,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 42572-2024</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4944,10 +4959,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45565</v>
+        <v>46097</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4960,7 +4975,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5003,7 +5018,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5017,10 +5032,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44894</v>
+        <v>45478</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5033,7 +5048,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5076,7 +5091,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 41702-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5090,10 +5105,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44989</v>
+        <v>45176</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5105,8 +5120,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5149,7 +5169,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5163,10 +5183,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45089</v>
+        <v>44803</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5178,13 +5198,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5227,7 +5242,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5237,14 +5252,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45089</v>
+        <v>44678</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5256,13 +5271,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5305,7 +5315,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 42572-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5315,14 +5325,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44502</v>
+        <v>45565</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5335,7 +5345,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>14.7</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5378,7 +5388,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 28681-2025</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5392,10 +5402,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45819</v>
+        <v>45575</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5408,7 +5418,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5451,7 +5461,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5461,14 +5471,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45363</v>
+        <v>45257</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5480,8 +5490,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5524,7 +5539,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 28681-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5538,10 +5553,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45261</v>
+        <v>45819</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5554,7 +5569,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>7.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5597,7 +5612,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5607,14 +5622,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45061</v>
+        <v>44776</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5626,8 +5641,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5670,7 +5690,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5684,10 +5704,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45187</v>
+        <v>45035</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5700,7 +5720,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5743,7 +5763,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 22913-2026</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5753,14 +5773,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46159</v>
+        <v>45330</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5772,13 +5792,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5821,7 +5836,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5831,14 +5846,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44546</v>
+        <v>45061</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5851,7 +5866,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5894,7 +5909,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5908,10 +5923,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44557</v>
+        <v>44904</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5924,7 +5939,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5967,7 +5982,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5981,10 +5996,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45035</v>
+        <v>44749</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5997,7 +6012,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6040,7 +6055,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6054,10 +6069,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45110</v>
+        <v>45713</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6069,8 +6084,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6113,7 +6133,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6123,14 +6143,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44606</v>
+        <v>44502</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6143,7 +6163,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>14.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6186,7 +6206,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6196,14 +6216,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45191</v>
+        <v>45363</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6215,13 +6235,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6264,7 +6279,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6278,10 +6293,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45110</v>
+        <v>45191</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6293,8 +6308,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6337,7 +6357,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 22913-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6347,14 +6367,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44678</v>
+        <v>46159</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6366,8 +6386,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6410,7 +6435,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6424,10 +6449,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45478</v>
+        <v>45110</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6440,7 +6465,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6483,7 +6508,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6493,14 +6518,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44571</v>
+        <v>45110</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6513,7 +6538,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6556,7 +6581,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24636-2023</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6570,10 +6595,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45084</v>
+        <v>45261</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6586,7 +6611,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6629,7 +6654,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6639,14 +6664,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45653</v>
+        <v>45054</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6659,7 +6684,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6702,7 +6727,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6712,14 +6737,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44776</v>
+        <v>45160</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6731,13 +6756,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>18.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6780,7 +6800,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 2496-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6794,10 +6814,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45257</v>
+        <v>45313</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6811,11 +6831,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6858,7 +6878,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 2496-2024</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6872,10 +6892,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45313</v>
+        <v>44904</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6887,13 +6907,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6936,7 +6951,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6946,14 +6961,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45533</v>
+        <v>44546</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6966,7 +6981,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7009,7 +7024,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7023,10 +7038,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44803</v>
+        <v>45061</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7039,7 +7054,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.1</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7082,7 +7097,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7096,10 +7111,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44803</v>
+        <v>46275</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7112,7 +7127,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7155,7 +7170,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7165,14 +7180,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45700</v>
+        <v>46275</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7185,7 +7200,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7228,7 +7243,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 38695-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7242,10 +7257,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7258,7 +7273,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7301,7 +7316,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7315,10 +7330,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46275</v>
+        <v>45251</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7331,7 +7346,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7374,7 +7389,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7388,10 +7403,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44992</v>
+        <v>45187</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7404,7 +7419,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7447,7 +7462,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 60922-2023</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7461,10 +7476,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45261</v>
+        <v>44894</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7477,7 +7492,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7520,7 +7535,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 38695-2026</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7534,10 +7549,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46283</v>
+        <v>44803</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7550,7 +7565,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7593,7 +7608,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 60922-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7607,10 +7622,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44642</v>
+        <v>45261</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7622,13 +7637,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.8</v>
+        <v>7.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7671,7 +7681,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7681,14 +7691,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44827</v>
+        <v>45653</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7700,13 +7710,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7749,7 +7754,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7763,10 +7768,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45540</v>
+        <v>45162</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7779,7 +7784,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7822,7 +7827,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7836,10 +7841,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45162</v>
+        <v>44606</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7852,7 +7857,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7895,7 +7900,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7905,14 +7910,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44776</v>
+        <v>44992</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7924,13 +7929,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7973,7 +7973,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45644</v>
+        <v>45089</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8002,8 +8002,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8046,7 +8051,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8060,10 +8065,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45713</v>
+        <v>45644</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8075,13 +8080,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>9.699999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8124,7 +8124,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8138,10 +8138,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45461</v>
+        <v>45222</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8197,7 +8197,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8207,14 +8207,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45567</v>
+        <v>44776</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8226,8 +8226,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8270,7 +8275,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8284,10 +8289,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45461</v>
+        <v>45533</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8300,7 +8305,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>12.5</v>
+        <v>0.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8360,7 +8365,7 @@
         <v>45684</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8416,7 +8421,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21513-2025</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8430,10 +8435,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45782</v>
+        <v>45567</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8446,7 +8451,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8489,7 +8494,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48375-2024</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8503,10 +8508,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45590</v>
+        <v>45461</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8518,13 +8523,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>4.8</v>
+        <v>12.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8567,7 +8567,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 22402-2025</t>
+          <t>A 21513-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8581,10 +8581,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45786</v>
+        <v>45782</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8640,7 +8640,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 35961-2024</t>
+          <t>A 19031-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8650,14 +8650,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45533</v>
+        <v>45427</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8713,7 +8713,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 19031-2024</t>
+          <t>A 35961-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8723,14 +8723,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45427</v>
+        <v>45533</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>45558</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>45903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45020</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>46057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>45166</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>45520</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>45198</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44618</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>44776</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>44619</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>44515</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>44474</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45211</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>45089</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>45700</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45786</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>45590</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>45996</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>45540</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>45084</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>46043</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>45796</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>45261</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44989</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>46048</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>45461</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>44571</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>44827</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>45930</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>45940</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>44642</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>44557</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>46086</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>46097</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>45478</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>45176</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>44803</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>44678</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>45565</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>45575</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>45257</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>45819</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>44776</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>45035</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45330</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45061</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>44904</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44749</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45713</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>44502</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>45363</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>45191</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>46159</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>45110</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>45110</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>45261</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>45054</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>45160</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>45313</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>44904</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>44546</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>45061</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>46275</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>46275</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>46283</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>45251</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>45187</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>44894</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>44803</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>45261</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         <v>45653</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>45162</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>44606</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>44992</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>45089</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>45644</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>45222</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>44776</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>45533</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         <v>45684</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>45567</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>45461</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>45782</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>45427</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>45533</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>45558</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>45903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45020</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>46057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>45166</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>45520</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>45198</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44618</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>44776</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>44619</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>44515</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>44474</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45211</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>45089</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>45700</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45786</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>45590</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>45996</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>45540</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>45084</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>46043</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>45796</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>45261</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44989</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>46048</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>45461</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>44571</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>44827</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>45930</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>45940</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>44642</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>44557</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>46086</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>46097</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>45478</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>45176</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>44803</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>44678</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>45565</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>45575</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>45257</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>45819</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>44776</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>45035</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45330</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45061</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>44904</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44749</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45713</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>44502</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>45363</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>45191</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>46159</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>45110</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>45110</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>45261</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>45054</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>45160</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>45313</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>44904</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>44546</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>45061</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>46275</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>46275</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>46283</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>45251</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>45187</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>44894</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>44803</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>45261</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         <v>45653</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>45162</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>44606</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>44992</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>45089</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>45644</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>45222</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>44776</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>45533</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         <v>45684</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>45567</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>45461</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>45782</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>45427</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>45533</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE99"/>
+  <dimension ref="A1:AE97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 40643-2024</t>
+          <t>A 41957-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2043,14 +2043,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45558</v>
+        <v>45903</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2099,146 +2099,146 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Gröngöling
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 40643-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45558</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Bergsslok
 Getrams</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 41957-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45903</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Gröngöling
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
         <v/>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
         <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 15452-2023</t>
+          <t>A 6893-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2476,14 +2476,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45020</v>
+        <v>46057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2495,23 +2495,18 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2525,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2537,50 +2532,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 6893-2026</t>
+          <t>A 46757-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2590,14 +2581,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46057</v>
+        <v>45198</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2610,10 +2601,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2650,42 +2641,46 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 39716-2023</t>
+          <t>A 33751-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2695,14 +2690,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45166</v>
+        <v>45520</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2714,8 +2709,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2748,53 +2748,53 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33751-2024</t>
+          <t>A 39716-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2804,14 +2804,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45520</v>
+        <v>45166</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2823,13 +2823,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2841,10 +2836,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2862,53 +2857,53 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 46757-2023</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2918,14 +2913,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45198</v>
+        <v>46275</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2938,19 +2933,19 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2965,7 +2960,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2974,50 +2969,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svartfjällig musseron</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 37339-2026 artfynd.xlsx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 37339-2026 karta.png", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 37339-2026 georefererad karta.tif", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 37339-2026 FSC-klagomål.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 37339-2026 FSC-klagomål mail.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 37339-2026 tillsynsbegäran.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 37339-2026 tillsynsbegäran mail.docx", "A 37339-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 9750-2022</t>
+          <t>A 15452-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3027,14 +3018,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44618</v>
+        <v>45020</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3046,11 +3037,16 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>10.8</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -3077,20 +3073,56 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31697-2022</t>
+          <t>A 9750-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3100,14 +3132,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44776</v>
+        <v>44618</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3119,13 +3151,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>10.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3168,7 +3195,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9767-2022</t>
+          <t>A 31697-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3178,14 +3205,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44619</v>
+        <v>44776</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3197,8 +3224,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3241,7 +3273,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 65340-2021</t>
+          <t>A 9767-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3251,14 +3283,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44515</v>
+        <v>44619</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3270,13 +3302,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3319,7 +3346,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 55112-2021</t>
+          <t>A 65340-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3329,14 +3356,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44474</v>
+        <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3348,8 +3375,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3409,7 +3441,7 @@
         <v>45211</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3465,7 +3497,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3479,10 +3511,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45089</v>
+        <v>45251</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3494,13 +3526,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3543,7 +3570,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3557,10 +3584,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45700</v>
+        <v>45330</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3573,7 +3600,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3616,7 +3643,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22402-2025</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3630,10 +3657,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45786</v>
+        <v>44904</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3646,7 +3673,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3689,7 +3716,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 48375-2024</t>
+          <t>A 41702-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3703,10 +3730,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45590</v>
+        <v>45176</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3724,7 +3751,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3767,7 +3794,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60949-2025</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3781,10 +3808,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45996</v>
+        <v>45160</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3797,7 +3824,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>21.9</v>
+        <v>18.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3840,7 +3867,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3854,10 +3881,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45540</v>
+        <v>45575</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3870,7 +3897,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3913,7 +3940,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 24636-2023</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3927,10 +3954,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45084</v>
+        <v>45054</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3943,7 +3970,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4003,7 +4030,7 @@
         <v>46043</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4059,7 +4086,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 24105-2025</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4073,10 +4100,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45796</v>
+        <v>46048</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4089,7 +4116,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4132,7 +4159,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60934-2023</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4146,10 +4173,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45261</v>
+        <v>45222</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4162,7 +4189,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4205,7 +4232,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4219,10 +4246,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44989</v>
+        <v>44904</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4278,7 +4305,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4292,10 +4319,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46048</v>
+        <v>45061</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4308,7 +4335,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4351,7 +4378,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4365,10 +4392,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45461</v>
+        <v>44749</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4381,7 +4408,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4424,7 +4451,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 28681-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4434,14 +4461,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44571</v>
+        <v>45819</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4454,7 +4481,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4497,7 +4524,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4511,10 +4538,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44827</v>
+        <v>45930</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4526,13 +4553,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4575,7 +4597,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 42572-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4589,10 +4611,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45930</v>
+        <v>45565</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4605,7 +4627,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4648,7 +4670,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4662,10 +4684,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45940</v>
+        <v>44894</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4678,7 +4700,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4721,7 +4743,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4735,10 +4757,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44642</v>
+        <v>45940</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4750,13 +4772,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4799,7 +4816,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4813,10 +4830,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44557</v>
+        <v>46086</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4829,7 +4846,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4872,7 +4889,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4886,10 +4903,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46086</v>
+        <v>46097</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4902,7 +4919,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4945,7 +4962,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4959,10 +4976,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46097</v>
+        <v>44989</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4975,7 +4992,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5018,7 +5035,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5032,10 +5049,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45478</v>
+        <v>45089</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5047,8 +5064,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5091,7 +5113,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 41702-2023</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5105,10 +5127,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45176</v>
+        <v>45089</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5122,11 +5144,11 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5169,7 +5191,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5179,14 +5201,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44803</v>
+        <v>44502</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5199,7 +5221,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6.1</v>
+        <v>14.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5242,7 +5264,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5252,14 +5274,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44678</v>
+        <v>45261</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5272,7 +5294,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5315,7 +5337,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 42572-2024</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5329,10 +5351,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45565</v>
+        <v>45061</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5345,7 +5367,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5388,7 +5410,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5402,10 +5424,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45575</v>
+        <v>45187</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5418,7 +5440,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5461,7 +5483,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5471,14 +5493,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45257</v>
+        <v>44546</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5490,13 +5512,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5539,7 +5556,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 28681-2025</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5553,10 +5570,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45819</v>
+        <v>44557</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5569,7 +5586,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.5</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5612,7 +5629,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5622,14 +5639,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44776</v>
+        <v>45035</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5641,13 +5658,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5690,7 +5702,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5704,10 +5716,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45035</v>
+        <v>44606</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5720,7 +5732,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5763,7 +5775,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5773,14 +5785,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45330</v>
+        <v>45191</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5792,8 +5804,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5836,7 +5853,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5846,14 +5863,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45061</v>
+        <v>45363</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5866,7 +5883,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5909,7 +5926,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5919,14 +5936,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44904</v>
+        <v>44678</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5939,7 +5956,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5982,7 +5999,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 22913-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5996,10 +6013,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44749</v>
+        <v>46159</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6011,8 +6028,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6055,7 +6077,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6069,10 +6091,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45713</v>
+        <v>45478</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6084,13 +6106,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>9.699999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6133,7 +6150,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6147,10 +6164,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44502</v>
+        <v>44571</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6163,7 +6180,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>14.7</v>
+        <v>2.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6206,7 +6223,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6216,14 +6233,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45363</v>
+        <v>45110</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6236,7 +6253,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6279,7 +6296,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6293,10 +6310,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45191</v>
+        <v>45110</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6308,13 +6325,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6357,7 +6369,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 22913-2026</t>
+          <t>A 24636-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6371,10 +6383,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46159</v>
+        <v>45084</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6386,13 +6398,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6435,7 +6442,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6445,14 +6452,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45110</v>
+        <v>45653</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6465,7 +6472,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6508,7 +6515,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6518,14 +6525,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45110</v>
+        <v>44776</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6537,8 +6544,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6581,7 +6593,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6595,10 +6607,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45261</v>
+        <v>45257</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6610,8 +6622,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6654,7 +6671,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 2496-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6668,10 +6685,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45054</v>
+        <v>45313</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6683,8 +6700,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6727,7 +6749,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6741,10 +6763,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45160</v>
+        <v>45533</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6757,7 +6779,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>18.1</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6800,7 +6822,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 2496-2024</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6814,10 +6836,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45313</v>
+        <v>44803</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6829,13 +6851,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6878,7 +6895,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6892,10 +6909,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44904</v>
+        <v>44803</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6908,7 +6925,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6951,7 +6968,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6965,10 +6982,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44546</v>
+        <v>45700</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6981,7 +6998,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7024,7 +7041,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7038,10 +7055,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45061</v>
+        <v>44992</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7054,7 +7071,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7097,7 +7114,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 60922-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7111,10 +7128,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46275</v>
+        <v>45261</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7127,7 +7144,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>7.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7170,7 +7187,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7184,10 +7201,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46275</v>
+        <v>44642</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7199,8 +7216,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7243,7 +7265,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38695-2026</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7257,10 +7279,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46283</v>
+        <v>46275</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7273,7 +7295,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7316,7 +7338,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7330,10 +7352,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45251</v>
+        <v>44827</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7343,6 +7365,11 @@
       <c r="G80" t="inlineStr">
         <is>
           <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -7389,7 +7416,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7403,10 +7430,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45187</v>
+        <v>45540</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7419,7 +7446,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7462,7 +7489,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 38695-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7476,10 +7503,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44894</v>
+        <v>46283</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7492,7 +7519,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5.2</v>
+        <v>2.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7535,7 +7562,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7549,10 +7576,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44803</v>
+        <v>45162</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7565,7 +7592,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7608,7 +7635,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 60922-2023</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7618,14 +7645,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45261</v>
+        <v>44776</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7637,8 +7664,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7681,7 +7713,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7691,14 +7723,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45653</v>
+        <v>45644</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7711,7 +7743,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7754,7 +7786,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7768,10 +7800,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45162</v>
+        <v>45713</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7783,8 +7815,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7827,7 +7864,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7841,10 +7878,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44606</v>
+        <v>45461</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7857,7 +7894,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7900,7 +7937,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7914,10 +7951,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44992</v>
+        <v>45567</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7930,7 +7967,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7973,7 +8010,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7987,10 +8024,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45089</v>
+        <v>45461</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8002,13 +8039,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>12.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8051,7 +8083,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 3890-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8065,10 +8097,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45644</v>
+        <v>45684</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8081,7 +8113,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.2</v>
+        <v>2.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8124,7 +8156,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 21513-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8138,10 +8170,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45222</v>
+        <v>45782</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8154,7 +8186,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8197,7 +8229,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 48375-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8207,14 +8239,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44776</v>
+        <v>45590</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8228,11 +8260,11 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8275,7 +8307,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 22402-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8289,10 +8321,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45533</v>
+        <v>45786</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8305,7 +8337,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8348,7 +8380,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 3890-2025</t>
+          <t>A 35961-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8362,10 +8394,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45684</v>
+        <v>45533</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8378,7 +8410,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8421,7 +8453,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 19031-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8431,14 +8463,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45567</v>
+        <v>45427</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8451,7 +8483,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8494,7 +8526,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 24105-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8508,10 +8540,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45461</v>
+        <v>45796</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8524,7 +8556,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>12.5</v>
+        <v>3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8564,10 +8596,10 @@
       </c>
       <c r="V96" s="2" t="inlineStr"/>
     </row>
-    <row r="97" ht="15" customHeight="1">
+    <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 21513-2025</t>
+          <t>A 60934-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8581,10 +8613,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45782</v>
+        <v>45261</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8597,7 +8629,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8636,152 +8668,6 @@
         <v>0</v>
       </c>
       <c r="V97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98" ht="15" customHeight="1">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>A 19031-2024</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D98" s="1" t="n">
-        <v>45427</v>
-      </c>
-      <c r="E98" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I98" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J98" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
-      <c r="R98" t="n">
-        <v>0</v>
-      </c>
-      <c r="S98" t="n">
-        <v>0</v>
-      </c>
-      <c r="T98" t="n">
-        <v>0</v>
-      </c>
-      <c r="U98" t="n">
-        <v>0</v>
-      </c>
-      <c r="V98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>A 35961-2024</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="n">
-        <v>45533</v>
-      </c>
-      <c r="E99" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I99" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J99" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0</v>
-      </c>
-      <c r="S99" t="n">
-        <v>0</v>
-      </c>
-      <c r="T99" t="n">
-        <v>0</v>
-      </c>
-      <c r="U99" t="n">
-        <v>0</v>
-      </c>
-      <c r="V99" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41957-2025</t>
+          <t>A 40643-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2043,14 +2043,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45903</v>
+        <v>45558</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2099,146 +2099,146 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Bergsslok
+Getrams</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 41957-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45903</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Gröngöling
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 40643-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45558</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Bergsslok
-Getrams</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
         <v/>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
         <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>46057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46757-2023</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2581,14 +2581,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45198</v>
+        <v>46275</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2601,19 +2601,19 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2628,7 +2628,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2637,50 +2637,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svartfjällig musseron</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 37339-2026 artfynd.xlsx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 37339-2026 karta.png", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 37339-2026 georefererad karta.tif", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 37339-2026 FSC-klagomål.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 37339-2026 FSC-klagomål mail.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 37339-2026 tillsynsbegäran.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 37339-2026 tillsynsbegäran mail.docx", "A 37339-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33751-2024</t>
+          <t>A 39716-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2690,14 +2686,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45520</v>
+        <v>45166</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2709,13 +2705,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2727,10 +2718,10 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2748,53 +2739,53 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 39716-2023</t>
+          <t>A 33751-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2804,14 +2795,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45166</v>
+        <v>45520</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2823,8 +2814,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2836,10 +2832,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2857,53 +2853,53 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 46757-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2913,14 +2909,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46275</v>
+        <v>45198</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2933,19 +2929,19 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2960,7 +2956,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2969,39 +2965,43 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Svartfjällig musseron</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 37339-2026 artfynd.xlsx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 37339-2026 karta.png", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 37339-2026 georefererad karta.tif", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 37339-2026 FSC-klagomål.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 37339-2026 FSC-klagomål mail.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 37339-2026 tillsynsbegäran.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 37339-2026 tillsynsbegäran mail.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
         <v/>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
         <v>45020</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44618</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>44776</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44619</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 49592-2023</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45211</v>
+        <v>45089</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3453,8 +3453,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3497,7 +3502,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 49592-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3511,10 +3516,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45251</v>
+        <v>45211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3527,7 +3532,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3570,7 +3575,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3584,10 +3589,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45330</v>
+        <v>45700</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3600,7 +3605,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3643,7 +3648,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3657,10 +3662,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44904</v>
+        <v>45540</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3673,7 +3678,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3716,7 +3721,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 41702-2023</t>
+          <t>A 24636-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3730,10 +3735,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45176</v>
+        <v>45084</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3745,13 +3750,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45160</v>
+        <v>44989</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>18.1</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45575</v>
+        <v>45461</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3950,14 +3950,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45054</v>
+        <v>44571</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3673-2026</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46043</v>
+        <v>44827</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4042,8 +4042,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4086,7 +4091,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 3673-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4100,10 +4105,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46048</v>
+        <v>46043</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4116,7 +4121,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4159,7 +4164,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4173,10 +4178,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45222</v>
+        <v>46048</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4189,7 +4194,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4232,7 +4237,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4246,10 +4251,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44904</v>
+        <v>44642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4261,8 +4266,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4305,7 +4315,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4319,10 +4329,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45061</v>
+        <v>44557</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4335,7 +4345,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4378,7 +4388,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4392,10 +4402,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44749</v>
+        <v>46086</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4408,7 +4418,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4451,7 +4461,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 28681-2025</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4465,10 +4475,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45819</v>
+        <v>45930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4481,7 +4491,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>7.5</v>
+        <v>3.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4524,7 +4534,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4538,10 +4548,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45930</v>
+        <v>46097</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4554,7 +4564,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4597,7 +4607,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 42572-2024</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4611,10 +4621,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45565</v>
+        <v>45478</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4627,7 +4637,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4670,7 +4680,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4684,10 +4694,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44894</v>
+        <v>45940</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4700,7 +4710,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4743,7 +4753,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 41702-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4757,10 +4767,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45940</v>
+        <v>45176</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4772,8 +4782,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4816,7 +4831,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 28681-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4830,10 +4845,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46086</v>
+        <v>45819</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4846,7 +4861,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4889,7 +4904,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4903,10 +4918,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46097</v>
+        <v>44803</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4919,7 +4934,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4962,7 +4977,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4972,14 +4987,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44989</v>
+        <v>44678</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4992,7 +5007,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5035,7 +5050,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 42572-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5049,10 +5064,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45089</v>
+        <v>45565</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5064,13 +5079,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5113,7 +5123,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5127,10 +5137,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45089</v>
+        <v>45575</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5142,13 +5152,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5191,7 +5196,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5201,14 +5206,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44502</v>
+        <v>45257</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5220,8 +5225,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>14.7</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5264,7 +5274,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5274,14 +5284,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45261</v>
+        <v>45363</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5294,7 +5304,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5337,7 +5347,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 22913-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5351,10 +5361,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45061</v>
+        <v>46159</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5366,8 +5376,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5410,7 +5425,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5424,10 +5439,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45187</v>
+        <v>45110</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5440,7 +5455,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5483,7 +5498,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5493,14 +5508,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44546</v>
+        <v>45110</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5513,7 +5528,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5556,7 +5571,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5566,14 +5581,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44557</v>
+        <v>44776</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5583,6 +5598,11 @@
       <c r="G56" t="inlineStr">
         <is>
           <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -5646,7 +5666,7 @@
         <v>45035</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5702,7 +5722,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5712,14 +5732,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44606</v>
+        <v>45330</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5732,7 +5752,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5775,7 +5795,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5789,10 +5809,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45191</v>
+        <v>45061</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5804,13 +5824,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5853,7 +5868,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5863,14 +5878,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45363</v>
+        <v>44904</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5883,7 +5898,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5926,7 +5941,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5936,14 +5951,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44678</v>
+        <v>44749</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5956,7 +5971,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5999,7 +6014,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 22913-2026</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6013,10 +6028,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46159</v>
+        <v>45713</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6030,11 +6045,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6077,7 +6092,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6087,14 +6102,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45478</v>
+        <v>44502</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6107,7 +6122,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.7</v>
+        <v>14.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6150,7 +6165,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6160,14 +6175,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44571</v>
+        <v>45191</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6179,8 +6194,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6223,7 +6243,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6237,10 +6257,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45110</v>
+        <v>45261</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6253,7 +6273,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6296,7 +6316,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6310,10 +6330,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45110</v>
+        <v>45054</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6326,7 +6346,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6369,7 +6389,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 24636-2023</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6383,10 +6403,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45084</v>
+        <v>45160</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6399,7 +6419,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>18.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6442,7 +6462,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6452,14 +6472,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45653</v>
+        <v>46275</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6472,7 +6492,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6515,7 +6535,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 2496-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6525,14 +6545,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44776</v>
+        <v>45313</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6550,7 +6570,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6593,7 +6613,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6607,10 +6627,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45257</v>
+        <v>44904</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6622,13 +6642,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6671,7 +6686,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 2496-2024</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6681,14 +6696,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45313</v>
+        <v>44546</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6700,13 +6715,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6749,7 +6759,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 38695-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6763,10 +6773,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45533</v>
+        <v>46283</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6779,7 +6789,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6822,7 +6832,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6836,10 +6846,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44803</v>
+        <v>45061</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6852,7 +6862,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.1</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6895,7 +6905,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6909,10 +6919,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44803</v>
+        <v>45251</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6925,7 +6935,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6968,7 +6978,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6978,14 +6988,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45700</v>
+        <v>45187</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6998,7 +7008,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7041,7 +7051,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7055,10 +7065,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44992</v>
+        <v>44894</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7071,7 +7081,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7114,7 +7124,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 60922-2023</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7128,10 +7138,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45261</v>
+        <v>44803</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7144,7 +7154,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>7.6</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7187,7 +7197,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 60922-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7201,10 +7211,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44642</v>
+        <v>45261</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7216,13 +7226,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>7.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7265,7 +7270,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7275,14 +7280,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46275</v>
+        <v>45653</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7295,7 +7300,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7338,7 +7343,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7352,10 +7357,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44827</v>
+        <v>45162</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7367,13 +7372,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7430,10 +7430,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45540</v>
+        <v>44606</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7489,7 +7489,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 38695-2026</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7503,10 +7503,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46283</v>
+        <v>44992</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7562,7 +7562,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7576,10 +7576,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45162</v>
+        <v>45089</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7589,6 +7589,11 @@
       <c r="G83" t="inlineStr">
         <is>
           <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -7635,7 +7640,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7645,14 +7650,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44776</v>
+        <v>45644</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7664,13 +7669,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7713,7 +7713,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7727,10 +7727,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45644</v>
+        <v>45222</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7786,7 +7786,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7796,14 +7796,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45713</v>
+        <v>44776</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7817,11 +7817,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>9.699999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7864,7 +7864,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7878,10 +7878,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45461</v>
+        <v>45533</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7937,7 +7937,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 3890-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7951,10 +7951,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45567</v>
+        <v>45684</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8010,7 +8010,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8024,10 +8024,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45461</v>
+        <v>45567</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 3890-2025</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8097,10 +8097,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45684</v>
+        <v>45461</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.9</v>
+        <v>12.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
         <v>45782</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 48375-2024</t>
+          <t>A 19031-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8239,14 +8239,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45590</v>
+        <v>45427</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8258,13 +8258,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8307,7 +8302,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 22402-2025</t>
+          <t>A 35961-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8321,10 +8316,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45786</v>
+        <v>45533</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8337,7 +8332,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8380,7 +8375,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 35961-2024</t>
+          <t>A 22402-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8394,10 +8389,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45533</v>
+        <v>45786</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8410,7 +8405,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8453,7 +8448,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 19031-2024</t>
+          <t>A 48375-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8463,14 +8458,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45427</v>
+        <v>45590</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8482,8 +8477,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8543,7 +8543,7 @@
         <v>45796</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>45261</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 40643-2024</t>
+          <t>A 41957-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2043,14 +2043,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45558</v>
+        <v>45903</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2099,257 +2099,257 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Gröngöling
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 22874-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 22874-2026 artfynd.xlsx", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 22874-2026 karta.png", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 22874-2026 georefererad karta.tif", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 22874-2026 FSC-klagomål.docx", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 22874-2026 FSC-klagomål mail.docx", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 22874-2026 tillsynsbegäran.docx", "A 22874-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 22874-2026 tillsynsbegäran mail.docx", "A 22874-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 40643-2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45558</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Bergsslok
 Getrams</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 41957-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45903</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Gröngöling
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 22874-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46156</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Kandelabersvamp
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 22874-2026 artfynd.xlsx", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 22874-2026 karta.png", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 22874-2026 georefererad karta.tif", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 22874-2026 FSC-klagomål.docx", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 22874-2026 FSC-klagomål mail.docx", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 22874-2026 tillsynsbegäran.docx", "A 22874-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 22874-2026 tillsynsbegäran mail.docx", "A 22874-2026")</f>
         <v/>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6893-2026</t>
+          <t>A 46757-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2476,14 +2476,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46057</v>
+        <v>45198</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2536,42 +2536,46 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 15452-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2581,14 +2585,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46275</v>
+        <v>45020</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2600,11 +2604,16 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2613,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2625,10 +2634,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2641,42 +2650,46 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svartfjällig musseron</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 37339-2026 artfynd.xlsx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 37339-2026 karta.png", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 37339-2026 georefererad karta.tif", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 37339-2026 FSC-klagomål.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 37339-2026 FSC-klagomål mail.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 37339-2026 tillsynsbegäran.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 37339-2026 tillsynsbegäran mail.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 39716-2023</t>
+          <t>A 33751-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2686,14 +2699,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45166</v>
+        <v>45520</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2705,8 +2718,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2718,10 +2736,10 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2739,53 +2757,53 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33751-2024</t>
+          <t>A 39716-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2795,14 +2813,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45520</v>
+        <v>45166</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2814,13 +2832,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2832,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2853,53 +2866,53 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 46757-2023</t>
+          <t>A 6893-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2909,14 +2922,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45198</v>
+        <v>46057</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2929,10 +2942,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2969,46 +2982,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15452-2023</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3018,14 +3027,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45020</v>
+        <v>46275</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3037,26 +3046,21 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
@@ -3067,10 +3071,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3083,39 +3087,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svartfjällig musseron</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 37339-2026 artfynd.xlsx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 37339-2026 karta.png", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 37339-2026 georefererad karta.tif", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 37339-2026 FSC-klagomål.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 37339-2026 FSC-klagomål mail.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 37339-2026 tillsynsbegäran.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 37339-2026 tillsynsbegäran mail.docx", "A 37339-2026")</f>
         <v/>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
         <v>44618</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>44776</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44619</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 65340-2021</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3356,14 +3356,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44515</v>
+        <v>44989</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3375,13 +3375,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3424,7 +3419,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 65340-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3434,14 +3429,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45089</v>
+        <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3455,11 +3450,11 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3502,7 +3497,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 49592-2023</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3516,10 +3511,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45211</v>
+        <v>45089</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3531,8 +3526,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3585,14 +3585,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45700</v>
+        <v>45089</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3604,8 +3604,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3648,7 +3653,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3658,14 +3663,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45540</v>
+        <v>44502</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3683,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>14.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3721,7 +3726,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 24636-2023</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3735,10 +3740,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45084</v>
+        <v>45251</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3751,7 +3756,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3794,7 +3799,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 49592-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3808,10 +3813,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44989</v>
+        <v>45211</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3867,7 +3872,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3881,10 +3886,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45461</v>
+        <v>45567</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3897,7 +3902,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3940,7 +3945,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3950,14 +3955,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44571</v>
+        <v>45461</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3970,7 +3975,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>12.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4013,7 +4018,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 3890-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4027,10 +4032,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44827</v>
+        <v>45684</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4042,13 +4047,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4091,7 +4091,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3673-2026</t>
+          <t>A 21513-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46043</v>
+        <v>45782</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4174,14 +4174,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46048</v>
+        <v>45330</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4237,7 +4237,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 48375-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4251,10 +4251,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44642</v>
+        <v>45590</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4268,11 +4268,11 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 22402-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44557</v>
+        <v>45786</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 35961-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46086</v>
+        <v>45533</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45930</v>
+        <v>45261</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 19031-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4544,14 +4544,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46097</v>
+        <v>45427</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45478</v>
+        <v>45061</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 24105-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4694,10 +4694,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45940</v>
+        <v>45796</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4753,7 +4753,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 41702-2023</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4767,10 +4767,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45176</v>
+        <v>45187</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4782,13 +4782,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4831,7 +4826,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28681-2025</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4845,10 +4840,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45819</v>
+        <v>44904</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4861,7 +4856,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>7.5</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4904,7 +4899,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 60934-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4918,10 +4913,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44803</v>
+        <v>45261</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4934,7 +4929,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.1</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4977,7 +4972,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4991,10 +4986,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44678</v>
+        <v>44546</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5007,7 +5002,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5050,7 +5045,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 42572-2024</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5064,10 +5059,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45565</v>
+        <v>44557</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5080,7 +5075,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5123,7 +5118,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 41702-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5137,10 +5132,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45575</v>
+        <v>45176</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5152,8 +5147,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5196,7 +5196,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5210,10 +5210,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45257</v>
+        <v>45930</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5225,13 +5225,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5274,7 +5269,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5284,14 +5279,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45363</v>
+        <v>45035</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5347,7 +5342,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22913-2026</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5361,10 +5356,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46159</v>
+        <v>44606</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5376,13 +5371,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5425,7 +5415,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5439,10 +5429,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45110</v>
+        <v>45191</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5454,8 +5444,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5498,7 +5493,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5512,10 +5507,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45110</v>
+        <v>45940</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5528,7 +5523,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5571,7 +5566,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5581,14 +5576,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44776</v>
+        <v>45160</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5600,13 +5595,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>18.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5649,7 +5639,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5663,10 +5653,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45035</v>
+        <v>45575</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5679,7 +5669,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5722,7 +5712,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5732,14 +5722,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45330</v>
+        <v>45054</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5752,7 +5742,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5795,7 +5785,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5805,14 +5795,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45061</v>
+        <v>44678</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5825,7 +5815,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5868,7 +5858,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5882,10 +5872,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44904</v>
+        <v>45222</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5898,7 +5888,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5941,7 +5931,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 28681-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5955,10 +5945,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44749</v>
+        <v>45819</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5971,7 +5961,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>7.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6014,7 +6004,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6028,10 +6018,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45713</v>
+        <v>45478</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6043,13 +6033,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>9.699999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6092,7 +6077,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6102,14 +6087,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44502</v>
+        <v>44904</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6122,7 +6107,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>14.7</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6165,7 +6150,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6179,10 +6164,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45191</v>
+        <v>45061</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6194,13 +6179,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6243,7 +6223,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6257,10 +6237,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45261</v>
+        <v>44749</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6273,7 +6253,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6316,7 +6296,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6326,14 +6306,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45054</v>
+        <v>44571</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6346,7 +6326,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6389,7 +6369,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 24636-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6403,10 +6383,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45160</v>
+        <v>45084</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6419,7 +6399,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>18.1</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6462,7 +6442,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6472,14 +6452,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46275</v>
+        <v>45363</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6492,7 +6472,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6535,7 +6515,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 2496-2024</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6545,14 +6525,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45313</v>
+        <v>45653</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6564,13 +6544,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6613,7 +6588,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 42572-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6627,10 +6602,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44904</v>
+        <v>45565</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6643,7 +6618,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6686,7 +6661,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6696,14 +6671,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44546</v>
+        <v>44776</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6715,8 +6690,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6759,7 +6739,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 38695-2026</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6773,10 +6753,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46283</v>
+        <v>44894</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6789,7 +6769,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.3</v>
+        <v>5.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6832,7 +6812,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 22913-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6846,10 +6826,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45061</v>
+        <v>46159</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6861,8 +6841,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6905,7 +6890,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6919,10 +6904,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45251</v>
+        <v>45110</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6935,7 +6920,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6978,7 +6963,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6992,10 +6977,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45187</v>
+        <v>45257</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7007,8 +6992,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7051,7 +7041,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 2496-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7065,10 +7055,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44894</v>
+        <v>45313</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7080,8 +7070,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7124,7 +7119,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7138,10 +7133,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44803</v>
+        <v>45110</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7154,7 +7149,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7197,7 +7192,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60922-2023</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7211,10 +7206,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45261</v>
+        <v>45533</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7227,7 +7222,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>7.6</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7270,7 +7265,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7280,14 +7275,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45653</v>
+        <v>44803</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7300,7 +7295,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>6.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7343,7 +7338,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7357,10 +7352,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45162</v>
+        <v>44803</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7373,7 +7368,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7416,7 +7411,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7426,14 +7421,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44606</v>
+        <v>45700</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7446,7 +7441,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7489,7 +7484,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 3673-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7503,10 +7498,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44992</v>
+        <v>46043</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7519,7 +7514,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7562,7 +7557,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7576,10 +7571,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45089</v>
+        <v>46048</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7591,13 +7586,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7640,7 +7630,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7654,10 +7644,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45644</v>
+        <v>44992</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7670,7 +7660,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7713,7 +7703,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 60922-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7727,10 +7717,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45222</v>
+        <v>45261</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7743,7 +7733,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7786,7 +7776,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7796,14 +7786,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44776</v>
+        <v>46086</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7815,13 +7805,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7864,7 +7849,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7878,10 +7863,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45533</v>
+        <v>46097</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7894,7 +7879,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7937,7 +7922,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 3890-2025</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7951,10 +7936,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45684</v>
+        <v>44642</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7966,8 +7951,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8010,7 +8000,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8024,10 +8014,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45567</v>
+        <v>44827</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8039,8 +8029,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8083,7 +8078,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8097,10 +8092,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45461</v>
+        <v>45540</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8113,7 +8108,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>12.5</v>
+        <v>2.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8156,7 +8151,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 21513-2025</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8170,10 +8165,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45782</v>
+        <v>45162</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8186,7 +8181,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8229,7 +8224,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 19031-2024</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8239,14 +8234,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45427</v>
+        <v>44776</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8258,8 +8253,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8302,7 +8302,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 35961-2024</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45533</v>
+        <v>45644</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8375,7 +8375,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 22402-2025</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45786</v>
+        <v>45713</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8404,8 +8404,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>4.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8448,7 +8453,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 48375-2024</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8462,10 +8467,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45590</v>
+        <v>45461</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8477,13 +8482,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8526,7 +8526,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 24105-2025</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8540,10 +8540,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45796</v>
+        <v>46275</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8599,7 +8599,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 60934-2023</t>
+          <t>A 38695-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8613,10 +8613,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45261</v>
+        <v>46283</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41957-2025</t>
+          <t>A 40643-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2043,14 +2043,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45903</v>
+        <v>45558</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2099,257 +2099,257 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Bergsslok
+Getrams</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 41957-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45903</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Gröngöling
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 22874-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D15" s="1" t="n">
         <v>46156</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="E15" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I15" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Kandelabersvamp
 Blåsippa</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 22874-2026 artfynd.xlsx", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 22874-2026 karta.png", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 22874-2026 georefererad karta.tif", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 22874-2026 FSC-klagomål.docx", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 22874-2026 FSC-klagomål mail.docx", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 22874-2026 tillsynsbegäran.docx", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 22874-2026 tillsynsbegäran mail.docx", "A 22874-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 40643-2024</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45558</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Bergsslok
-Getrams</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
         <v/>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46757-2023</t>
+          <t>A 6893-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2476,14 +2476,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45198</v>
+        <v>46057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2536,46 +2536,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 15452-2023</t>
+          <t>A 39716-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2585,14 +2581,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45020</v>
+        <v>45166</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,13 +2600,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2625,7 +2616,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2634,10 +2625,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2646,50 +2637,50 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33751-2024</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2699,14 +2690,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45520</v>
+        <v>46275</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2718,16 +2709,11 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2757,53 +2743,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Svartfjällig musseron</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 37339-2026 artfynd.xlsx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 37339-2026 karta.png", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 37339-2026 georefererad karta.tif", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 37339-2026 FSC-klagomål.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 37339-2026 FSC-klagomål mail.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 37339-2026 tillsynsbegäran.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 37339-2026 tillsynsbegäran mail.docx", "A 37339-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 39716-2023</t>
+          <t>A 33751-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2813,14 +2795,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45166</v>
+        <v>45520</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2832,8 +2814,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2845,10 +2832,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2866,53 +2853,53 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 6893-2026</t>
+          <t>A 46757-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2922,14 +2909,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46057</v>
+        <v>45198</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2942,10 +2929,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2982,42 +2969,46 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 15452-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3027,14 +3018,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46275</v>
+        <v>45020</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3046,11 +3037,16 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -3059,7 +3055,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -3071,10 +3067,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3087,35 +3083,39 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Svartfjällig musseron</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 37339-2026 artfynd.xlsx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 37339-2026 karta.png", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 37339-2026 georefererad karta.tif", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 37339-2026 FSC-klagomål.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 37339-2026 FSC-klagomål mail.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 37339-2026 tillsynsbegäran.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 37339-2026 tillsynsbegäran mail.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
         <v/>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
         <v>44618</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>44776</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44619</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 65340-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3356,14 +3356,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44989</v>
+        <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3375,8 +3375,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3419,7 +3424,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 65340-2021</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3429,14 +3434,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44515</v>
+        <v>45089</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3450,11 +3455,11 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3497,7 +3502,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 49592-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3511,10 +3516,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45089</v>
+        <v>45211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3526,13 +3531,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3585,14 +3585,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45089</v>
+        <v>45700</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3604,13 +3604,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3653,7 +3648,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3663,14 +3658,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44502</v>
+        <v>45540</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3683,7 +3678,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>14.7</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3726,7 +3721,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 24636-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3740,10 +3735,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45251</v>
+        <v>45084</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3756,7 +3751,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3799,7 +3794,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 49592-2023</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3813,10 +3808,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45211</v>
+        <v>45461</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3829,7 +3824,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3872,7 +3867,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3886,10 +3881,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45567</v>
+        <v>44989</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3902,7 +3897,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3945,7 +3940,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3959,10 +3954,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45461</v>
+        <v>44827</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3974,8 +3969,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>12.5</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3890-2025</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4028,14 +4028,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45684</v>
+        <v>44571</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4091,7 +4091,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21513-2025</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45782</v>
+        <v>44642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4120,8 +4120,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4164,7 +4169,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4174,14 +4179,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45330</v>
+        <v>44557</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4194,7 +4199,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4237,7 +4242,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48375-2024</t>
+          <t>A 28681-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4251,10 +4256,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45590</v>
+        <v>45819</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4266,13 +4271,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22402-2025</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45786</v>
+        <v>46086</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 35961-2024</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45533</v>
+        <v>45478</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 41702-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45261</v>
+        <v>45176</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4490,8 +4490,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4534,7 +4539,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19031-2024</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4544,14 +4549,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45427</v>
+        <v>46097</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4564,7 +4569,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4607,7 +4612,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4621,10 +4626,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45061</v>
+        <v>44803</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4637,7 +4642,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.3</v>
+        <v>6.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4680,7 +4685,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 24105-2025</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4690,14 +4695,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45796</v>
+        <v>44678</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4710,7 +4715,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4753,7 +4758,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4767,10 +4772,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45187</v>
+        <v>45930</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4783,7 +4788,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4826,7 +4831,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 42572-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4840,10 +4845,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44904</v>
+        <v>45565</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4856,7 +4861,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4899,7 +4904,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 60934-2023</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4913,10 +4918,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45261</v>
+        <v>45575</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4929,7 +4934,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4972,7 +4977,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4982,14 +4987,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44546</v>
+        <v>45257</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5001,8 +5006,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5045,7 +5055,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5059,10 +5069,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44557</v>
+        <v>45940</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5075,7 +5085,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5118,7 +5128,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 41702-2023</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5128,14 +5138,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45176</v>
+        <v>44776</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5149,11 +5159,11 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5196,7 +5206,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5210,10 +5220,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45930</v>
+        <v>45035</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5226,7 +5236,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5269,7 +5279,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5279,14 +5289,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45035</v>
+        <v>45330</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5299,7 +5309,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5342,7 +5352,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5356,10 +5366,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44606</v>
+        <v>45061</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5372,7 +5382,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5415,7 +5425,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5429,10 +5439,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45191</v>
+        <v>44904</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5444,13 +5454,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5493,7 +5498,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5507,10 +5512,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45940</v>
+        <v>44749</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5523,7 +5528,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5566,7 +5571,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5580,10 +5585,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45160</v>
+        <v>45713</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5595,8 +5600,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>18.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5639,7 +5649,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5649,14 +5659,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45575</v>
+        <v>44502</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5669,7 +5679,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>14.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5712,7 +5722,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5726,10 +5736,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45054</v>
+        <v>45191</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5741,8 +5751,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5785,7 +5800,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 3673-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5795,14 +5810,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44678</v>
+        <v>46043</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5815,7 +5830,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5858,7 +5873,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5872,10 +5887,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45222</v>
+        <v>46048</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5888,7 +5903,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5931,7 +5946,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28681-2025</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5945,10 +5960,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45819</v>
+        <v>45261</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5961,7 +5976,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7.5</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6004,7 +6019,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6018,10 +6033,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45478</v>
+        <v>45054</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6034,7 +6049,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6077,7 +6092,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6087,14 +6102,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44904</v>
+        <v>45363</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6107,7 +6122,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6150,7 +6165,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6164,10 +6179,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45061</v>
+        <v>45160</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6180,7 +6195,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>18.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6223,7 +6238,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 2496-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6237,10 +6252,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44749</v>
+        <v>45313</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6252,8 +6267,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6296,7 +6316,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6306,14 +6326,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44571</v>
+        <v>44904</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6326,7 +6346,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6369,7 +6389,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 24636-2023</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6379,14 +6399,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45084</v>
+        <v>44546</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6399,7 +6419,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6442,7 +6462,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 22913-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6452,14 +6472,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45363</v>
+        <v>46159</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6471,8 +6491,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6515,7 +6540,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6525,14 +6550,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45653</v>
+        <v>45061</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6588,7 +6613,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 42572-2024</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6602,10 +6627,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45565</v>
+        <v>45110</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6618,7 +6643,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6661,7 +6686,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6671,14 +6696,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44776</v>
+        <v>45110</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6690,13 +6715,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6739,7 +6759,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6753,10 +6773,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44894</v>
+        <v>45251</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6769,7 +6789,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6812,7 +6832,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 22913-2026</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6826,10 +6846,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46159</v>
+        <v>45187</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6841,13 +6861,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6890,7 +6905,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6904,10 +6919,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45110</v>
+        <v>44894</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6920,7 +6935,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6963,7 +6978,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6977,10 +6992,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45257</v>
+        <v>44803</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6992,13 +7007,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7041,7 +7051,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 2496-2024</t>
+          <t>A 60922-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7055,10 +7065,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45313</v>
+        <v>45261</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7070,13 +7080,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>3.3</v>
+        <v>7.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7119,7 +7124,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7129,14 +7134,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45110</v>
+        <v>45653</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7149,7 +7154,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7192,7 +7197,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7206,10 +7211,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45533</v>
+        <v>45162</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7222,7 +7227,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7265,7 +7270,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7279,10 +7284,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44803</v>
+        <v>44606</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7295,7 +7300,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>6.1</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7338,7 +7343,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7352,10 +7357,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44803</v>
+        <v>44992</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7368,7 +7373,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7411,7 +7416,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7421,14 +7426,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45700</v>
+        <v>45089</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7440,8 +7445,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7484,7 +7494,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3673-2026</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7498,10 +7508,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46043</v>
+        <v>45644</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7514,7 +7524,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7557,7 +7567,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7571,10 +7581,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46048</v>
+        <v>45222</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7587,7 +7597,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7630,7 +7640,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7644,10 +7654,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44992</v>
+        <v>46275</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7660,7 +7670,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7703,7 +7713,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 60922-2023</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7713,14 +7723,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45261</v>
+        <v>44776</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7732,8 +7742,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7776,7 +7791,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7790,10 +7805,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46086</v>
+        <v>45533</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7806,7 +7821,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7849,7 +7864,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 3890-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7863,10 +7878,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46097</v>
+        <v>45684</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7879,7 +7894,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7922,7 +7937,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7936,10 +7951,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44642</v>
+        <v>45567</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7951,13 +7966,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8000,7 +8010,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8014,10 +8024,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44827</v>
+        <v>45461</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8029,13 +8039,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>12.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8078,7 +8083,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 21513-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8092,10 +8097,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45540</v>
+        <v>45782</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8108,7 +8113,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8151,7 +8156,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 38695-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8165,10 +8170,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45162</v>
+        <v>46283</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8181,7 +8186,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8224,7 +8229,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 19031-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8234,14 +8239,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44776</v>
+        <v>45427</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8253,13 +8258,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8302,7 +8302,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 35961-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45644</v>
+        <v>45533</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8375,7 +8375,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 22402-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45713</v>
+        <v>45786</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8404,13 +8404,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>9.699999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8453,7 +8448,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 48375-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8467,10 +8462,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45461</v>
+        <v>45590</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8482,8 +8477,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8526,7 +8526,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 24105-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8540,10 +8540,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46275</v>
+        <v>45796</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8599,7 +8599,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 38695-2026</t>
+          <t>A 60934-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8613,10 +8613,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46283</v>
+        <v>45261</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 40643-2024</t>
+          <t>A 41957-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2043,14 +2043,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45558</v>
+        <v>45903</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2099,153 +2099,153 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Gröngöling
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 40643-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45558</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Bergsslok
 Getrams</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 41957-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45903</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Gröngöling
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 22874-2026</t>
+          <t>A 64345-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2255,14 +2255,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46156</v>
+        <v>45280</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2274,16 +2274,11 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>9.199999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2313,160 +2308,165 @@
         <v>2</v>
       </c>
       <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 64345-2023 artfynd.xlsx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 64345-2023 karta.png", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 64345-2023 georefererad karta.tif", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 64345-2023 FSC-klagomål.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 64345-2023 FSC-klagomål mail.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 64345-2023 tillsynsbegäran.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 64345-2023 tillsynsbegäran mail.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 64345-2023 prioriterade fågelarter.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 22874-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Kandelabersvamp
 Blåsippa</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 22874-2026 artfynd.xlsx", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 22874-2026 karta.png", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 22874-2026 georefererad karta.tif", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 22874-2026 FSC-klagomål.docx", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 22874-2026 FSC-klagomål mail.docx", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 22874-2026 tillsynsbegäran.docx", "A 22874-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 22874-2026 tillsynsbegäran mail.docx", "A 22874-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 64345-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45280</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 64345-2023 artfynd.xlsx", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 64345-2023 karta.png", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 64345-2023 georefererad karta.tif", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 64345-2023 FSC-klagomål.docx", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 64345-2023 FSC-klagomål mail.docx", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 64345-2023 tillsynsbegäran.docx", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 64345-2023 tillsynsbegäran mail.docx", "A 64345-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 64345-2023 prioriterade fågelarter.docx", "A 64345-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6893-2026</t>
+          <t>A 33751-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2476,14 +2476,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46057</v>
+        <v>45520</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2495,20 +2495,25 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2523,48 +2528,52 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
         <v/>
       </c>
     </row>
@@ -2588,7 +2597,7 @@
         <v>45166</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2680,7 +2689,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 15452-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2690,14 +2699,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46275</v>
+        <v>45020</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2709,11 +2718,16 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2722,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2734,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2750,42 +2764,46 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Svartfjällig musseron</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 37339-2026 artfynd.xlsx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 37339-2026 karta.png", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 37339-2026 georefererad karta.tif", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 37339-2026 FSC-klagomål.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 37339-2026 FSC-klagomål mail.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 37339-2026 tillsynsbegäran.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 37339-2026 tillsynsbegäran mail.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33751-2024</t>
+          <t>A 46757-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2799,10 +2817,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45520</v>
+        <v>45198</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2814,13 +2832,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2829,10 +2842,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2847,59 +2860,59 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 46757-2023</t>
+          <t>A 6893-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2909,14 +2922,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45198</v>
+        <v>46057</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2929,10 +2942,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2969,46 +2982,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15452-2023</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3018,14 +3027,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45020</v>
+        <v>46275</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3037,26 +3046,21 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
@@ -3067,10 +3071,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3083,39 +3087,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svartfjällig musseron</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 37339-2026 artfynd.xlsx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 37339-2026 karta.png", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 37339-2026 georefererad karta.tif", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 37339-2026 FSC-klagomål.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 37339-2026 FSC-klagomål mail.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 37339-2026 tillsynsbegäran.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 37339-2026 tillsynsbegäran mail.docx", "A 37339-2026")</f>
         <v/>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
         <v>44618</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31697-2022</t>
+          <t>A 9767-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3205,14 +3205,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44776</v>
+        <v>44619</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3224,13 +3224,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3273,7 +3268,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9767-2022</t>
+          <t>A 31697-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3283,14 +3278,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44619</v>
+        <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3302,8 +3297,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3434,14 +3434,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45089</v>
+        <v>45330</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3453,13 +3453,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3502,7 +3497,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 49592-2023</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3516,10 +3511,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45211</v>
+        <v>45540</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3527,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3575,7 +3570,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3585,14 +3580,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45700</v>
+        <v>45061</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3600,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3648,7 +3643,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3662,10 +3657,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45540</v>
+        <v>45162</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3673,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3721,7 +3716,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 24636-2023</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3735,10 +3730,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45084</v>
+        <v>45251</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3751,7 +3746,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3794,7 +3789,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3804,14 +3799,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45461</v>
+        <v>44776</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3823,8 +3818,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44989</v>
+        <v>45187</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 49592-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44827</v>
+        <v>45211</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3969,13 +3969,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4018,7 +4013,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4032,10 +4027,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44571</v>
+        <v>44546</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4048,7 +4043,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4091,7 +4086,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4105,10 +4100,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44642</v>
+        <v>44904</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4120,13 +4115,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4169,7 +4159,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4183,10 +4173,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44557</v>
+        <v>45644</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4199,7 +4189,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4242,7 +4232,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28681-2025</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4256,10 +4246,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45819</v>
+        <v>45713</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4271,8 +4261,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>7.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4315,7 +4310,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4329,10 +4324,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46086</v>
+        <v>44557</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4345,7 +4340,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4388,7 +4383,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4402,10 +4397,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45478</v>
+        <v>45461</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4418,7 +4413,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4478,7 +4473,7 @@
         <v>45176</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4539,7 +4534,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4553,10 +4548,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46097</v>
+        <v>45035</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4569,7 +4564,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4612,7 +4607,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4626,10 +4621,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44803</v>
+        <v>45567</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4642,7 +4637,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4685,7 +4680,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4695,14 +4690,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44678</v>
+        <v>45461</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4715,7 +4710,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.6</v>
+        <v>12.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4758,7 +4753,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 3890-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4772,10 +4767,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45930</v>
+        <v>45684</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4788,7 +4783,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4831,7 +4826,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 42572-2024</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4845,10 +4840,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45565</v>
+        <v>44606</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4861,7 +4856,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4904,7 +4899,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4918,10 +4913,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45575</v>
+        <v>45191</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4933,8 +4928,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4977,7 +4977,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45257</v>
+        <v>45160</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5006,13 +5006,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>18.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5055,7 +5050,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5069,10 +5064,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45940</v>
+        <v>45575</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5128,7 +5123,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 21513-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5138,14 +5133,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44776</v>
+        <v>45782</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5157,13 +5152,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5206,7 +5196,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5220,10 +5210,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45035</v>
+        <v>45054</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5236,7 +5226,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5279,7 +5269,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 48375-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5289,14 +5279,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45330</v>
+        <v>45590</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5308,8 +5298,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5352,7 +5347,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 22402-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5366,10 +5361,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45061</v>
+        <v>45786</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5382,7 +5377,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.3</v>
+        <v>4.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5425,7 +5420,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 35961-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5439,10 +5434,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44904</v>
+        <v>45533</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5455,7 +5450,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5498,7 +5493,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 19031-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5508,14 +5503,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44749</v>
+        <v>45427</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5528,7 +5523,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5571,7 +5566,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5585,10 +5580,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45713</v>
+        <v>45222</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5600,13 +5595,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>9.699999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5649,7 +5639,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5659,14 +5649,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44502</v>
+        <v>44904</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5679,7 +5669,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>14.7</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5722,7 +5712,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5732,14 +5722,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45191</v>
+        <v>44678</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5751,13 +5741,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5800,7 +5785,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3673-2026</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5814,10 +5799,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46043</v>
+        <v>45930</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5830,7 +5815,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5873,7 +5858,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 24105-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5887,10 +5872,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46048</v>
+        <v>45796</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5903,7 +5888,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5946,7 +5931,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5960,10 +5945,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45261</v>
+        <v>45478</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5976,7 +5961,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6019,7 +6004,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6033,10 +6018,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45054</v>
+        <v>45061</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6049,7 +6034,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6092,7 +6077,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6102,14 +6087,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45363</v>
+        <v>44749</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6122,7 +6107,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6165,7 +6150,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 60934-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6179,10 +6164,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45160</v>
+        <v>45261</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6195,7 +6180,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>18.1</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6238,7 +6223,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 2496-2024</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6248,14 +6233,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45313</v>
+        <v>44571</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6267,13 +6252,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6316,7 +6296,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6330,10 +6310,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44904</v>
+        <v>45940</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6346,7 +6326,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6389,7 +6369,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 24636-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6399,14 +6379,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44546</v>
+        <v>45084</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6419,7 +6399,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6462,7 +6442,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 22913-2026</t>
+          <t>A 42572-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6476,10 +6456,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46159</v>
+        <v>45565</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6491,13 +6471,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6540,7 +6515,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6550,14 +6525,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45061</v>
+        <v>45653</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6613,7 +6588,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6627,10 +6602,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45110</v>
+        <v>44894</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6643,7 +6618,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6686,7 +6661,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6696,14 +6671,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45110</v>
+        <v>44776</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6715,8 +6690,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6759,7 +6739,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 28681-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6773,10 +6753,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45251</v>
+        <v>45819</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6789,7 +6769,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>7.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6832,7 +6812,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6846,10 +6826,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45187</v>
+        <v>45257</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6861,8 +6841,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6905,7 +6890,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6919,10 +6904,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44894</v>
+        <v>44989</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6935,7 +6920,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6978,7 +6963,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6992,10 +6977,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44803</v>
+        <v>45089</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7007,8 +6992,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7051,7 +7041,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60922-2023</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7065,10 +7055,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45261</v>
+        <v>45089</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7080,8 +7070,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>7.6</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7124,7 +7119,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7138,10 +7133,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45653</v>
+        <v>44502</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7154,7 +7149,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>14.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7197,7 +7192,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 2496-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7211,10 +7206,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45162</v>
+        <v>45313</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7226,8 +7221,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7270,7 +7270,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7284,10 +7284,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44606</v>
+        <v>45533</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7343,7 +7343,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7357,10 +7357,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44992</v>
+        <v>44803</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7430,10 +7430,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45089</v>
+        <v>44803</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7445,13 +7445,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7494,7 +7489,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7504,14 +7499,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45644</v>
+        <v>45700</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7524,7 +7519,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7567,7 +7562,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7581,10 +7576,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45222</v>
+        <v>45261</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7597,7 +7592,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7640,7 +7635,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7654,10 +7649,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46275</v>
+        <v>44992</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7670,7 +7665,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7713,7 +7708,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 60922-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7723,14 +7718,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44776</v>
+        <v>45261</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7742,13 +7737,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2.5</v>
+        <v>7.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7791,7 +7781,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7805,10 +7795,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45533</v>
+        <v>44642</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7820,8 +7810,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7864,7 +7859,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 3890-2025</t>
+          <t>A 3673-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7878,10 +7873,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45684</v>
+        <v>46043</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7894,7 +7889,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7937,7 +7932,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7951,10 +7946,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45567</v>
+        <v>46048</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7967,7 +7962,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8010,7 +8005,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8024,10 +8019,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45461</v>
+        <v>44827</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8039,8 +8034,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>12.5</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21513-2025</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8093,14 +8093,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45782</v>
+        <v>45363</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 38695-2026</t>
+          <t>A 22913-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8170,10 +8170,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46283</v>
+        <v>46159</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8185,8 +8185,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8229,7 +8234,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 19031-2024</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8239,14 +8244,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45427</v>
+        <v>46086</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8259,7 +8264,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8302,7 +8307,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 35961-2024</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8316,10 +8321,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45533</v>
+        <v>46097</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8332,7 +8337,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8375,7 +8380,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 22402-2025</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8389,10 +8394,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45786</v>
+        <v>45110</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8405,7 +8410,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8448,7 +8453,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 48375-2024</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8462,10 +8467,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45590</v>
+        <v>45110</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8477,13 +8482,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8526,7 +8526,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 24105-2025</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8540,10 +8540,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45796</v>
+        <v>46275</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8599,7 +8599,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 60934-2023</t>
+          <t>A 38695-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8613,10 +8613,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45261</v>
+        <v>46283</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>45903</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>45558</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>45280</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>46156</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45520</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>45166</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>45020</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>45198</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>46057</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>46275</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44618</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>44619</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44776</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>45330</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45540</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>45061</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>45162</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>45251</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>44776</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>45187</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>45211</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44546</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>44904</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45644</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>45713</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>44557</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>45461</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>45176</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>45035</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>45567</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>45461</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>45684</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>44606</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>45191</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>45160</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>45575</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>45782</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>45054</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>45590</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>45786</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>45533</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>45427</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>45222</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>44904</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>44678</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>45930</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>45796</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>45478</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>45061</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>44749</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>45261</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>44571</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>45940</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>45084</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>45565</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45653</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>44894</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>44776</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>45819</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>45257</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>44989</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>45089</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>45089</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>44502</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45313</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>45533</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44803</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>44803</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>45700</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45261</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>44992</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45261</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>44642</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>46043</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>46048</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>44827</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>45363</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>46159</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>46086</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>46097</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>45110</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>45110</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>46275</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>46283</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>45558</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>45903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>46057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>46275</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>45166</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>45520</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45198</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>45020</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44618</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>44776</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44619</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>45089</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>45700</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45540</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45084</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>44989</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>45461</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>44827</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>44571</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>44642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44557</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>45478</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45176</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>44803</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>44678</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>45565</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>45575</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>45257</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>45363</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>45930</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>45940</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>44776</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>45035</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>45330</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>45061</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>46159</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>44904</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>44749</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>45713</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>44502</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45191</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>45110</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45261</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>45110</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>46043</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>46048</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>45054</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45160</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>45313</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>44904</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44546</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>46086</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>46097</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>45061</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>45251</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>46275</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>45187</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>44894</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44803</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>46283</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>45261</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45653</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>45162</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44606</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>44992</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>45089</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>45644</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>45222</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>44776</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>45533</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>45684</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>45567</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>45461</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>45782</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>45427</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>45533</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>45786</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>45590</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>45796</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>45261</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>45819</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>45558</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>45903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>46057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>46275</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>45166</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>45520</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45198</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>45020</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44618</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>44776</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44619</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>45089</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>45700</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45540</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45084</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>44989</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>45461</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>44827</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>44571</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>44642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44557</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>45478</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45176</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>44803</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>44678</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>45565</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>45575</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>45257</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>45363</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>45930</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>45940</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>44776</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>45035</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>45330</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>45061</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>46159</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>44904</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>44749</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>45713</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>44502</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45191</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>45110</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45261</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>45110</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>46043</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>46048</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>45054</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45160</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>45313</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>44904</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44546</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>46086</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>46097</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>45061</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>45251</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>46275</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>45187</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>44894</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44803</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>46283</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>45261</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45653</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>45162</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44606</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>44992</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>45089</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>45644</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>45222</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>44776</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>45533</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>45684</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>45567</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>45461</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>45782</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>45427</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>45533</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>45786</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>45590</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>45796</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>45261</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>45819</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>45558</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>45903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6893-2026</t>
+          <t>A 46757-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2476,14 +2476,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46057</v>
+        <v>45198</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2536,42 +2536,46 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 33751-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2581,14 +2585,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46275</v>
+        <v>45520</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2600,11 +2604,16 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2634,42 +2643,46 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svartfjällig musseron</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 37339-2026 artfynd.xlsx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 37339-2026 karta.png", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 37339-2026 georefererad karta.tif", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 37339-2026 FSC-klagomål.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 37339-2026 FSC-klagomål mail.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 37339-2026 tillsynsbegäran.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 37339-2026 tillsynsbegäran mail.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
         <v/>
       </c>
     </row>
@@ -2693,7 +2706,7 @@
         <v>45166</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2785,7 +2798,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33751-2024</t>
+          <t>A 6893-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2795,14 +2808,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45520</v>
+        <v>46057</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2814,25 +2827,20 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2847,59 +2855,55 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 46757-2023</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2909,14 +2913,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45198</v>
+        <v>46275</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2929,19 +2933,19 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2956,7 +2960,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2965,43 +2969,39 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svartfjällig musseron</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 37339-2026 artfynd.xlsx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 37339-2026 karta.png", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 37339-2026 georefererad karta.tif", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 37339-2026 FSC-klagomål.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 37339-2026 FSC-klagomål mail.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 37339-2026 tillsynsbegäran.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 37339-2026 tillsynsbegäran mail.docx", "A 37339-2026")</f>
         <v/>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
         <v>45020</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44618</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>44776</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44619</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 49592-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45089</v>
+        <v>45211</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3453,13 +3453,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3502,7 +3497,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 49592-2023</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3516,10 +3511,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45211</v>
+        <v>45251</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3527,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3575,7 +3570,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3589,10 +3584,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45700</v>
+        <v>45330</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3600,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3648,7 +3643,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3662,10 +3657,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45540</v>
+        <v>44904</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3673,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3721,7 +3716,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 24636-2023</t>
+          <t>A 41702-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3735,10 +3730,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45084</v>
+        <v>45176</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3750,8 +3745,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44989</v>
+        <v>45575</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45461</v>
+        <v>45054</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44827</v>
+        <v>45160</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3969,13 +3969,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>18.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4018,7 +4013,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4028,14 +4023,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44571</v>
+        <v>45222</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4048,7 +4043,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4091,7 +4086,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4105,10 +4100,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44642</v>
+        <v>44904</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4120,13 +4115,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4169,7 +4159,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4183,10 +4173,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44557</v>
+        <v>45061</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4199,7 +4189,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4242,7 +4232,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4256,10 +4246,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45478</v>
+        <v>44749</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4272,7 +4262,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4315,7 +4305,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 41702-2023</t>
+          <t>A 42572-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4329,10 +4319,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45176</v>
+        <v>45565</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4344,13 +4334,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4393,7 +4378,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4407,10 +4392,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44803</v>
+        <v>44894</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4423,7 +4408,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.1</v>
+        <v>5.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4466,7 +4451,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4476,14 +4461,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44678</v>
+        <v>44989</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4496,7 +4481,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4539,7 +4524,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 42572-2024</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4553,10 +4538,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45565</v>
+        <v>45089</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4568,8 +4553,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4612,7 +4602,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4626,10 +4616,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45575</v>
+        <v>45089</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4641,8 +4631,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4685,7 +4680,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4695,14 +4690,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45257</v>
+        <v>44502</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4714,13 +4709,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>14.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4763,7 +4753,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4773,14 +4763,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45363</v>
+        <v>45930</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4793,7 +4783,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4836,7 +4826,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4846,14 +4836,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45930</v>
+        <v>45363</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4866,7 +4856,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4909,7 +4899,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4923,10 +4913,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45940</v>
+        <v>45261</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4939,7 +4929,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4982,7 +4972,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4992,14 +4982,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44776</v>
+        <v>45940</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5011,13 +5001,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5060,7 +5045,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5074,10 +5059,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45035</v>
+        <v>45061</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5090,7 +5075,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5133,7 +5118,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5143,14 +5128,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45330</v>
+        <v>45187</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5163,7 +5148,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5206,7 +5191,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5216,14 +5201,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45061</v>
+        <v>44546</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5236,7 +5221,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5296,7 +5281,7 @@
         <v>46159</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5357,7 +5342,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5371,10 +5356,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44904</v>
+        <v>44557</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5387,7 +5372,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5430,7 +5415,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5444,10 +5429,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44749</v>
+        <v>45035</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5460,7 +5445,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5503,7 +5488,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5517,10 +5502,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45713</v>
+        <v>44606</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5532,13 +5517,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>9.699999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5581,7 +5561,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5591,14 +5571,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44502</v>
+        <v>45191</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5610,8 +5590,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>14.7</v>
+        <v>2.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5654,7 +5639,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5668,10 +5653,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45191</v>
+        <v>45110</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5683,13 +5668,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5732,7 +5712,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5742,14 +5722,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45110</v>
+        <v>44678</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5762,7 +5742,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5805,7 +5785,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5819,10 +5799,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45261</v>
+        <v>45478</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5835,7 +5815,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5895,7 +5875,7 @@
         <v>45110</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5968,7 +5948,7 @@
         <v>46043</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6024,7 +6004,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6034,14 +6014,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46048</v>
+        <v>44571</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6054,7 +6034,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6097,7 +6077,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6111,10 +6091,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45054</v>
+        <v>46048</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6127,7 +6107,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6170,7 +6150,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 24636-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6184,10 +6164,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45160</v>
+        <v>45084</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6200,7 +6180,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>18.1</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6243,7 +6223,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 2496-2024</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6253,14 +6233,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45313</v>
+        <v>45653</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6272,13 +6252,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6321,7 +6296,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6331,14 +6306,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44904</v>
+        <v>44776</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6350,8 +6325,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6394,7 +6374,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6404,14 +6384,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44546</v>
+        <v>46086</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6424,7 +6404,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6467,7 +6447,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6481,10 +6461,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46086</v>
+        <v>46097</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6497,7 +6477,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6540,7 +6520,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6554,10 +6534,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46097</v>
+        <v>45257</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6569,8 +6549,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6613,7 +6598,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 2496-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6627,10 +6612,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45061</v>
+        <v>45313</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6642,8 +6627,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6686,7 +6676,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6700,10 +6690,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45251</v>
+        <v>45533</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6716,7 +6706,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6759,7 +6749,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6773,10 +6763,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46275</v>
+        <v>44803</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6789,7 +6779,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6832,7 +6822,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6846,10 +6836,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45187</v>
+        <v>44803</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6862,7 +6852,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6905,7 +6895,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6915,14 +6905,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44894</v>
+        <v>45700</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6935,7 +6925,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6978,7 +6968,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6992,10 +6982,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44803</v>
+        <v>44992</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7008,7 +6998,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7051,7 +7041,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 38695-2026</t>
+          <t>A 60922-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7065,10 +7055,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46283</v>
+        <v>45261</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7081,7 +7071,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.3</v>
+        <v>7.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7124,7 +7114,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 60922-2023</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7138,10 +7128,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45261</v>
+        <v>44642</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7153,8 +7143,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>7.6</v>
+        <v>1.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7197,7 +7192,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7207,14 +7202,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45653</v>
+        <v>44827</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7226,8 +7221,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7270,7 +7270,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7284,10 +7284,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45162</v>
+        <v>46275</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7343,7 +7343,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7357,10 +7357,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44606</v>
+        <v>45540</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7430,10 +7430,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44992</v>
+        <v>45162</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 38695-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7503,10 +7503,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45089</v>
+        <v>46283</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7518,13 +7518,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7567,7 +7562,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7577,14 +7572,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45644</v>
+        <v>44776</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7596,8 +7591,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7640,7 +7640,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7654,10 +7654,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45222</v>
+        <v>45644</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7713,7 +7713,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7723,14 +7723,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44776</v>
+        <v>45713</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7744,11 +7744,11 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7791,7 +7791,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7805,10 +7805,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45533</v>
+        <v>45461</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7864,7 +7864,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 3890-2025</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7878,10 +7878,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45684</v>
+        <v>45567</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7937,7 +7937,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7951,10 +7951,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45567</v>
+        <v>45461</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8010,7 +8010,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 3890-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8024,10 +8024,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45461</v>
+        <v>45684</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>12.5</v>
+        <v>2.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8100,7 +8100,7 @@
         <v>45782</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 19031-2024</t>
+          <t>A 48375-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8166,14 +8166,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45427</v>
+        <v>45590</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8185,8 +8185,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8229,7 +8234,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 35961-2024</t>
+          <t>A 22402-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8243,10 +8248,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45533</v>
+        <v>45786</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8259,7 +8264,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8302,7 +8307,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 22402-2025</t>
+          <t>A 35961-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8316,10 +8321,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45786</v>
+        <v>45533</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8332,7 +8337,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8375,7 +8380,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 48375-2024</t>
+          <t>A 19031-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8385,14 +8390,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45590</v>
+        <v>45427</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8404,13 +8409,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8470,7 +8470,7 @@
         <v>45796</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>45261</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>45819</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>45558</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>45903</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46757-2023</t>
+          <t>A 15452-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45198</v>
+        <v>45020</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2495,8 +2495,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2505,7 +2510,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2520,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2532,50 +2537,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
         <v/>
       </c>
       <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33751-2024</t>
+          <t>A 6893-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2585,14 +2590,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45520</v>
+        <v>46057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,25 +2609,20 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2637,59 +2637,55 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 39716-2023</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2703,10 +2699,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45166</v>
+        <v>46275</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2719,22 +2715,22 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2755,50 +2751,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Svartfjällig musseron</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 37339-2026 artfynd.xlsx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 37339-2026 karta.png", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 37339-2026 georefererad karta.tif", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 37339-2026 FSC-klagomål.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 37339-2026 FSC-klagomål mail.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 37339-2026 tillsynsbegäran.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 37339-2026 tillsynsbegäran mail.docx", "A 37339-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 6893-2026</t>
+          <t>A 39716-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2812,10 +2804,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46057</v>
+        <v>45166</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2828,22 +2820,22 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2855,7 +2847,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2868,42 +2860,46 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 6893-2026 artfynd.xlsx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 6893-2026 karta.png", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 6893-2026 georefererad karta.tif", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 6893-2026 FSC-klagomål.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 6893-2026 FSC-klagomål mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 6893-2026 tillsynsbegäran.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 6893-2026 tillsynsbegäran mail.docx", "A 6893-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 33751-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2913,14 +2909,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46275</v>
+        <v>45520</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2932,11 +2928,16 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2966,49 +2967,53 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Svartfjällig musseron</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 37339-2026 artfynd.xlsx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 37339-2026 karta.png", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 37339-2026 georefererad karta.tif", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 37339-2026 FSC-klagomål.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 37339-2026 FSC-klagomål mail.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 37339-2026 tillsynsbegäran.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 37339-2026 tillsynsbegäran mail.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15452-2023</t>
+          <t>A 46757-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3022,10 +3027,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45020</v>
+        <v>45198</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3037,13 +3042,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3052,7 +3052,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -3067,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3079,43 +3079,43 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 15452-2023 artfynd.xlsx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 15452-2023 karta.png", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 15452-2023 georefererad karta.tif", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 15452-2023 FSC-klagomål.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 15452-2023 FSC-klagomål mail.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 15452-2023 tillsynsbegäran.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 15452-2023 tillsynsbegäran mail.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 15452-2023 prioriterade fågelarter.docx", "A 15452-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
         <v/>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
         <v>44618</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>44776</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44619</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 49592-2023</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45211</v>
+        <v>45089</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3453,8 +3453,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3497,7 +3502,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 49592-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3511,10 +3516,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45251</v>
+        <v>45211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3527,7 +3532,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3570,7 +3575,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3584,10 +3589,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45330</v>
+        <v>45700</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3600,7 +3605,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3643,7 +3648,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 24105-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3657,10 +3662,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44904</v>
+        <v>45796</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3673,7 +3678,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3716,7 +3721,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 41702-2023</t>
+          <t>A 60934-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3730,10 +3735,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45176</v>
+        <v>45261</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3745,13 +3750,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45575</v>
+        <v>45540</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 24636-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45054</v>
+        <v>45084</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 3673-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45160</v>
+        <v>46043</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>18.1</v>
+        <v>3.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45222</v>
+        <v>44989</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44904</v>
+        <v>46048</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45061</v>
+        <v>45461</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4232,7 +4232,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4242,14 +4242,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44749</v>
+        <v>44571</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 42572-2024</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45565</v>
+        <v>44827</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4334,8 +4334,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4378,7 +4383,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4392,10 +4397,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44894</v>
+        <v>45930</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4408,7 +4413,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4451,7 +4456,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4465,10 +4470,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44989</v>
+        <v>45940</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4524,7 +4529,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4538,10 +4543,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45089</v>
+        <v>44642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4555,11 +4560,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4602,7 +4607,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4616,10 +4621,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45089</v>
+        <v>46086</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4631,13 +4636,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4690,14 +4690,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44502</v>
+        <v>46097</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>14.7</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4753,7 +4753,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4767,10 +4767,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45930</v>
+        <v>44557</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4836,14 +4836,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45363</v>
+        <v>45478</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4899,7 +4899,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 41702-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45261</v>
+        <v>45176</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4928,8 +4928,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4972,7 +4977,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4986,10 +4991,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45940</v>
+        <v>44803</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5002,7 +5007,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5045,7 +5050,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5055,14 +5060,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45061</v>
+        <v>44678</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5075,7 +5080,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5118,7 +5123,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 28681-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5132,10 +5137,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45187</v>
+        <v>45819</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5148,7 +5153,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5191,7 +5196,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 42572-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5201,14 +5206,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44546</v>
+        <v>45565</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5221,7 +5226,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5264,7 +5269,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22913-2026</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5278,10 +5283,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46159</v>
+        <v>45575</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5293,13 +5298,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5342,7 +5342,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5356,10 +5356,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44557</v>
+        <v>45257</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5371,8 +5371,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5415,7 +5420,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5425,14 +5430,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45035</v>
+        <v>45363</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5488,7 +5493,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5498,14 +5503,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44606</v>
+        <v>44776</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5517,8 +5522,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5561,7 +5571,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5575,10 +5585,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45191</v>
+        <v>45035</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5590,13 +5600,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5639,7 +5644,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5649,14 +5654,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45110</v>
+        <v>45330</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5669,7 +5674,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5712,7 +5717,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5722,14 +5727,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44678</v>
+        <v>45061</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5742,7 +5747,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.6</v>
+        <v>0.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5785,7 +5790,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5799,10 +5804,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45478</v>
+        <v>44904</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5815,7 +5820,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5858,7 +5863,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5872,10 +5877,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45110</v>
+        <v>44749</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5888,7 +5893,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5931,7 +5936,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3673-2026</t>
+          <t>A 22913-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5945,10 +5950,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46043</v>
+        <v>46159</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5960,8 +5965,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6004,7 +6014,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6014,14 +6024,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44571</v>
+        <v>45713</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6033,8 +6043,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6077,7 +6092,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6087,14 +6102,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46048</v>
+        <v>44502</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6107,7 +6122,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>14.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6150,7 +6165,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 24636-2023</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6164,10 +6179,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45084</v>
+        <v>45191</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6179,8 +6194,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6223,7 +6243,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6233,14 +6253,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45653</v>
+        <v>45110</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6253,7 +6273,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6296,7 +6316,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6306,14 +6326,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44776</v>
+        <v>45110</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6325,13 +6345,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6374,7 +6389,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6388,10 +6403,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46086</v>
+        <v>45261</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6404,7 +6419,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6447,7 +6462,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6461,10 +6476,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46097</v>
+        <v>45054</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6477,7 +6492,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6520,7 +6535,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6534,10 +6549,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45257</v>
+        <v>45160</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6549,13 +6564,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>18.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6615,7 +6625,7 @@
         <v>45313</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6676,7 +6686,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6690,10 +6700,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45533</v>
+        <v>44904</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6706,7 +6716,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6749,7 +6759,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6759,14 +6769,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44803</v>
+        <v>44546</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6779,7 +6789,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.1</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6822,7 +6832,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6836,10 +6846,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44803</v>
+        <v>46275</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6852,7 +6862,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6895,7 +6905,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 38695-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6905,14 +6915,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45700</v>
+        <v>46283</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6925,7 +6935,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6968,7 +6978,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6982,10 +6992,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44992</v>
+        <v>45061</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6998,7 +7008,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7041,7 +7051,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60922-2023</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7055,10 +7065,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45261</v>
+        <v>45251</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7071,7 +7081,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>7.6</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7114,7 +7124,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7128,10 +7138,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44642</v>
+        <v>45187</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7143,13 +7153,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7192,7 +7197,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7206,10 +7211,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44827</v>
+        <v>44894</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7221,13 +7226,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7270,7 +7270,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7284,10 +7284,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46275</v>
+        <v>44803</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7343,7 +7343,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 60922-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7357,10 +7357,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45540</v>
+        <v>45261</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7426,14 +7426,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45162</v>
+        <v>45653</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7489,7 +7489,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 38695-2026</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7503,10 +7503,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46283</v>
+        <v>45162</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7562,7 +7562,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7572,14 +7572,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44776</v>
+        <v>44606</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7591,13 +7591,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7640,7 +7635,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7654,10 +7649,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45644</v>
+        <v>44992</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7670,7 +7665,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7713,7 +7708,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7727,10 +7722,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45713</v>
+        <v>45089</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7744,11 +7739,11 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>9.699999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7791,7 +7786,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7805,10 +7800,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45461</v>
+        <v>45644</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7821,7 +7816,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7864,7 +7859,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 43158-2024</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7878,10 +7873,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45567</v>
+        <v>45222</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7894,7 +7889,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7937,7 +7932,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 24946-2024</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7947,14 +7942,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45461</v>
+        <v>44776</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7966,8 +7961,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8010,7 +8010,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 3890-2025</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8024,10 +8024,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45684</v>
+        <v>45533</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21513-2025</t>
+          <t>A 3890-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8097,10 +8097,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45782</v>
+        <v>45684</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 48375-2024</t>
+          <t>A 43158-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8170,10 +8170,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45590</v>
+        <v>45567</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8185,13 +8185,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8234,7 +8229,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 22402-2025</t>
+          <t>A 24946-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8248,10 +8243,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45786</v>
+        <v>45461</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8264,7 +8259,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8307,7 +8302,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 35961-2024</t>
+          <t>A 21513-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8321,10 +8316,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45533</v>
+        <v>45782</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8337,7 +8332,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8397,7 +8392,7 @@
         <v>45427</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8453,7 +8448,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 24105-2025</t>
+          <t>A 35961-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8467,10 +8462,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45796</v>
+        <v>45533</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8483,7 +8478,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8526,7 +8521,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 60934-2023</t>
+          <t>A 22402-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8540,10 +8535,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45261</v>
+        <v>45786</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8556,7 +8551,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8599,7 +8594,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 28681-2025</t>
+          <t>A 48375-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8613,10 +8608,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45819</v>
+        <v>45590</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8628,8 +8623,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 40643-2024</t>
+          <t>A 41957-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2043,14 +2043,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45558</v>
+        <v>45903</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2099,146 +2099,146 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Gröngöling
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 40643-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45558</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Bergsslok
 Getrams</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 41957-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45903</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Gröngöling
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
         <v/>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
         <v>46156</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45020</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>46057</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 37339-2026</t>
+          <t>A 46757-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2695,14 +2695,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46275</v>
+        <v>45198</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2715,19 +2715,19 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2742,7 +2742,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2751,46 +2751,50 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Svartfjällig musseron</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 37339-2026 artfynd.xlsx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 37339-2026 karta.png", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 37339-2026 georefererad karta.tif", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 37339-2026 FSC-klagomål.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 37339-2026 FSC-klagomål mail.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 37339-2026 tillsynsbegäran.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 37339-2026 tillsynsbegäran mail.docx", "A 37339-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 39716-2023</t>
+          <t>A 33751-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2800,14 +2804,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45166</v>
+        <v>45520</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2819,8 +2823,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2832,10 +2841,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2853,53 +2862,53 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
         <v/>
       </c>
       <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33751-2024</t>
+          <t>A 39716-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2909,14 +2918,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45520</v>
+        <v>45166</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2928,13 +2937,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2946,10 +2950,10 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2967,53 +2971,53 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 33751-2024 artfynd.xlsx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 39716-2023 artfynd.xlsx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 33751-2024 karta.png", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 39716-2023 karta.png", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 33751-2024 georefererad karta.tif", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 39716-2023 georefererad karta.tif", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 33751-2024 FSC-klagomål.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 39716-2023 FSC-klagomål.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 33751-2024 FSC-klagomål mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 39716-2023 FSC-klagomål mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 33751-2024 tillsynsbegäran.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 39716-2023 tillsynsbegäran.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 33751-2024 tillsynsbegäran mail.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 39716-2023 tillsynsbegäran mail.docx", "A 39716-2023")</f>
         <v/>
       </c>
       <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 33751-2024 prioriterade fågelarter.docx", "A 33751-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 39716-2023 prioriterade fågelarter.docx", "A 39716-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 46757-2023</t>
+          <t>A 37339-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3023,14 +3027,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45198</v>
+        <v>46275</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3043,19 +3047,19 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -3070,7 +3074,7 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3079,43 +3083,39 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svartfjällig musseron</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 46757-2023 artfynd.xlsx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 37339-2026 artfynd.xlsx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 46757-2023 karta.png", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 37339-2026 karta.png", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 46757-2023 georefererad karta.tif", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 37339-2026 georefererad karta.tif", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 46757-2023 FSC-klagomål.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 37339-2026 FSC-klagomål.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 46757-2023 FSC-klagomål mail.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 37339-2026 FSC-klagomål mail.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 46757-2023 tillsynsbegäran.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 37339-2026 tillsynsbegäran.docx", "A 37339-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 46757-2023 tillsynsbegäran mail.docx", "A 46757-2023")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/fåglar/A 46757-2023 prioriterade fågelarter.docx", "A 46757-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 37339-2026 tillsynsbegäran mail.docx", "A 37339-2026")</f>
         <v/>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
         <v>44618</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>44776</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44619</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 25459-2023</t>
+          <t>A 58619-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45089</v>
+        <v>45251</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3453,13 +3453,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3519,7 +3514,7 @@
         <v>45211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3575,7 +3570,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 6826-2025</t>
+          <t>A 5142-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3589,10 +3584,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45700</v>
+        <v>45330</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3605,7 +3600,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3648,7 +3643,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 24105-2025</t>
+          <t>A 19031-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3658,14 +3653,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45796</v>
+        <v>45427</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3678,7 +3673,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3721,7 +3716,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60934-2023</t>
+          <t>A 24105-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3735,10 +3730,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45261</v>
+        <v>45796</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3751,7 +3746,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3794,7 +3789,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 37392-2024</t>
+          <t>A 59168-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3808,10 +3803,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45540</v>
+        <v>44904</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3824,7 +3819,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3867,7 +3862,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 24636-2023</t>
+          <t>A 60934-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3881,10 +3876,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45084</v>
+        <v>45261</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3897,7 +3892,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3940,7 +3935,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3673-2026</t>
+          <t>A 41702-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3954,10 +3949,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46043</v>
+        <v>45176</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3969,8 +3964,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10790-2023</t>
+          <t>A 38276-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44989</v>
+        <v>45160</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>18.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4788-2026</t>
+          <t>A 45233-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46048</v>
+        <v>45575</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4159,7 +4159,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24967-2024</t>
+          <t>A 20375-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45461</v>
+        <v>45054</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4232,7 +4232,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 862-2022</t>
+          <t>A 47392-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4242,14 +4242,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44571</v>
+        <v>45930</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 41693-2022</t>
+          <t>A 51770-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44827</v>
+        <v>45222</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4334,13 +4334,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4383,7 +4378,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 47392-2025</t>
+          <t>A 49916-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4397,10 +4392,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45930</v>
+        <v>45940</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4413,7 +4408,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4456,7 +4451,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 49916-2025</t>
+          <t>A 59165-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4470,10 +4465,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45940</v>
+        <v>44904</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4529,7 +4524,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12931-2022</t>
+          <t>A 28681-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4543,10 +4538,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44642</v>
+        <v>45819</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4558,13 +4553,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>1.8</v>
+        <v>7.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4607,7 +4597,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12052-2026</t>
+          <t>A 20960-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4621,10 +4611,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46086</v>
+        <v>45061</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4637,7 +4627,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4680,7 +4670,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13662-2026</t>
+          <t>A 28851-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4694,10 +4684,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46097</v>
+        <v>44749</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4710,7 +4700,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4753,7 +4743,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 74170-2021</t>
+          <t>A 3673-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4767,10 +4757,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44557</v>
+        <v>46043</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4783,7 +4773,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4826,7 +4816,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28752-2024</t>
+          <t>A 42572-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4840,10 +4830,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45478</v>
+        <v>45565</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4856,7 +4846,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4899,7 +4889,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 41702-2023</t>
+          <t>A 4788-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4913,10 +4903,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45176</v>
+        <v>46048</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4928,13 +4918,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4977,7 +4962,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 36179-2022</t>
+          <t>A 56796-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4991,10 +4976,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44803</v>
+        <v>44894</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5007,7 +4992,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>6.1</v>
+        <v>5.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5050,7 +5035,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17286-2022</t>
+          <t>A 10790-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5060,14 +5045,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44678</v>
+        <v>44989</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5080,7 +5065,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5123,7 +5108,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 28681-2025</t>
+          <t>A 25452-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5137,10 +5122,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45819</v>
+        <v>45089</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5152,8 +5137,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>7.5</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5196,7 +5186,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 42572-2024</t>
+          <t>A 25459-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5210,10 +5200,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45565</v>
+        <v>45089</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5225,8 +5215,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5269,7 +5264,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45233-2024</t>
+          <t>A 61937-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5279,14 +5274,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45575</v>
+        <v>44502</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5299,7 +5294,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>14.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5342,7 +5337,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59957-2023</t>
+          <t>A 12052-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5356,10 +5351,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45257</v>
+        <v>46086</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5371,13 +5366,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5420,7 +5410,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9856-2024</t>
+          <t>A 13662-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5430,14 +5420,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45363</v>
+        <v>46097</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5450,7 +5440,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5493,7 +5483,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 31695-2022</t>
+          <t>A 60935-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5503,14 +5493,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44776</v>
+        <v>45261</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5522,13 +5512,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5571,7 +5556,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 17320-2023</t>
+          <t>A 20957-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5585,10 +5570,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45035</v>
+        <v>45061</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5601,7 +5586,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5644,7 +5629,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 5142-2024</t>
+          <t>A 43700-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5654,14 +5639,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45330</v>
+        <v>45187</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5674,7 +5659,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5717,7 +5702,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 20957-2023</t>
+          <t>A 72530-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5727,14 +5712,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45061</v>
+        <v>44546</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5747,7 +5732,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5790,7 +5775,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 59165-2022</t>
+          <t>A 74170-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5804,10 +5789,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44904</v>
+        <v>44557</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5820,7 +5805,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5863,7 +5848,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 28851-2022</t>
+          <t>A 17320-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5877,10 +5862,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44749</v>
+        <v>45035</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5893,7 +5878,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5936,7 +5921,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22913-2026</t>
+          <t>A 7214-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5950,10 +5935,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46159</v>
+        <v>44606</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5965,13 +5950,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6014,7 +5994,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9120-2025</t>
+          <t>A 45319-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6028,10 +6008,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45713</v>
+        <v>45191</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6049,7 +6029,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>9.699999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6092,7 +6072,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 61937-2021</t>
+          <t>A 17286-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6106,10 +6086,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44502</v>
+        <v>44678</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6122,7 +6102,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>14.7</v>
+        <v>3.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6165,7 +6145,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 45319-2023</t>
+          <t>A 28752-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6179,10 +6159,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45191</v>
+        <v>45478</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6194,13 +6174,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6243,7 +6218,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 32424-2023</t>
+          <t>A 9856-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6253,14 +6228,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45110</v>
+        <v>45363</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6273,7 +6248,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6316,7 +6291,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 32426-2023</t>
+          <t>A 862-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6326,14 +6301,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45110</v>
+        <v>44571</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6346,7 +6321,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6389,7 +6364,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60935-2023</t>
+          <t>A 22913-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6403,10 +6378,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45261</v>
+        <v>46159</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6418,8 +6393,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6462,7 +6442,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 20375-2023</t>
+          <t>A 24636-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6476,10 +6456,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45054</v>
+        <v>45084</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6492,7 +6472,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6535,7 +6515,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 38276-2023</t>
+          <t>A 273-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6545,14 +6525,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45160</v>
+        <v>45653</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6565,7 +6545,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>18.1</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6608,7 +6588,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 2496-2024</t>
+          <t>A 31695-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6618,14 +6598,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45313</v>
+        <v>44776</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6643,7 +6623,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6686,7 +6666,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 59168-2022</t>
+          <t>A 32424-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6700,10 +6680,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44904</v>
+        <v>45110</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6716,7 +6696,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6759,7 +6739,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 72530-2021</t>
+          <t>A 32426-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6769,14 +6749,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44546</v>
+        <v>45110</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6789,7 +6769,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6832,7 +6812,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 37345-2026</t>
+          <t>A 59957-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6846,10 +6826,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46275</v>
+        <v>45257</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6861,8 +6841,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6905,7 +6890,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38695-2026</t>
+          <t>A 2496-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6919,10 +6904,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46283</v>
+        <v>45313</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6934,8 +6919,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6978,7 +6968,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 20960-2023</t>
+          <t>A 35966-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6992,10 +6982,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45061</v>
+        <v>45533</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7008,7 +6998,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7051,7 +7041,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 58619-2023</t>
+          <t>A 36179-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7065,10 +7055,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45251</v>
+        <v>44803</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7081,7 +7071,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>6.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7124,7 +7114,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 43700-2023</t>
+          <t>A 36181-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7138,10 +7128,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45187</v>
+        <v>44803</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7154,7 +7144,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7197,7 +7187,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 56796-2022</t>
+          <t>A 6826-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7207,14 +7197,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44894</v>
+        <v>45700</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7227,7 +7217,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7270,7 +7260,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 36181-2022</t>
+          <t>A 11285-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7284,10 +7274,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44803</v>
+        <v>44992</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7300,7 +7290,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7360,7 +7350,7 @@
         <v>45261</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7416,7 +7406,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 273-2025</t>
+          <t>A 12931-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7426,14 +7416,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45653</v>
+        <v>44642</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7445,8 +7435,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7489,7 +7484,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 38465-2023</t>
+          <t>A 37345-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7503,10 +7498,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45162</v>
+        <v>46275</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7519,7 +7514,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7562,7 +7557,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 7214-2022</t>
+          <t>A 41693-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7576,10 +7571,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44606</v>
+        <v>44827</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7591,8 +7586,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7635,7 +7635,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 11285-2023</t>
+          <t>A 37392-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44992</v>
+        <v>45540</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7708,7 +7708,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 25452-2023</t>
+          <t>A 38695-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7722,10 +7722,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45089</v>
+        <v>46283</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7737,13 +7737,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7786,7 +7781,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 60865-2024</t>
+          <t>A 38465-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7800,10 +7795,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45644</v>
+        <v>45162</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7816,7 +7811,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7859,7 +7854,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 51770-2023</t>
+          <t>A 31684-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7869,14 +7864,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45222</v>
+        <v>44776</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7888,8 +7883,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7932,7 +7932,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 31684-2022</t>
+          <t>A 60865-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7942,14 +7942,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44776</v>
+        <v>45644</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7961,13 +7961,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8010,7 +8005,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 35966-2024</t>
+          <t>A 9120-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8024,10 +8019,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45533</v>
+        <v>45713</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8039,8 +8034,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 3890-2025</t>
+          <t>A 24967-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8097,10 +8097,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45684</v>
+        <v>45461</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
         <v>45567</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>45461</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 21513-2025</t>
+          <t>A 3890-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45782</v>
+        <v>45684</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8375,7 +8375,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 19031-2024</t>
+          <t>A 21513-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8385,14 +8385,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45427</v>
+        <v>45782</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8448,7 +8448,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 35961-2024</t>
+          <t>A 48375-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8462,10 +8462,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45533</v>
+        <v>45590</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8477,8 +8477,13 @@
           <t>SIGTUNA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8538,7 +8543,7 @@
         <v>45786</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8594,7 +8599,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48375-2024</t>
+          <t>A 35961-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8608,10 +8613,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45590</v>
+        <v>45533</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8623,13 +8628,8 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>

--- a/Översikt SIGTUNA.xlsx
+++ b/Översikt SIGTUNA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE97"/>
+  <dimension ref="A1:AE98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44761</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44502</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>45163</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45163</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>45607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45786</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46043</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41957-2025</t>
+          <t>A 40643-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2043,14 +2043,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45903</v>
+        <v>45558</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2099,153 +2099,153 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Bergsslok
+Getrams</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 41957-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45903</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SIGTUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Gröngöling
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 41957-2025 artfynd.xlsx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 41957-2025 karta.png", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 41957-2025 georefererad karta.tif", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 41957-2025 FSC-klagomål.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 41957-2025 FSC-klagomål mail.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 41957-2025 tillsynsbegäran.docx", "A 41957-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 41957-2025 tillsynsbegäran mail.docx", "A 41957-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 40643-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45558</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SIGTUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Bergsslok
-Getrams</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 40643-2024 artfynd.xlsx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 40643-2024 karta.png", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 40643-2024 georefererad karta.tif", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 40643-2024 FSC-klagomål.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsmail/A 40643-2024 FSC-klagomål mail.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsyn/A 40643-2024 tillsynsbegäran.docx", "A 40643-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0191/tillsynsmail/A 40643-2024 tillsynsbegäran mail.docx", "A 40643-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 22874-2026</t>
+          <t>A 64345-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2255,14 +2255,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46156</v>
+        <v>45280</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2274,16 +2274,11 @@
           <t>SIGTUNA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>9.199999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2313,160 +2308,165 @@
         <v>2</v>
       </c>
       <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/artfynd/A 64345-2023 artfynd.xlsx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor/A 64345-2023 karta.png", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/kartor_geotiff/A 64345-2023 georefererad karta.tif", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomål/A 64345-2023 FSC-klagomål.docx", "A 64345-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0191/klagomålsm